--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D907AC-A013-4E3B-A71E-B146E799C0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35EDF40-CB69-4483-81A8-7957D8340E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3860,29 +3860,31 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="181" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3896,8 +3898,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4358,13 +4358,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4564,22 +4564,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="345" t="s">
+      <c r="B36" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C36" s="345"/>
-      <c r="D36" s="345"/>
-      <c r="E36" s="345"/>
-      <c r="F36" s="345"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="347" t="s">
+      <c r="B37" s="352" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="347"/>
-      <c r="D37" s="347"/>
-      <c r="E37" s="347"/>
-      <c r="F37" s="347"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4591,13 +4591,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="346" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="346"/>
-      <c r="D40" s="346"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4617,13 +4617,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="346" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="346"/>
-      <c r="D43" s="346"/>
-      <c r="E43" s="346"/>
-      <c r="F43" s="346"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4652,13 +4652,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="346" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="346"/>
-      <c r="D47" s="346"/>
-      <c r="E47" s="346"/>
-      <c r="F47" s="346"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4674,13 +4674,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="346" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="346"/>
-      <c r="D50" s="346"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="346" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="346"/>
-      <c r="D58" s="346"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4766,13 +4766,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="346" t="s">
+      <c r="B61" s="350" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="349"/>
-      <c r="D61" s="349"/>
-      <c r="E61" s="349"/>
-      <c r="F61" s="349"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4788,22 +4788,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="349" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="345" t="s">
+      <c r="B65" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C65" s="345"/>
-      <c r="D65" s="345"/>
-      <c r="E65" s="345"/>
-      <c r="F65" s="345"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4872,22 +4872,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="345" t="s">
+      <c r="B74" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C74" s="345"/>
-      <c r="D74" s="345"/>
-      <c r="E74" s="345"/>
-      <c r="F74" s="345"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="347" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="347"/>
-      <c r="D75" s="347"/>
-      <c r="E75" s="347"/>
-      <c r="F75" s="347"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4931,22 +4931,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="345" t="s">
+      <c r="B83" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C83" s="345"/>
-      <c r="D83" s="345"/>
-      <c r="E83" s="345"/>
-      <c r="F83" s="345"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="345" t="s">
+      <c r="B84" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C84" s="345"/>
-      <c r="D84" s="345"/>
-      <c r="E84" s="345"/>
-      <c r="F84" s="345"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4983,13 +4983,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="345" t="s">
+      <c r="B91" s="349" t="s">
         <v>369</v>
       </c>
-      <c r="C91" s="345"/>
-      <c r="D91" s="345"/>
-      <c r="E91" s="345"/>
-      <c r="F91" s="345"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5002,13 +5002,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="345" t="s">
+      <c r="B95" s="349" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="345"/>
-      <c r="D95" s="345"/>
-      <c r="E95" s="345"/>
-      <c r="F95" s="345"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5139,13 +5139,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="345" t="s">
+      <c r="B111" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C111" s="345"/>
-      <c r="D111" s="345"/>
-      <c r="E111" s="345"/>
-      <c r="F111" s="345"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5184,13 +5184,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="346" t="s">
+      <c r="B118" s="350" t="s">
         <v>371</v>
       </c>
-      <c r="C118" s="346"/>
-      <c r="D118" s="346"/>
-      <c r="E118" s="346"/>
-      <c r="F118" s="346"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5333,13 +5333,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="350" t="s">
+      <c r="B129" s="353" t="s">
         <v>374</v>
       </c>
-      <c r="C129" s="350"/>
-      <c r="D129" s="350"/>
-      <c r="E129" s="350"/>
-      <c r="F129" s="350"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5352,22 +5352,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="348" t="s">
+      <c r="B133" s="354" t="s">
         <v>372</v>
       </c>
-      <c r="C133" s="348"/>
-      <c r="D133" s="348"/>
-      <c r="E133" s="348"/>
-      <c r="F133" s="348"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="345" t="s">
+      <c r="B134" s="349" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="345"/>
-      <c r="D134" s="345"/>
-      <c r="E134" s="345"/>
-      <c r="F134" s="345"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5700,13 +5700,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="352" t="s">
+      <c r="B174" s="348" t="s">
         <v>380</v>
       </c>
-      <c r="C174" s="345"/>
-      <c r="D174" s="345"/>
-      <c r="E174" s="345"/>
-      <c r="F174" s="345"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5714,13 +5714,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="349" t="s">
+      <c r="B177" s="351" t="s">
         <v>384</v>
       </c>
-      <c r="C177" s="349"/>
-      <c r="D177" s="349"/>
-      <c r="E177" s="349"/>
-      <c r="F177" s="349"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="214" t="s">
@@ -5743,13 +5743,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="346" t="s">
+      <c r="B183" s="350" t="s">
         <v>385</v>
       </c>
-      <c r="C183" s="346"/>
-      <c r="D183" s="346"/>
-      <c r="E183" s="346"/>
-      <c r="F183" s="346"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5757,22 +5757,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="351" t="s">
+      <c r="B186" s="347" t="s">
         <v>386</v>
       </c>
-      <c r="C186" s="351"/>
-      <c r="D186" s="351"/>
-      <c r="E186" s="351"/>
-      <c r="F186" s="351"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="351" t="s">
+      <c r="B187" s="347" t="s">
         <v>387</v>
       </c>
-      <c r="C187" s="351"/>
-      <c r="D187" s="351"/>
-      <c r="E187" s="351"/>
-      <c r="F187" s="351"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5796,17 +5796,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5823,6 +5812,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -8442,7 +8442,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80 C19:M25">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
     <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
@@ -9550,8 +9550,8 @@
       <c r="B75" s="80" t="s">
         <v>322</v>
       </c>
-      <c r="C75" s="357"/>
-      <c r="D75" s="358">
+      <c r="C75" s="345"/>
+      <c r="D75" s="346">
         <f>MAX(-D73*D76,G5)</f>
         <v>932345179.85106742</v>
       </c>
@@ -15481,10 +15481,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="353" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="353"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15499,8 +15499,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="353"/>
-      <c r="F7" s="353"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15515,8 +15515,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15531,8 +15531,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -17011,8 +17011,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="353"/>
-      <c r="F6" s="353"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18477,11 +18477,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="355" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 景津装备(603279.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="355"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18502,8 +18502,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="355"/>
-      <c r="F8" s="355"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18524,8 +18524,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="355"/>
-      <c r="F9" s="355"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18535,8 +18535,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="355"/>
-      <c r="F10" s="355"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18549,8 +18549,8 @@
       <c r="B11" s="159" t="s">
         <v>452</v>
       </c>
-      <c r="E11" s="355"/>
-      <c r="F11" s="355"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18568,8 +18568,8 @@
         <v>9.6365877843450409E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="355"/>
-      <c r="F12" s="355"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18586,8 +18586,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.12333037284725878</v>
       </c>
-      <c r="E13" s="355"/>
-      <c r="F13" s="355"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18604,8 +18604,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.10557193538775511</v>
       </c>
-      <c r="E14" s="355"/>
-      <c r="F14" s="355"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18631,21 +18631,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="355" t="s">
+      <c r="E18" s="357" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="356"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="356"/>
-      <c r="F19" s="356"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>305</v>
       </c>
-      <c r="E20" s="356"/>
-      <c r="F20" s="356"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18659,8 +18659,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="356"/>
-      <c r="F21" s="356"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18674,8 +18674,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="356"/>
-      <c r="F22" s="356"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18695,8 +18695,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="354"/>
-      <c r="F25" s="354"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18706,8 +18706,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="354"/>
-      <c r="F26" s="354"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18721,8 +18721,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="354"/>
-      <c r="F27" s="354"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18732,8 +18732,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="354"/>
-      <c r="F28" s="354"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18753,8 +18753,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="354"/>
-      <c r="F31" s="354"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18764,8 +18764,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="354"/>
-      <c r="F32" s="354"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18779,8 +18779,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="354"/>
-      <c r="F33" s="354"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18790,8 +18790,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="354"/>
-      <c r="F34" s="354"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18811,8 +18811,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="354"/>
-      <c r="F37" s="354"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18822,8 +18822,8 @@
         <v>0.09</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="354"/>
-      <c r="F38" s="354"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18837,8 +18837,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="354"/>
-      <c r="F39" s="354"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18849,8 +18849,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="354"/>
-      <c r="F40" s="354"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18912,8 +18912,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="354"/>
-      <c r="F49" s="354"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18923,8 +18923,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="354"/>
-      <c r="F50" s="354"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18938,8 +18938,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="354"/>
-      <c r="F51" s="354"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18949,8 +18949,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="354"/>
-      <c r="F52" s="354"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -18970,8 +18970,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="354"/>
-      <c r="F55" s="354"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -18981,8 +18981,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="354"/>
-      <c r="F56" s="354"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -18996,8 +18996,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="354"/>
-      <c r="F57" s="354"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19007,8 +19007,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="354"/>
-      <c r="F58" s="354"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35EDF40-CB69-4483-81A8-7957D8340E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E51AE5-6E5D-4131-8683-B0138C7107A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4300,7 +4300,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>16.350000000000001</v>
+        <v>16.52</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9425.0719499999996</v>
+        <v>9523.0696399999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="E26" s="302">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21749652247472429</v>
+        <v>0.21308600349914264</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C29" s="311">
         <f>C144</f>
-        <v>11.008213811100902</v>
+        <v>12.534408209968158</v>
       </c>
       <c r="D29" s="311" t="str">
         <f>D144</f>
@@ -4489,7 +4489,7 @@
         <v>429</v>
       </c>
       <c r="F29" s="303">
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="C30" s="312">
         <f>C152</f>
-        <v>16.254577859854386</v>
+        <v>17.577047192866189</v>
       </c>
       <c r="D30" s="312" t="str">
         <f>D152</f>
@@ -4508,7 +4508,7 @@
         <v>442</v>
       </c>
       <c r="F30" s="313">
-        <v>0.22</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C32" s="312">
         <f>C168</f>
-        <v>20.756795150826846</v>
+        <v>22.61787767563613</v>
       </c>
       <c r="D32" s="312" t="str">
         <f>D168</f>
@@ -4546,7 +4546,7 @@
         <v>443</v>
       </c>
       <c r="F32" s="313">
-        <v>0.12</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.3157149765156035E-2</v>
+        <v>8.230141638379547E-2</v>
       </c>
       <c r="F69" s="315"/>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.4831804281345565E-2</v>
+        <v>6.4164648910411626E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>453</v>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C137" s="224">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C141" s="297">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="C142" s="216">
         <f>Scenarios!C81</f>
-        <v>1.6842565597667636</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="C143" s="216">
         <f>Scenarios!C82</f>
-        <v>9.3239572513341376</v>
+        <v>10.705085959638616</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C144" s="215">
         <f>Scenarios!C83</f>
-        <v>11.008213811100902</v>
+        <v>12.534408209968158</v>
       </c>
       <c r="D144" s="301" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.56973851134897036</v>
+        <v>0.51008644741782672</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="C149" s="297">
         <f>Scenarios!C90</f>
-        <v>0.22</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C150" s="216">
         <f>Scenarios!C91</f>
-        <v>2.1647759063533951</v>
+        <v>2.279132885208865</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C151" s="216">
         <f>Scenarios!C92</f>
-        <v>14.089801953500992</v>
+        <v>15.297914307657322</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C152" s="215">
         <f>Scenarios!C93</f>
-        <v>16.254577859854386</v>
+        <v>17.577047192866189</v>
       </c>
       <c r="D152" s="301" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.36468177422912962</v>
+        <v>0.31299240539227124</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C165" s="92">
         <f>F32</f>
-        <v>0.12</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C166" s="216">
         <f>Scenarios!C103</f>
-        <v>2.5459411443148712</v>
+        <v>2.6975834619563113</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="C167" s="216">
         <f>Scenarios!C104</f>
-        <v>18.210854006511976</v>
+        <v>19.920294213679817</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C168" s="215">
         <f>Scenarios!C105</f>
-        <v>20.756795150826846</v>
+        <v>22.61787767563613</v>
       </c>
       <c r="D168" s="301" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.18856037332942344</v>
+        <v>0.11580559118887601</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.4831804281345565E-2</v>
+        <v>6.4164648910411626E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.4831804281345565E-2</v>
+        <v>6.4164648910411626E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4831804281345565E-2</v>
+        <v>6.4164648910411626E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.1162079510703356E-2</v>
+        <v>6.0532687651331719E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14600,50 +14600,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3157149765156035E-2</v>
+        <v>8.230141638379547E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.1965248616396364E-2</v>
+        <v>9.1018874992619903E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10487349164679642</v>
+        <v>0.10379428501362722</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.8954417306641068E-2</v>
+        <v>8.8039026813776122E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.8055422113550049E-2</v>
+        <v>6.7355093919887615E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.551007381427224E-2</v>
+        <v>5.4938844241122956E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.3883798351746231E-2</v>
+        <v>4.3432209627787585E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.6169112268686713E-2</v>
+        <v>2.5899817529844295E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.046845414267633E-2</v>
+        <v>2.0257822350651215E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0366368874245037E-2</v>
+        <v>2.0156787596483438E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.097060107854137E-2</v>
+        <v>2.0754801914900207E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14657,43 +14657,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9997317314909203E-2</v>
+        <v>8.9071194800167397E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10695827727872147</v>
+        <v>0.10585761704038112</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8478759040136565E-2</v>
+        <v>8.7568263335728369E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8647336533064873E-2</v>
+        <v>6.7940917210388058E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4607813046986871E-2</v>
+        <v>5.4045868239602626E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3827458526722443E-2</v>
+        <v>4.3376449570938974E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5938872116514716E-2</v>
+        <v>2.5671946677059059E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1852003262426024E-2</v>
+        <v>2.162713397945917E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6948937986621948E-2</v>
+        <v>1.6774523975863733E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5131097115921751E-2</v>
+        <v>1.4975389700079942E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.350000000000001</v>
+        <v>-16.52</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.350000000000001</v>
+        <v>16.52</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.4</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19201,7 +19201,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6842565597667636</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>9.3239572513341376</v>
+        <v>10.705085959638616</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>11.008213811100902</v>
+        <v>12.534408209968158</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19234,7 +19234,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.56973851134897036</v>
+        <v>0.51008644741782672</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.350000000000001</v>
+        <v>16.52</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19264,7 +19264,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21749652247472429</v>
+        <v>0.21308600349914264</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.22</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19290,7 +19290,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.1647759063533951</v>
+        <v>2.279132885208865</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19302,7 +19302,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>14.089801953500992</v>
+        <v>15.297914307657322</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>16.254577859854386</v>
+        <v>17.577047192866189</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.36468177422912962</v>
+        <v>0.31299240539227124</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
-        <v>0.12</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -19410,7 +19410,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.5459411443148712</v>
+        <v>2.6975834619563113</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>18.210854006511976</v>
+        <v>19.920294213679817</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>20.756795150826846</v>
+        <v>22.61787767563613</v>
       </c>
       <c r="D105" t="s">
         <v>400</v>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.18856037332942344</v>
+        <v>0.11580559118887601</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761D40CF-1DBD-47D0-88F3-D6F4CA3BFA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F414564D-222A-4979-B773-B4D6E81169ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4322,7 +4322,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>16.52</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9523.0696399999997</v>
+        <v>9476.9530799999993</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4380,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21308600349914264</v>
+        <v>0.21515370353352314</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4511,7 +4511,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4586,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,13 +4613,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4639,13 +4639,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4674,13 +4674,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4696,13 +4696,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4766,13 +4766,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4788,7 +4788,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4810,22 +4810,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.230141638379547E-2</v>
+        <v>8.2701909894178902E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.4164648910411626E-2</v>
+        <v>6.4476885644768861E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4960,22 +4960,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5019,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5071,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5218,13 +5218,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5263,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5412,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5431,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5779,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5822,13 +5822,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5836,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5875,6 +5875,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5891,17 +5902,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,20 +13480,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.4164648910411626E-2</v>
+        <v>6.4476885644768861E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.4164648910411626E-2</v>
+        <v>6.4476885644768861E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4164648910411626E-2</v>
+        <v>6.4476885644768861E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.0532687651331719E-2</v>
+        <v>6.0827250608272501E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.230141638379547E-2</v>
+        <v>8.2701909894178902E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.1018874992619903E-2</v>
+        <v>9.146178922616062E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10379428501362722</v>
+        <v>0.10429936669252564</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.8039026813776122E-2</v>
+        <v>8.8467440569560907E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.7355093919887615E-2</v>
+        <v>6.76828559340963E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4938844241122956E-2</v>
+        <v>5.5206186548865638E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.3432209627787585E-2</v>
+        <v>4.3643558579747624E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.5899817529844295E-2</v>
+        <v>2.6025850705172004E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0257822350651215E-2</v>
+        <v>2.0356400561603285E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0156787596483438E-2</v>
+        <v>2.0254874154130558E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.0754801914900207E-2</v>
+        <v>2.0855798517892418E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9071194800167397E-2</v>
+        <v>8.9504631271214441E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10585761704038112</v>
+        <v>0.10637273926442189</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7568263335728369E-2</v>
+        <v>8.7994386271668654E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7940917210388058E-2</v>
+        <v>6.8271529946205028E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4045868239602626E-2</v>
+        <v>5.4308865165342786E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3376449570938974E-2</v>
+        <v>4.3587527184422867E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5671946677059059E-2</v>
+        <v>2.5796870991789272E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.162713397945917E-2</v>
+        <v>2.1732375507339748E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6774523975863733E-2</v>
+        <v>1.6856151829760878E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4975389700079942E-2</v>
+        <v>1.5048262642659406E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18492,7 +18492,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.52</v>
+        <v>-16.440000000000001</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.52</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.52</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19343,7 +19343,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21308600349914264</v>
+        <v>0.21515370353352314</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F414564D-222A-4979-B773-B4D6E81169ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E879AF47-2B68-49F1-81D2-23921C8A0641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2501,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3149,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3821,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3865,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3880,6 +3854,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4380,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4511,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,19 +4629,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>1037280588.8935957</v>
       </c>
@@ -4639,19 +4655,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>213321214.99999997</v>
       </c>
@@ -4664,7 +4680,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-213321214.99999997</v>
       </c>
@@ -4674,19 +4690,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4696,19 +4712,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>13985177.697766012</v>
       </c>
@@ -4723,7 +4739,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-6249607</v>
       </c>
@@ -4738,7 +4754,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>7735570.6977660116</v>
       </c>
@@ -4756,7 +4772,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
@@ -4766,19 +4782,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-261254039.89784044</v>
       </c>
@@ -4788,19 +4804,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4810,28 +4826,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>866779085.10917377</v>
       </c>
@@ -4844,7 +4860,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>783762119.69352126</v>
       </c>
@@ -4883,10 +4899,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4908,11 +4924,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.173581864935303</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.18394654535282634</v>
       </c>
@@ -4922,11 +4938,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.69418106703013427</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.70676723862204571</v>
       </c>
@@ -4936,11 +4952,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.9427325871638936</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.9427325871638936</v>
       </c>
@@ -4960,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,19 +5106,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>270317959.52999997</v>
       </c>
@@ -5128,7 +5144,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>6.0553888114002474E-2</v>
       </c>
@@ -5137,7 +5153,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>0.26060254325045429</v>
       </c>
@@ -5151,7 +5167,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>1723046566.25</v>
       </c>
@@ -5164,7 +5180,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>790701386.39893258</v>
       </c>
@@ -5195,7 +5211,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>30193430.795999996</v>
       </c>
@@ -5218,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.829322250329541</v>
+        <v>1.8293222503295408</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5793,13 +5809,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5822,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6017,405 +6033,405 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>6129461219</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>6249319078</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>5682141447</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>4651100995</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>3329297918</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>3310864083</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>2918572854</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>2210529514</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>1544300894</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>1583235731</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>4407422084</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>4321480843</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>3978855242</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>3293652640</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>2298160068</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>2198164870</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>2065727128</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>1559929846</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>993637032</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>996799764</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>456603351</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>451772305</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>471987592</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>430231756</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>315308507</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>532728643</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>471904599</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>360354823</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>268427406</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>341642106</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>304923157</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>285858877</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>267651684</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>222391023</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>172179694</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>410723752</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>343598742</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>286174672</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>197063391</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>242768584</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>151760727</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>210426001</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>184885909</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>141554165</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>61678851</v>
       </c>
-      <c r="H8" s="334">
+      <c r="H8" s="321">
         <v>68644761</v>
       </c>
-      <c r="I8" s="334">
+      <c r="I8" s="321">
         <v>48742254</v>
       </c>
-      <c r="J8" s="334">
+      <c r="J8" s="321">
         <v>47311155</v>
       </c>
-      <c r="K8" s="334">
+      <c r="K8" s="321">
         <v>47605907</v>
       </c>
-      <c r="L8" s="334">
-        <v>0</v>
-      </c>
-      <c r="M8" s="334"/>
+      <c r="L8" s="321">
+        <v>0</v>
+      </c>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>6249607</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>4610251</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>1311423</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>394228</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>74051</v>
       </c>
-      <c r="H12" s="334">
-        <v>0</v>
-      </c>
-      <c r="I12" s="334">
-        <v>0</v>
-      </c>
-      <c r="J12" s="334">
-        <v>0</v>
-      </c>
-      <c r="K12" s="334">
-        <v>0</v>
-      </c>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="H12" s="321">
+        <v>0</v>
+      </c>
+      <c r="I12" s="321">
+        <v>0</v>
+      </c>
+      <c r="J12" s="321">
+        <v>0</v>
+      </c>
+      <c r="K12" s="321">
+        <v>0</v>
+      </c>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>37086796</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>31023567</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>31991799</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>18258659</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>12674421</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>7073727</v>
       </c>
-      <c r="I13" s="334">
-        <v>0</v>
-      </c>
-      <c r="J13" s="334">
-        <v>0</v>
-      </c>
-      <c r="K13" s="334">
-        <v>0</v>
-      </c>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="I13" s="321">
+        <v>0</v>
+      </c>
+      <c r="J13" s="321">
+        <v>0</v>
+      </c>
+      <c r="K13" s="321">
+        <v>0</v>
+      </c>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>260714131</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>289376410</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>224010347</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>153720766</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>137748165</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>101545465</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>85553107</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>50017037</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>42676057</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>47144437</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>848231191</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>1008089459</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>833918670</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>647006086</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>514682567</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>413076950</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>244475736</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>205956703</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>159744960</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>142611679</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
-        <v>0</v>
-      </c>
-      <c r="D16" s="334">
-        <v>0</v>
-      </c>
-      <c r="E16" s="334">
-        <v>0</v>
-      </c>
-      <c r="F16" s="334">
-        <v>0</v>
-      </c>
-      <c r="G16" s="334">
-        <v>0</v>
-      </c>
-      <c r="H16" s="334">
-        <v>0</v>
-      </c>
-      <c r="I16" s="334">
-        <v>0</v>
-      </c>
-      <c r="J16" s="334">
-        <v>0</v>
-      </c>
-      <c r="K16" s="334">
-        <v>0</v>
-      </c>
-      <c r="L16" s="334">
-        <v>0</v>
-      </c>
-      <c r="M16" s="334"/>
+      <c r="C16" s="321">
+        <v>0</v>
+      </c>
+      <c r="D16" s="321">
+        <v>0</v>
+      </c>
+      <c r="E16" s="321">
+        <v>0</v>
+      </c>
+      <c r="F16" s="321">
+        <v>0</v>
+      </c>
+      <c r="G16" s="321">
+        <v>0</v>
+      </c>
+      <c r="H16" s="321">
+        <v>0</v>
+      </c>
+      <c r="I16" s="321">
+        <v>0</v>
+      </c>
+      <c r="J16" s="321">
+        <v>0</v>
+      </c>
+      <c r="K16" s="321">
+        <v>0</v>
+      </c>
+      <c r="L16" s="321">
+        <v>0</v>
+      </c>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6427,175 +6443,175 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>213321215</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>173104850</v>
       </c>
-      <c r="E19" s="334">
+      <c r="E19" s="321">
         <v>130450506</v>
       </c>
-      <c r="F19" s="334">
+      <c r="F19" s="321">
         <v>105234144</v>
       </c>
-      <c r="G19" s="334">
+      <c r="G19" s="321">
         <v>99116575</v>
       </c>
-      <c r="H19" s="334">
+      <c r="H19" s="321">
         <v>95719410</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="321">
         <v>87904740</v>
       </c>
-      <c r="J19" s="334">
+      <c r="J19" s="321">
         <v>78828048</v>
       </c>
-      <c r="K19" s="334">
+      <c r="K19" s="321">
         <v>74835527</v>
       </c>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>1040530375</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>268029963</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>1022817247</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>577079594</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>610942604</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>443891507</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>326910600</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>29944782</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>366836089</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>298070452</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-241780101</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-44910807</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-310348060</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-333430153</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>206352378</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-307940933</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-21315461</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-61592804</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-40659058</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-49353967</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-865081548</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-517389967</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-285534453</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-463128689</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-123908474</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>261892739</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-5745476</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-109372169</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-375277495</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>-28573770</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6635,186 +6651,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>1180157900.1600001</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>851687201</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>790890033</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>567013771</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>458930449</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>595526269</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>643156397</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>642505610</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>606387186</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>754112914</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>2566018245.5700002</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>2819492731</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>2459595915</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>1867069694</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>1603890018</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>1464309401</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>1241320451</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>957439830</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>589826147</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>412378412</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>4208442385.48</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>4086723205</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>3962039491</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>2581011486</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>2275269694</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>2004846282</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>1560581012</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>1160274283</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>894522509</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>1020621379</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>4464089226.1300011</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>4542064792</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>4014575003</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>3369724644</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>2971650742</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>2672345812</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>2009953108</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>1762034156</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>1651561675</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>1489799476</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>0</v>
       </c>
-      <c r="D32" s="334">
-        <v>0</v>
-      </c>
-      <c r="E32" s="334">
-        <v>0</v>
-      </c>
-      <c r="F32" s="334">
-        <v>0</v>
-      </c>
-      <c r="G32" s="334">
-        <v>0</v>
-      </c>
-      <c r="H32" s="334">
-        <v>0</v>
-      </c>
-      <c r="I32" s="334">
-        <v>0</v>
-      </c>
-      <c r="J32" s="334">
-        <v>0</v>
-      </c>
-      <c r="K32" s="334">
-        <v>0</v>
-      </c>
-      <c r="L32" s="334">
-        <v>0</v>
-      </c>
-      <c r="M32" s="334"/>
+      <c r="D32" s="321">
+        <v>0</v>
+      </c>
+      <c r="E32" s="321">
+        <v>0</v>
+      </c>
+      <c r="F32" s="321">
+        <v>0</v>
+      </c>
+      <c r="G32" s="321">
+        <v>0</v>
+      </c>
+      <c r="H32" s="321">
+        <v>0</v>
+      </c>
+      <c r="I32" s="321">
+        <v>0</v>
+      </c>
+      <c r="J32" s="321">
+        <v>0</v>
+      </c>
+      <c r="K32" s="321">
+        <v>0</v>
+      </c>
+      <c r="L32" s="321">
+        <v>0</v>
+      </c>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6841,47 +6857,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>6129461219</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>6249319078</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>5682141447</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>4651100995</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>3329297918</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>3310864083</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>2918572854</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>2210529514</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>1544300894</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>1583235731</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6890,47 +6906,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-4407422084</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-4321480843</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-3978855242</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-3293652640</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-2298160068</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-2198164870</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-2065727128</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-1559929846</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-993637032</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-996799764</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6939,47 +6955,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>1722039135</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>1927838235</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>1703286205</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>1357448355</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>1031137850</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>1112699213</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>852845726</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>650599668</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>550663862</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>586435967</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6988,47 +7004,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-456603351</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-451772305</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-471987592</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-430231756</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-315308507</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-532728643</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-471904599</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-360354823</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-268427406</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-341642106</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7037,47 +7053,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-304923157</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-285858877</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-267651684</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-222391023</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-172179694</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-410723752</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-343598742</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-286174672</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-197063391</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-242768584</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7086,47 +7102,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-151680194</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-165913428</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-204335908</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-207840733</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-143128813</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-122004891</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-128305857</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-74180151</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-71364015</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-98873522</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7135,47 +7151,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-151760727</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-210426001</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-184885909</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-141554165</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-61678851</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>-68644761</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>-48742254</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>-47311155</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>-47605907</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7184,47 +7200,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>1113675057</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>1265639929</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>1046412704</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>785662434</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>654150492</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>511325809</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>332198873</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>242933690</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>234630549</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>244793861</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7331,47 +7347,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-260714131</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-289376410</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-224010347</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-153720766</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-137748165</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-101545465</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-85553107</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-50017037</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-42676057</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-47144437</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7380,47 +7396,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>848231191</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>1008089459</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>833918670</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>647006086</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>514682567</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>413076950</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>244475736</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>205956703</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>159744960</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>142611679</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7429,47 +7445,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7483,47 +7499,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-6249607</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-4610251</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-1311423</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-394228</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-74051</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7532,47 +7548,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>37086796</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>31023567</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>31991799</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>18258659</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>12674421</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>7073727</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7788,47 +7804,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-213321215</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-173104850</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>-130450506</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>-105234144</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>-99116575</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>-95719410</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>-87904740</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>-78828048</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>-74835527</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7837,47 +7853,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-213321215</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-173104850</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-130450506</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-105234144</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-99116575</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>-95719410</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>-87904740</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>-78828048</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>-74835527</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7886,47 +7902,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7935,47 +7951,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-66331274</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>-294270811</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>426934734</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>-219479248</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>693386508</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>397843313</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>299849663</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>-141020191</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>-49100464</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>220142715</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8357,115 +8373,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>1180157900.1600001</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>851687201</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>790890033</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>567013771</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>458930449</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>595526269</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>2566018245.5700002</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>2819492731</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>2459595915</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>1867069694</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>1603890018</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>1464309401</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>4208442385.48</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>4086723205</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>3962039491</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>2581011486</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>2275269694</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>2004846282</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>1560581012</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>1160274283</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>894522509</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>1020621379</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8474,47 +8490,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>4464089226.1300011</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>4542064792</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>4014575003</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>3369724644</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>2971650742</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>2672345812</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>2009953108</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>1762034156</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>1651561675</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>1489799476</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9597,11 +9613,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-468902548.5</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-466172589.92553371</v>
       </c>
@@ -9629,8 +9645,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>932345179.85106742</v>
       </c>
@@ -9934,54 +9950,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:I4)</f>
         <v>6020307248</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>6129461219</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>6249319078</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>5682141447</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>4651100995</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>3329297918</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>3310864083</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>2918572854</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>2210529514</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>1544300894</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>1583235731</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9991,52 +10007,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-4628427392.8564043</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-4712345241</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-4607339720</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-4246506926</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-3516043663</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-2470339762</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-2608888622</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-2409325870</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-1846104518</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-1190700423</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-1239568348</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10046,52 +10062,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>1391879855.1435957</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>1417115978</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>1641979358</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>1435634521</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>1135057332</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>858958156</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>701975461</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>509246984</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>364424996</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>353600471</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>343667383</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10101,52 +10117,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-354599266.25</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-303440921</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-376339429</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-389221817</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-349394898</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-204807664</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-190649652</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-177048111</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-121491306</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-118969922</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-98873522</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10156,54 +10172,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>1037280588.8935957</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>1113675057</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>1265639929</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>1046412704</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>785662434</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>654150492</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>511325809</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>332198873</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>242933690</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>234630549</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>244793861</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10213,52 +10229,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>213321214.99999997</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>213321215</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>173104850</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>130450506</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>105234144</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>99116575</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>95719410</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>87904740</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>78828048</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>74835527</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10268,52 +10284,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-213321214.99999997</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-213321215</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-173104850</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-130450506</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-105234144</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-99116575</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>-95719410</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>-87904740</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>-78828048</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>-74835527</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10323,54 +10339,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10380,52 +10396,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>7735570.6977660116</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>13818159.109173693</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>12176685.418780401</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>15999426.385417301</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>9485582.0078302585</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>6784112.6493268209</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>3827612.9044996742</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10435,52 +10451,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>1045016159.5913618</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1127493216.1091738</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>1277816614.4187803</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>1062412130.3854173</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>795148016.00783026</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>660934604.6493268</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>515153421.90449965</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>332198873</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>242933690</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>234630549</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>244793861</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10490,52 +10506,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-261254039.89784044</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-260714131</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-289376410</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-224010347</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-153720766</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-137748165</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-101545465</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-85553107</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-50017037</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-42676057</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-47144437</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10545,54 +10561,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>0</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>0</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>0</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>0</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>0</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>0</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10602,54 +10618,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>783762119.69352126</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>866779085.10917377</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>988440204.41878033</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>838401783.38541734</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>641427250.00783026</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>523186439.6493268</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>413607956.90449965</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>246645766</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>192916653</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>191954492</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>197649424</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10659,7 +10675,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10668,24 +10684,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10693,71 +10709,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>783762119.69352126</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>866779085.10917377</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>988440204.41878033</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>838401783.38541734</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>641427250.00783026</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>523186439.6493268</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>413607956.90449965</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>246645766</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>192916653</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>191954492</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>197649424</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10830,54 +10846,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-4328934333.5839558</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-4407422084</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-4321480843</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-3978855242</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-3293652640</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-2298160068</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-2198164870</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-2065727128</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-1559929846</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-993637032</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-996799764</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10887,54 +10903,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-299493059.2724486</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-304923157</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-285858877</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-267651684</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-222391023</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-172179694</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-410723752</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-343598742</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-286174672</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-197063391</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-242768584</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10944,54 +10960,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-4628427392.8564043</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-4712345241</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-4607339720</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-4246506926</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-3516043663</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-2470339762</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-2608888622</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-2409325870</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-1846104518</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-1190700423</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-1239568348</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11197,54 +11213,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:J33)</f>
         <v>-182442565.75</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-151680194</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-165913428</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-204335908</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-207840733</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-143128813</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-122004891</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-128305857</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-74180151</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-71364015</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-98873522</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11254,7 +11270,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>-172156700.5</v>
       </c>
@@ -11263,47 +11279,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-151760727</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-210426001</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-184885909</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-141554165</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-61678851</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>-68644761</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>-48742254</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>-47311155</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>-47605907</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11313,54 +11329,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-354599266.25</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-303440921</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-376339429</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-389221817</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-349394898</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-204807664</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-190649652</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-177048111</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-121491306</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-118969922</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-98873522</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11654,52 +11670,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-6249607</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-6249607</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-4610251</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-1311423</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-394228</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-74051</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>0</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>0</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11709,52 +11725,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>13985177.697766012</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>20067766.109173693</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>16786936.418780401</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>17310849.385417301</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>9879810.0078302585</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>6858163.6493268209</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>3827612.9044996742</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11764,54 +11780,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>25845698.493749999</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>37086796</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>31023567</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>31991799</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>18258659</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>12674421</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>7073727</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11821,52 +11837,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>7735570.6977660116</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>13818159.109173693</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>12176685.418780401</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>15999426.385417301</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>9485582.0078302585</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>6784112.6493268209</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>3827612.9044996742</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -12012,52 +12028,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12067,52 +12083,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12122,52 +12138,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12177,52 +12193,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12232,53 +12248,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>-35566924</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>5412624</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>-19164063</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>-2800013</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>-14320130</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>-3777121</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>-2170030</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>13040050</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>-32209532</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>-55037745</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12288,52 +12304,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-35566924</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>5412624</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>-19164063</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>-2800013</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>-14320130</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>-3777121</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>-2170030</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>13040050</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>-32209532</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>-55037745</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13708,54 +13724,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>8672531611.6100006</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>8672531611.6100006</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>8628787997</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>7976614494</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>5950736130</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>5246920436</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>4677192094</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>3570534120</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>2922308439</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>2546084184</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>2510420855</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13765,54 +13781,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>1180157900.1600001</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>851687201</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>790890033</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>567013771</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>458930449</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>595526269</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13822,54 +13838,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>2566018245.5700002</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>2819492731</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>2459595915</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1867069694</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>1603890018</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>1464309401</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13879,54 +13895,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>4208442385.48</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>4208442385.48</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>4086723205</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>3962039491</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>2581011486</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>2275269694</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>2004846282</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>1560581012</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>1160274283</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>894522509</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>1020621379</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13936,54 +13952,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>4464089226.1300011</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>4464089226.1300011</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>4542064792</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>4014575003</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>3369724644</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>2971650742</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>2672345812</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>2009953108</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>1762034156</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>1651561675</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>1489799476</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15481,7 +15497,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15520,7 +15536,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>783762119.69352126</v>
       </c>
@@ -15552,7 +15568,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>13062701994.892021</v>
       </c>
@@ -15560,17 +15576,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>270317959.52999997</v>
       </c>
@@ -15578,15 +15594,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>790701386.39893258</v>
       </c>
@@ -15594,15 +15610,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>30193430.795999996</v>
       </c>
@@ -15610,15 +15626,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>13613278852.556953</v>
       </c>
@@ -15685,7 +15701,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15695,7 +15711,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15709,10 +15725,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15730,7 +15746,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15752,7 +15768,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15774,7 +15790,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15794,9 +15810,19 @@
         <f t="shared" si="1"/>
         <v>776282231.1092273</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15816,9 +15842,19 @@
         <f t="shared" si="1"/>
         <v>773804831.98940206</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15838,9 +15874,19 @@
         <f t="shared" si="1"/>
         <v>771335339.15179336</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15862,7 +15908,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15884,7 +15930,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15906,7 +15952,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15928,7 +15974,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15950,7 +15996,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15972,7 +16018,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15994,11 +16040,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16014,13 +16060,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16036,13 +16092,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16058,9 +16124,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16082,7 +16158,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16104,7 +16180,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16126,7 +16202,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16148,7 +16224,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16170,7 +16246,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16192,7 +16268,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16214,7 +16290,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16236,7 +16312,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16258,7 +16334,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16280,7 +16356,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16302,11 +16378,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16322,13 +16398,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16344,13 +16430,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16366,13 +16462,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16388,9 +16494,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16412,7 +16528,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16423,11 +16539,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16437,7 +16553,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>14195313617.70599</v>
@@ -16464,7 +16580,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16486,7 +16602,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16507,14 +16623,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>13062701994.892014</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>13667588593.43734</v>
       </c>
       <c r="D58" s="123">
@@ -16526,16 +16642,26 @@
       <c r="F58" s="123">
         <v>22010314408.807312</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>13062701994.892012</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>13922280236.862001</v>
       </c>
       <c r="D59" s="123">
@@ -16547,16 +16673,26 @@
       <c r="F59" s="123">
         <v>28138817927.979591</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>13062701994.892012</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>14175344804.62105</v>
       </c>
       <c r="D60" s="123">
@@ -16568,16 +16704,26 @@
       <c r="F60" s="123">
         <v>36205586897.343864</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>13062701994.892008</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>14413727115.698677</v>
       </c>
       <c r="D61" s="123">
@@ -16589,26 +16735,56 @@
       <c r="F61" s="123">
         <v>46430268757.777794</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16980,6 +17156,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17082,7 +17328,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>10184073666.666668</v>
       </c>
@@ -17090,8 +17336,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18548,7 +18794,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>1113675057</v>
       </c>
@@ -18556,11 +18802,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 景津装备(603279.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18573,7 +18819,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>866779085.10917377</v>
       </c>
@@ -18581,8 +18827,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18595,7 +18841,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>783762119.69352126</v>
       </c>
@@ -18603,8 +18849,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18614,8 +18860,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18628,8 +18874,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18647,8 +18893,8 @@
         <v>9.6365877843450409E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18665,8 +18911,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.12333037284725878</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18683,8 +18929,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.10557193538775511</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18710,21 +18956,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18738,8 +18984,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18753,8 +18999,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18774,8 +19020,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18785,8 +19031,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18800,8 +19046,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18811,8 +19057,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18832,8 +19078,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18843,8 +19089,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18858,8 +19104,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18869,8 +19115,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18890,8 +19136,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18901,8 +19147,8 @@
         <v>0.09</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18916,8 +19162,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18928,8 +19174,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18991,8 +19237,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19002,8 +19248,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19017,8 +19263,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19028,8 +19274,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19049,8 +19295,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19060,8 +19306,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19075,8 +19321,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19086,8 +19332,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19271,7 +19517,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19280,7 +19526,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.829322250329541</v>
+        <v>1.8293222503295408</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E879AF47-2B68-49F1-81D2-23921C8A0641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8100E05D-F719-4AB9-8407-65D423A24C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>16.440000000000001</v>
+        <v>16.45</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9476.9530799999993</v>
+        <v>9482.7176500000005</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4396,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21515370353352314</v>
+        <v>0.21489448267712397</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4527,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.2701909894178902E-2</v>
+        <v>8.2651635176918009E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.4476885644768861E-2</v>
+        <v>6.4437689969604875E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13496,20 +13496,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.4476885644768861E-2</v>
+        <v>6.4437689969604875E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.4476885644768861E-2</v>
+        <v>6.4437689969604875E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4476885644768861E-2</v>
+        <v>6.4437689969604875E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.0827250608272501E-2</v>
+        <v>6.0790273556231005E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14695,50 +14695,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.2701909894178902E-2</v>
+        <v>8.2651635176918009E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.146178922616062E-2</v>
+        <v>9.1406189354290623E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10429936669252564</v>
+        <v>0.10423596282219585</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.8467440569560907E-2</v>
+        <v>8.8413660970430491E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.76828559340963E-2</v>
+        <v>6.7641711340823307E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5206186548865638E-2</v>
+        <v>5.517262655704263E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.3643558579747624E-2</v>
+        <v>4.3617027541097322E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.6025850705172004E-2</v>
+        <v>2.6010029519332997E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0356400561603285E-2</v>
+        <v>2.0344025850015688E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0254874154130558E-2</v>
+        <v>2.0242561160723795E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.0855798517892418E-2</v>
+        <v>2.0843120220921059E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14752,43 +14752,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9504631271214441E-2</v>
+        <v>8.9450221161019167E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10637273926442189</v>
+        <v>0.1063080749852338</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7994386271668654E-2</v>
+        <v>8.7940894243539985E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8271529946205028E-2</v>
+        <v>6.8230027496389706E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4308865165342786E-2</v>
+        <v>5.4275850657643489E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3587527184422867E-2</v>
+        <v>4.3561030207411061E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5796870991789272E-2</v>
+        <v>2.5781189003344415E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1732375507339748E-2</v>
+        <v>2.1719164336818569E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6856151829760878E-2</v>
+        <v>1.6845904928952514E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5048262642659406E-2</v>
+        <v>1.5039114762633473E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.440000000000001</v>
+        <v>-16.45</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.440000000000001</v>
+        <v>16.45</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.440000000000001</v>
+        <v>16.45</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21515370353352314</v>
+        <v>0.21489448267712397</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C867A5-C35B-4CB8-805C-B80468C9D7D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D537A1C1-1570-B04D-ADE0-942D305157E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,17 +4340,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>16.27</v>
+        <v>16.22</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4349,13 +4360,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9378.9553899999992</v>
+        <v>9350.1325400000005</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4377,7 +4388,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4387,27 +4398,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4435,7 +4446,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4443,7 +4454,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4451,7 +4462,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4467,7 +4478,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4481,14 +4492,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21959401557257197</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.22091218945949698</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4507,7 +4518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4523,10 +4534,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4545,7 +4556,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4564,7 +4575,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4583,11 +4594,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4597,25 +4608,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4624,16 +4635,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4646,20 +4657,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4672,7 +4683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4685,16 +4696,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4707,16 +4718,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4731,7 +4742,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4746,7 +4757,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4759,12 +4770,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4777,16 +4788,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4799,8 +4810,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4808,7 +4819,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4821,25 +4832,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4852,7 +4863,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4865,23 +4876,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.3566035566091046E-2</v>
+        <v>8.3823637401991447E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.515058389674247E-2</v>
+        <v>6.5351418002466105E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4891,7 +4902,7 @@
         <v>0.7796299472076299</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4902,7 +4913,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4915,7 +4926,7 @@
         <v>0.25256959684173202</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4929,7 +4940,7 @@
         <v>0.18394654535282634</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4943,7 +4954,7 @@
         <v>0.70676723862204571</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4957,7 +4968,7 @@
         <v>1.9427325871638936</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4967,34 +4978,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5003,7 +5014,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5012,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5021,34 +5032,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5056,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5069,7 +5080,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5079,38 +5090,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5123,7 +5134,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5136,7 +5147,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5145,7 +5156,7 @@
         <v>6.0553888114002474E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5154,12 +5165,12 @@
         <v>0.26060254325045429</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5172,7 +5183,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5185,7 +5196,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5198,12 +5209,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5216,7 +5227,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5229,16 +5240,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5251,7 +5262,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5264,7 +5275,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5274,16 +5285,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5300,7 +5311,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5322,7 +5333,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5344,7 +5355,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5366,7 +5377,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5388,7 +5399,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5410,7 +5421,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5423,16 +5434,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5442,30 +5453,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5474,16 +5485,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5496,7 +5507,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5509,26 +5520,26 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.8293222503295408</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+        <v>1.829322250329541</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5538,7 +5549,7 @@
         <v>10.705085959638616</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5551,7 +5562,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5573,12 +5584,12 @@
         <v>0.51008644741782672</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5587,7 +5598,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5597,7 +5608,7 @@
         <v>2.279132885208865</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5607,7 +5618,7 @@
         <v>15.297914307657322</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5620,7 +5631,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5633,7 +5644,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5642,12 +5653,12 @@
         <v>0.31299240539227124</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5656,7 +5667,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5666,7 +5677,7 @@
         <v>2.8333926664293383</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5676,7 +5687,7 @@
         <v>21.481607885755405</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5689,7 +5700,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5702,7 +5713,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5711,12 +5722,12 @@
         <v>4.9636161355830488E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5735,7 +5746,7 @@
         <v>2.6975834619563113</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5745,7 +5756,7 @@
         <v>19.920294213679817</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5758,7 +5769,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5771,7 +5782,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5780,7 +5791,7 @@
         <v>0.11580559118887601</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5790,21 +5801,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5813,80 +5824,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5925,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5944,15 +5955,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6001,7 +6012,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6017,7 +6028,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6025,7 +6036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6061,7 +6072,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6097,7 +6108,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6133,7 +6144,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6169,7 +6180,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6205,7 +6216,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6221,7 +6232,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6237,7 +6248,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6253,7 +6264,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6287,7 +6298,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6321,7 +6332,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6357,7 +6368,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6393,7 +6404,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6429,13 +6440,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6469,7 +6480,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6485,7 +6496,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6501,7 +6512,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6537,7 +6548,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6573,7 +6584,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6609,7 +6620,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6635,7 +6646,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6643,7 +6654,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6680,7 +6691,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6717,7 +6728,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6754,7 +6765,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6791,7 +6802,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6828,7 +6839,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6844,12 +6855,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6898,7 +6909,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6947,7 +6958,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6996,7 +7007,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7045,7 +7056,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7094,7 +7105,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7143,7 +7154,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7192,7 +7203,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7241,7 +7252,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7290,7 +7301,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7339,7 +7350,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7388,7 +7399,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7437,7 +7448,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7486,12 +7497,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7540,7 +7551,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7589,12 +7600,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7643,7 +7654,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7692,7 +7703,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7741,7 +7752,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7790,13 +7801,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7845,7 +7856,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7894,7 +7905,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7943,7 +7954,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7992,7 +8003,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8041,12 +8052,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8096,7 +8107,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8145,7 +8156,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8195,7 +8206,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8244,7 +8255,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8294,7 +8305,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8310,13 +8321,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8365,7 +8376,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8399,7 +8410,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8433,7 +8444,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8482,7 +8493,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8563,18 +8574,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8590,7 +8601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8601,7 +8612,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8621,7 +8632,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8643,7 +8654,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8664,7 +8675,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8685,7 +8696,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8706,7 +8717,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8727,7 +8738,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8749,7 +8760,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8761,7 +8772,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8773,7 +8784,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8797,12 +8808,12 @@
         <v>1580935340.421</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8822,7 +8833,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8842,7 +8853,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8862,7 +8873,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8882,7 +8893,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8902,7 +8913,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8923,7 +8934,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8943,7 +8954,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8963,7 +8974,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8975,7 +8986,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8987,7 +8998,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9011,7 +9022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9028,7 +9039,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9047,7 +9058,7 @@
         <v>-249827926.10249996</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9062,7 +9073,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9081,7 +9092,7 @@
         <v>-249827926.10249996</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9097,7 +9108,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9114,7 +9125,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9134,7 +9145,7 @@
         <v>3958614459.3775001</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9145,7 +9156,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9158,7 +9169,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9177,7 +9188,7 @@
         <v>2377679118.9565001</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9193,7 +9204,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9209,7 +9220,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9225,7 +9236,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9244,7 +9255,7 @@
         <v>241356061.68599999</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9264,7 +9275,7 @@
         <v>1580935340.421</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9284,7 +9295,7 @@
         <v>1550741909.625</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9303,7 +9314,7 @@
         <v>30193430.795999996</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9314,7 +9325,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9328,7 +9339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9342,7 +9353,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9357,10 +9368,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9373,7 +9384,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9387,7 +9398,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9398,10 +9409,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9413,7 +9424,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9427,7 +9438,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9441,10 +9452,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9456,7 +9467,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9467,7 +9478,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9478,10 +9489,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9493,7 +9504,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9509,7 +9520,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9520,7 +9531,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9534,7 +9545,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9550,7 +9561,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9560,7 +9571,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9570,7 +9581,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9580,7 +9591,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9590,10 +9601,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9605,7 +9616,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9621,7 +9632,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9637,7 +9648,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9650,7 +9661,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9663,10 +9674,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9678,7 +9689,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9692,7 +9703,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9706,7 +9717,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9720,7 +9731,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9734,7 +9745,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9745,7 +9756,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9753,7 +9764,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9770,7 +9781,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9787,7 +9798,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9804,7 +9815,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9835,19 +9846,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9904,7 +9915,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9927,7 +9938,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9941,7 +9952,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9998,7 +10009,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10053,7 +10064,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10108,7 +10119,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10163,7 +10174,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10220,7 +10231,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10275,7 +10286,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10330,7 +10341,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10387,7 +10398,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10442,7 +10453,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10497,7 +10508,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10552,7 +10563,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10609,7 +10620,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10666,7 +10677,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10692,7 +10703,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10717,7 +10728,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10774,7 +10785,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10793,7 +10804,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10816,7 +10827,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10837,7 +10848,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10894,7 +10905,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10951,7 +10962,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11008,18 +11019,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11078,7 +11089,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11138,7 +11149,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11193,18 +11204,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11261,7 +11272,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11320,7 +11331,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11377,18 +11388,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11446,7 +11457,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11504,7 +11515,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11559,18 +11570,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11628,10 +11639,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11654,14 +11665,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11716,7 +11727,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11771,7 +11782,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11828,7 +11839,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11883,11 +11894,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11897,7 +11908,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11923,7 +11934,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11950,7 +11961,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -12005,11 +12016,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12019,7 +12030,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12074,7 +12085,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12129,7 +12140,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12184,7 +12195,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12239,7 +12250,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12295,7 +12306,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12350,11 +12361,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12364,7 +12375,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12389,7 +12400,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12414,7 +12425,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12439,7 +12450,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12466,10 +12477,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12492,7 +12503,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12513,7 +12524,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12570,7 +12581,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12627,7 +12638,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12684,7 +12695,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12741,7 +12752,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12798,7 +12809,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12857,7 +12868,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12914,7 +12925,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12971,7 +12982,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13028,7 +13039,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13085,7 +13096,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13143,7 +13154,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13200,7 +13211,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13226,7 +13237,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13250,7 +13261,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13307,18 +13318,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13374,7 +13385,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13430,7 +13441,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13485,27 +13496,27 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.515058389674247E-2</v>
+        <v>6.5351418002466105E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.515058389674247E-2</v>
+        <v>6.5351418002466105E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.515058389674247E-2</v>
+        <v>6.5351418002466105E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.1462814996926858E-2</v>
+        <v>6.1652281134401979E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13540,11 +13551,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13565,7 +13576,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13622,7 +13633,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13679,10 +13690,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13705,7 +13716,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13715,7 +13726,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13772,7 +13783,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13829,7 +13840,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13886,7 +13897,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13943,7 +13954,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -14000,11 +14011,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14027,7 +14038,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14084,7 +14095,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14141,7 +14152,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14168,18 +14179,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14231,7 +14242,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14283,11 +14294,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14341,7 +14352,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14396,7 +14407,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14450,7 +14461,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14506,7 +14517,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14563,7 +14574,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14582,7 +14593,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14605,7 +14616,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14626,7 +14637,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14684,795 +14695,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3566035566091046E-2</v>
+        <v>8.3823637401991447E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.2417444061344847E-2</v>
+        <v>9.2702331373494498E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10538915724800994</v>
+        <v>0.10571403134556855</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.9391808418167268E-2</v>
+        <v>8.9667368863352748E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.8390052339062285E-2</v>
+        <v>6.8600872475742494E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5783018246057234E-2</v>
+        <v>5.5954975762228805E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.4099576094102699E-2</v>
+        <v>4.4235518067265785E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.6297786453167042E-2</v>
+        <v>2.63788523793482E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0569098047495887E-2</v>
+        <v>2.0632504638271151E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0466510823227192E-2</v>
+        <v>2.0529601177182888E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.1073714052498551E-2</v>
+        <v>2.1138676179664084E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0439836392056883E-2</v>
+        <v>9.0718627503006494E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10748419382342322</v>
+        <v>0.10781552611017854</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8913811327979889E-2</v>
+        <v>8.9187898292616072E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8984877216693954E-2</v>
+        <v>6.9197530968903243E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4876321039842371E-2</v>
+        <v>5.5045483558460874E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4042959244739513E-2</v>
+        <v>4.41787266900069E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.606641420436482E-2</v>
+        <v>2.6146766899199484E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1959450113132481E-2</v>
+        <v>2.2027142622729069E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7032276341811238E-2</v>
+        <v>1.7084780276280447E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5205497101740666E-2</v>
+        <v>1.5252369780845909E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15494,16 +15505,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15515,7 +15526,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15528,7 +15539,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15549,7 +15560,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15560,7 +15571,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15578,7 +15589,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15594,7 +15605,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15610,7 +15621,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15626,7 +15637,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15640,7 +15651,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15654,7 +15665,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15668,10 +15679,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15681,13 +15692,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15697,7 +15708,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15707,7 +15718,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15721,10 +15732,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15742,7 +15753,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15764,7 +15775,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15786,7 +15797,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15818,7 +15829,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15850,7 +15861,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15882,7 +15893,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15904,7 +15915,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15926,7 +15937,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15948,7 +15959,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15970,7 +15981,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15992,7 +16003,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16014,7 +16025,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16036,7 +16047,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16068,7 +16079,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16100,7 +16111,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16132,7 +16143,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16154,7 +16165,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16176,7 +16187,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16198,7 +16209,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16220,7 +16231,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16242,7 +16253,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16264,7 +16275,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16286,7 +16297,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16308,7 +16319,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16330,7 +16341,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16352,7 +16363,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16374,7 +16385,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16406,7 +16417,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16438,7 +16449,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16470,7 +16481,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16502,7 +16513,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16524,7 +16535,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16535,11 +16546,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16549,7 +16560,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>14195313617.70599</v>
@@ -16576,7 +16587,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16598,7 +16609,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16619,7 +16630,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16650,7 +16661,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16681,7 +16692,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16712,7 +16723,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16743,7 +16754,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16760,7 +16771,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16780,7 +16791,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16803,7 +16814,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16829,7 +16840,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16856,7 +16867,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16883,7 +16894,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16910,7 +16921,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16937,7 +16948,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16963,7 +16974,7 @@
         <v>63.762195194106063</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16989,7 +17000,7 @@
         <v>81.499306306355422</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -17006,7 +17017,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17028,7 +17039,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17051,7 +17062,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17074,7 +17085,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17097,7 +17108,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17119,14 +17130,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17134,26 +17145,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17167,7 +17178,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17181,7 +17192,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17195,7 +17206,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17209,7 +17220,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17254,16 +17265,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17275,7 +17286,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17288,7 +17299,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17309,7 +17320,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17320,7 +17331,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17336,7 +17347,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17350,10 +17361,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17363,13 +17374,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17379,7 +17390,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17389,7 +17400,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17403,10 +17414,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17424,7 +17435,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17446,7 +17457,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17468,7 +17479,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17490,7 +17501,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17512,7 +17523,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17534,7 +17545,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17556,7 +17567,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17578,7 +17589,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17600,7 +17611,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17622,7 +17633,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17644,7 +17655,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17666,7 +17677,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17688,7 +17699,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17710,7 +17721,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17732,7 +17743,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17754,7 +17765,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17776,7 +17787,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17798,7 +17809,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17820,7 +17831,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17842,7 +17853,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17864,7 +17875,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17886,7 +17897,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17908,7 +17919,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17930,7 +17941,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17952,7 +17963,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17974,7 +17985,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17996,7 +18007,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18018,7 +18029,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18040,7 +18051,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18062,7 +18073,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18084,7 +18095,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18106,7 +18117,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18117,11 +18128,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18131,7 +18142,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>11067091606.367868</v>
@@ -18158,7 +18169,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18180,7 +18191,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18201,7 +18212,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18222,7 +18233,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18243,7 +18254,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18264,7 +18275,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18285,14 +18296,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18302,7 +18313,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18325,7 +18336,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18351,7 +18362,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18378,7 +18389,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18405,7 +18416,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18432,7 +18443,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18459,7 +18470,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18485,7 +18496,7 @@
         <v>48.966288554735989</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18511,7 +18522,7 @@
         <v>62.794671554794832</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18528,7 +18539,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18550,7 +18561,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18573,7 +18584,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18596,7 +18607,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18619,7 +18630,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18641,14 +18652,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18656,23 +18667,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18702,17 +18713,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18725,7 +18736,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18734,10 +18745,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.27</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-16.22</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18757,7 +18768,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18766,7 +18777,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18786,7 +18797,7 @@
         <v>26.644938697660866</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18811,7 +18822,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18833,7 +18844,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18855,7 +18866,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18866,7 +18877,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18880,7 +18891,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18899,7 +18910,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18917,7 +18928,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18928,7 +18939,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18937,7 +18948,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18945,7 +18956,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18957,24 +18968,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.27</v>
+        <v>16.22</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18983,7 +18994,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18998,7 +19009,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -19007,7 +19018,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19019,7 +19030,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19030,7 +19041,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19045,7 +19056,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19056,7 +19067,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19065,7 +19076,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19077,7 +19088,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19088,7 +19099,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19103,7 +19114,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19114,7 +19125,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19123,7 +19134,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19135,7 +19146,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19146,7 +19157,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19161,7 +19172,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19173,7 +19184,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19186,7 +19197,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19195,12 +19206,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19210,12 +19221,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19224,7 +19235,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19236,7 +19247,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19247,7 +19258,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19262,7 +19273,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19273,7 +19284,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19282,7 +19293,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19294,7 +19305,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19305,7 +19316,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19320,7 +19331,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19331,7 +19342,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19351,7 +19362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19360,7 +19371,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19368,7 +19379,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19381,7 +19392,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19393,7 +19404,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19409,7 +19420,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19417,7 +19428,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19427,7 +19438,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19439,7 +19450,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19449,7 +19460,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19465,7 +19476,7 @@
         <v>3.7330744802016626E-2</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19474,12 +19485,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19489,7 +19500,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19502,33 +19513,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.8293222503295408</v>
+        <v>1.829322250329541</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19538,7 +19549,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19558,45 +19569,45 @@
         <v>0.51008644741782672</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.27</v>
+        <v>16.22</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21959401557257197</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>0.22091218945949698</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19605,7 +19616,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19617,7 +19628,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19627,7 +19638,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19647,14 +19658,14 @@
         <v>0.31299240539227124</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19665,7 +19676,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19677,7 +19688,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19689,7 +19700,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19708,15 +19719,15 @@
         <v>4.9636161355830488E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19725,7 +19736,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19735,7 +19746,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19745,7 +19756,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19764,16 +19775,16 @@
         <v>0.11580559118887601</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19781,7 +19792,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19789,7 +19800,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D537A1C1-1570-B04D-ADE0-942D305157E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382D2188-FDE5-4CC6-A7D8-6107EEB146CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2513,7 +2502,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3905,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3943,7 +3932,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4232,7 +4221,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4241,7 +4230,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4272,7 +4261,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4281,7 +4270,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +4287,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4308,7 +4297,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4318,17 +4307,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4340,17 +4329,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>16.22</v>
+        <v>16.079999999999998</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4360,13 +4349,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9350.1325400000005</v>
+        <v>9269.4285599999985</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4388,7 +4377,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4398,27 +4387,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4433,7 +4422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4446,7 +4435,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4454,7 +4443,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4462,7 +4451,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4478,7 +4467,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4492,14 +4481,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22091218945949698</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.22463310478807719</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4518,7 +4507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4537,7 +4526,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4556,7 +4545,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4575,7 +4564,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4594,11 +4583,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4608,25 +4597,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4635,16 +4624,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4657,20 +4646,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4683,7 +4672,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4696,16 +4685,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4718,16 +4707,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4742,7 +4731,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4757,7 +4746,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4770,12 +4759,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4788,16 +4777,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4810,8 +4799,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,7 +4808,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4832,25 +4821,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4863,7 +4852,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4876,23 +4865,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.3823637401991447E-2</v>
+        <v>8.4553445190317253E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.5351418002466105E-2</v>
+        <v>6.5920398009950254E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4902,7 +4891,7 @@
         <v>0.7796299472076299</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4913,7 +4902,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4926,7 +4915,7 @@
         <v>0.25256959684173202</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4940,7 +4929,7 @@
         <v>0.18394654535282634</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4954,7 +4943,7 @@
         <v>0.70676723862204571</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4968,7 +4957,7 @@
         <v>1.9427325871638936</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4978,34 +4967,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5014,7 +5003,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5023,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5032,34 +5021,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5067,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5080,7 +5069,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5090,38 +5079,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5134,7 +5123,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5147,7 +5136,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5156,7 +5145,7 @@
         <v>6.0553888114002474E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5165,12 +5154,12 @@
         <v>0.26060254325045429</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5183,7 +5172,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5196,7 +5185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5209,12 +5198,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5227,7 +5216,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5240,16 +5229,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5262,7 +5251,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5275,7 +5264,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5285,16 +5274,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5311,7 +5300,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5333,7 +5322,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5355,7 +5344,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5377,7 +5366,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5399,7 +5388,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5421,7 +5410,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5434,16 +5423,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5453,30 +5442,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5485,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5494,7 +5483,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5507,7 +5496,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5520,7 +5509,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5529,7 +5518,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5539,7 +5528,7 @@
         <v>1.829322250329541</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5549,7 +5538,7 @@
         <v>10.705085959638616</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5562,7 +5551,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5584,12 +5573,12 @@
         <v>0.51008644741782672</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5598,7 +5587,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5608,7 +5597,7 @@
         <v>2.279132885208865</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5618,7 +5607,7 @@
         <v>15.297914307657322</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5631,7 +5620,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5644,7 +5633,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5653,12 +5642,12 @@
         <v>0.31299240539227124</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5667,7 +5656,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5677,7 +5666,7 @@
         <v>2.8333926664293383</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5687,7 +5676,7 @@
         <v>21.481607885755405</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5700,7 +5689,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5713,7 +5702,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5722,12 +5711,12 @@
         <v>4.9636161355830488E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5736,7 +5725,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5746,7 +5735,7 @@
         <v>2.6975834619563113</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5756,7 +5745,7 @@
         <v>19.920294213679817</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5769,7 +5758,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5782,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5791,7 +5780,7 @@
         <v>0.11580559118887601</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5801,21 +5790,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5824,91 +5813,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5925,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5955,15 +5944,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6012,7 +6001,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6028,7 +6017,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6036,7 +6025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6072,7 +6061,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6108,7 +6097,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6144,7 +6133,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6180,7 +6169,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6216,7 +6205,7 @@
       </c>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6232,7 +6221,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6248,7 +6237,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6264,7 +6253,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6298,7 +6287,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6332,7 +6321,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6368,7 +6357,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6404,7 +6393,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6440,13 +6429,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6480,7 +6469,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6496,7 +6485,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6512,7 +6501,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6548,7 +6537,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6584,7 +6573,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6620,7 +6609,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6646,7 +6635,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6654,7 +6643,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6691,7 +6680,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6728,7 +6717,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6765,7 +6754,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6802,7 +6791,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6839,7 +6828,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6855,12 +6844,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6909,7 +6898,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6958,7 +6947,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -7007,7 +6996,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7056,7 +7045,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7105,7 +7094,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7154,7 +7143,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7203,7 +7192,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7252,7 +7241,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7301,7 +7290,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7350,7 +7339,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7399,7 +7388,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7448,7 +7437,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7497,12 +7486,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7551,7 +7540,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7600,12 +7589,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7654,7 +7643,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7703,7 +7692,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7752,7 +7741,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7801,13 +7790,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7856,7 +7845,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7905,7 +7894,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7954,7 +7943,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -8003,7 +7992,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8052,12 +8041,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8107,7 +8096,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8156,7 +8145,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8206,7 +8195,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8255,7 +8244,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8305,7 +8294,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8321,13 +8310,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8376,7 +8365,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8410,7 +8399,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8444,7 +8433,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8493,7 +8482,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8574,7 +8563,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8585,7 +8574,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8601,7 +8590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8612,7 +8601,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8632,7 +8621,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8654,7 +8643,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8675,7 +8664,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8696,7 +8685,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8717,7 +8706,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8738,7 +8727,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8760,7 +8749,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8772,7 +8761,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8784,7 +8773,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8808,12 +8797,12 @@
         <v>1580935340.421</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8833,7 +8822,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8853,7 +8842,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8873,7 +8862,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8893,7 +8882,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8913,7 +8902,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8934,7 +8923,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8954,7 +8943,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8974,7 +8963,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8986,7 +8975,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8998,7 +8987,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9022,7 +9011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9039,7 +9028,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9058,7 +9047,7 @@
         <v>-249827926.10249996</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9073,7 +9062,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9092,7 +9081,7 @@
         <v>-249827926.10249996</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9108,7 +9097,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9125,7 +9114,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9145,7 +9134,7 @@
         <v>3958614459.3775001</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9156,7 +9145,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9169,7 +9158,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9188,7 +9177,7 @@
         <v>2377679118.9565001</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9204,7 +9193,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9220,7 +9209,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9236,7 +9225,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9255,7 +9244,7 @@
         <v>241356061.68599999</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9275,7 +9264,7 @@
         <v>1580935340.421</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9295,7 +9284,7 @@
         <v>1550741909.625</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9314,7 +9303,7 @@
         <v>30193430.795999996</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9325,7 +9314,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9339,7 +9328,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9353,7 +9342,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9368,10 +9357,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9384,7 +9373,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9398,7 +9387,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9409,10 +9398,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9424,7 +9413,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9438,7 +9427,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9452,10 +9441,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9467,7 +9456,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9478,7 +9467,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9489,10 +9478,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9504,7 +9493,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9520,7 +9509,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9531,7 +9520,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9545,7 +9534,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9561,7 +9550,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9571,7 +9560,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9581,7 +9570,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9591,7 +9580,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9601,10 +9590,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9616,7 +9605,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9632,7 +9621,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9648,7 +9637,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9661,7 +9650,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9674,10 +9663,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9689,7 +9678,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9703,7 +9692,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9717,7 +9706,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9731,7 +9720,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9745,7 +9734,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9756,7 +9745,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9764,7 +9753,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9781,7 +9770,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9798,7 +9787,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9815,7 +9804,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9846,19 +9835,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9915,7 +9904,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9938,7 +9927,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9952,7 +9941,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -10009,7 +9998,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10064,7 +10053,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10119,7 +10108,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10174,7 +10163,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10231,7 +10220,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10286,7 +10275,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10341,7 +10330,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10398,7 +10387,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10453,7 +10442,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10508,7 +10497,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10563,7 +10552,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10620,7 +10609,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10677,7 +10666,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10703,7 +10692,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10728,7 +10717,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10785,7 +10774,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10804,7 +10793,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10827,7 +10816,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10848,7 +10837,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10905,7 +10894,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10962,7 +10951,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11019,18 +11008,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11089,7 +11078,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11149,7 +11138,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11204,18 +11193,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11272,7 +11261,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11331,7 +11320,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11388,18 +11377,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11457,7 +11446,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11515,7 +11504,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11570,18 +11559,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11639,10 +11628,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11665,14 +11654,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11727,7 +11716,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11782,7 +11771,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11839,7 +11828,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11894,11 +11883,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11908,7 +11897,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11934,7 +11923,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11961,7 +11950,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -12016,11 +12005,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12030,7 +12019,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12085,7 +12074,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12140,7 +12129,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12195,7 +12184,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12250,7 +12239,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12306,7 +12295,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12361,11 +12350,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12375,7 +12364,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12400,7 +12389,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12425,7 +12414,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12450,7 +12439,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12477,10 +12466,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12503,7 +12492,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12524,7 +12513,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12581,7 +12570,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12638,7 +12627,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12695,7 +12684,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12752,7 +12741,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12809,7 +12798,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12868,7 +12857,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12925,7 +12914,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12982,7 +12971,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13039,7 +13028,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13096,7 +13085,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13154,7 +13143,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13211,7 +13200,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13237,7 +13226,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13261,7 +13250,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13318,18 +13307,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13385,7 +13374,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13441,7 +13430,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13496,27 +13485,27 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.5351418002466105E-2</v>
+        <v>6.5920398009950254E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5351418002466105E-2</v>
+        <v>6.5920398009950254E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5351418002466105E-2</v>
+        <v>6.5920398009950254E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.1652281134401979E-2</v>
+        <v>6.2189054726368168E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13551,11 +13540,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13576,7 +13565,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13633,7 +13622,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13690,10 +13679,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13716,7 +13705,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13726,7 +13715,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13783,7 +13772,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13840,7 +13829,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13897,7 +13886,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13954,7 +13943,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -14011,11 +14000,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14038,7 +14027,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14095,7 +14084,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14152,7 +14141,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14179,18 +14168,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14242,7 +14231,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14294,11 +14283,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14352,7 +14341,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14407,7 +14396,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14461,7 +14450,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14517,7 +14506,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14574,7 +14563,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14593,7 +14582,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14616,7 +14605,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14637,7 +14626,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14695,795 +14684,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3823637401991447E-2</v>
+        <v>8.4553445190317253E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.2702331373494498E-2</v>
+        <v>9.3509441223761244E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10571403134556855</v>
+        <v>0.10663442714086578</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.9667368863352748E-2</v>
+        <v>9.0448054910670497E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.8600872475742494E-2</v>
+        <v>6.9198143753516378E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5954975762228805E-2</v>
+        <v>5.6442145949213388E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.4235518067265785E-2</v>
+        <v>4.4620653174816609E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.63788523793482E-2</v>
+        <v>2.6608519004541531E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0632504638271151E-2</v>
+        <v>2.081214087268396E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0529601177182888E-2</v>
+        <v>2.0708341485939457E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.1138676179664084E-2</v>
+        <v>2.1322719380233297E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0718627503006494E-2</v>
+        <v>9.150846629967449E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10781552611017854</v>
+        <v>0.1087542185016851</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9187898292616072E-2</v>
+        <v>8.9964409844914994E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9197530968903243E-2</v>
+        <v>6.9799997034552919E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5045483558460874E-2</v>
+        <v>5.5524735280984797E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.41787266900069E-2</v>
+        <v>4.4563367345268161E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6146766899199484E-2</v>
+        <v>2.6374412879665157E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2027142622729069E-2</v>
+        <v>2.2218921227653329E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7084780276280447E-2</v>
+        <v>1.7233528363262991E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5252369780845909E-2</v>
+        <v>1.5385164045107008E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15505,16 +15494,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15526,7 +15515,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15539,7 +15528,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15560,7 +15549,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15571,7 +15560,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15589,7 +15578,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15605,7 +15594,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15621,7 +15610,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15637,7 +15626,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15651,7 +15640,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15665,7 +15654,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15679,10 +15668,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15692,13 +15681,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15708,7 +15697,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15718,7 +15707,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15732,10 +15721,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15753,7 +15742,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15775,7 +15764,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15797,7 +15786,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15829,7 +15818,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15861,7 +15850,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15893,7 +15882,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15915,7 +15904,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15937,7 +15926,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15959,7 +15948,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15981,7 +15970,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -16003,7 +15992,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16025,7 +16014,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16047,7 +16036,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16079,7 +16068,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16111,7 +16100,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16143,7 +16132,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16165,7 +16154,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16187,7 +16176,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16209,7 +16198,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16231,7 +16220,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16253,7 +16242,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16275,7 +16264,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16297,7 +16286,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16319,7 +16308,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16341,7 +16330,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16363,7 +16352,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16385,7 +16374,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16417,7 +16406,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16449,7 +16438,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16481,7 +16470,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16513,7 +16502,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16535,7 +16524,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16546,11 +16535,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16560,7 +16549,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>14195313617.70599</v>
@@ -16587,7 +16576,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16609,7 +16598,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16630,7 +16619,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16661,7 +16650,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16692,7 +16681,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16723,7 +16712,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16754,7 +16743,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16771,7 +16760,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16791,7 +16780,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16814,7 +16803,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16840,7 +16829,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16867,7 +16856,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16894,7 +16883,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16921,7 +16910,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16948,7 +16937,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16974,7 +16963,7 @@
         <v>63.762195194106063</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -17000,7 +16989,7 @@
         <v>81.499306306355422</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -17017,7 +17006,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17039,7 +17028,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17062,7 +17051,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17085,7 +17074,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17108,7 +17097,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17130,14 +17119,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17145,26 +17134,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17178,7 +17167,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17192,7 +17181,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17206,7 +17195,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17220,7 +17209,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17265,16 +17254,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17286,7 +17275,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17299,7 +17288,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17320,7 +17309,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17331,7 +17320,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17347,7 +17336,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17361,10 +17350,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17374,13 +17363,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17390,7 +17379,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17400,7 +17389,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17414,10 +17403,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17435,7 +17424,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17457,7 +17446,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17479,7 +17468,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17501,7 +17490,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17523,7 +17512,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17545,7 +17534,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17567,7 +17556,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17589,7 +17578,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17611,7 +17600,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17633,7 +17622,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17655,7 +17644,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17677,7 +17666,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17699,7 +17688,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17721,7 +17710,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17743,7 +17732,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17765,7 +17754,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17787,7 +17776,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17809,7 +17798,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17831,7 +17820,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17853,7 +17842,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17875,7 +17864,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17897,7 +17886,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17919,7 +17908,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17941,7 +17930,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17963,7 +17952,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17985,7 +17974,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -18007,7 +17996,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18029,7 +18018,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18051,7 +18040,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18073,7 +18062,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18095,7 +18084,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18117,7 +18106,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18128,11 +18117,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18142,7 +18131,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>11067091606.367868</v>
@@ -18169,7 +18158,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18191,7 +18180,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18212,7 +18201,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18233,7 +18222,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18254,7 +18243,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18275,7 +18264,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18296,14 +18285,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18313,7 +18302,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18336,7 +18325,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18362,7 +18351,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18389,7 +18378,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18416,7 +18405,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18443,7 +18432,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18470,7 +18459,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18496,7 +18485,7 @@
         <v>48.966288554735989</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18522,7 +18511,7 @@
         <v>62.794671554794832</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18539,7 +18528,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18561,7 +18550,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18584,7 +18573,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18607,7 +18596,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18630,7 +18619,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18652,14 +18641,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18667,23 +18656,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18713,7 +18702,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18723,7 +18712,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18736,7 +18725,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18745,10 +18734,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.22</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-16.079999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18768,7 +18757,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18777,7 +18766,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18797,7 +18786,7 @@
         <v>26.644938697660866</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18822,7 +18811,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18844,7 +18833,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18866,7 +18855,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18877,7 +18866,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18891,7 +18880,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18910,7 +18899,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18928,7 +18917,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18939,7 +18928,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18948,7 +18937,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18956,7 +18945,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18968,24 +18957,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.22</v>
+        <v>16.079999999999998</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18994,7 +18983,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -19009,7 +18998,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -19018,7 +19007,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19030,7 +19019,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19041,7 +19030,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19056,7 +19045,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19067,7 +19056,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19076,7 +19065,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19088,7 +19077,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19099,7 +19088,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19114,7 +19103,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19125,7 +19114,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19134,7 +19123,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19146,7 +19135,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19157,7 +19146,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19172,7 +19161,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19184,7 +19173,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19197,7 +19186,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19206,12 +19195,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19221,12 +19210,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19235,7 +19224,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19247,7 +19236,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19258,7 +19247,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19273,7 +19262,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19284,7 +19273,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19293,7 +19282,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19305,7 +19294,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19316,7 +19305,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19331,7 +19320,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19342,7 +19331,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19362,7 +19351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19371,7 +19360,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19379,7 +19368,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19392,7 +19381,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19404,7 +19393,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19420,7 +19409,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19428,7 +19417,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19438,7 +19427,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19450,7 +19439,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19460,7 +19449,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19476,7 +19465,7 @@
         <v>3.7330744802016626E-2</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19485,12 +19474,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19500,7 +19489,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19513,12 +19502,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19527,7 +19516,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19539,7 +19528,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19549,7 +19538,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19569,45 +19558,45 @@
         <v>0.51008644741782672</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.22</v>
+        <v>16.079999999999998</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22091218945949698</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.22463310478807719</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19616,7 +19605,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19628,7 +19617,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19638,7 +19627,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19658,14 +19647,14 @@
         <v>0.31299240539227124</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19676,7 +19665,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19688,7 +19677,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19700,7 +19689,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19719,15 +19708,15 @@
         <v>4.9636161355830488E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19736,7 +19725,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19746,7 +19735,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19756,7 +19745,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19775,16 +19764,16 @@
         <v>0.11580559118887601</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19792,7 +19781,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19800,7 +19789,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382D2188-FDE5-4CC6-A7D8-6107EEB146CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA138850-AA6B-4A51-A5FD-825C03E0BF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA138850-AA6B-4A51-A5FD-825C03E0BF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DC9B4A-F0FC-41E4-B5E1-A8E6FCBF2DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>16.079999999999998</v>
+        <v>15.93</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9269.4285599999985</v>
+        <v>9182.9600100000007</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22463310478807719</v>
+        <v>0.22866974293726483</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.4553445190317253E-2</v>
+        <v>8.5349616990602714E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.5920398009950254E-2</v>
+        <v>6.6541117388575016E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13492,20 +13492,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.5920398009950254E-2</v>
+        <v>6.6541117388575016E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5920398009950254E-2</v>
+        <v>6.6541117388575016E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5920398009950254E-2</v>
+        <v>6.6541117388575016E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.2189054726368168E-2</v>
+        <v>6.2774639045825489E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14691,50 +14691,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.4553445190317253E-2</v>
+        <v>8.5349616990602714E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.3509441223761244E-2</v>
+        <v>9.438994443679101E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10663442714086578</v>
+        <v>0.10763851779190971</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.0448054910670497E-2</v>
+        <v>9.1299731510582641E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.9198143753516378E-2</v>
+        <v>6.9849727028031591E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.6442145949213388E-2</v>
+        <v>5.6973616250053434E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.4620653174816609E-2</v>
+        <v>4.5040809984372314E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.6608519004541531E-2</v>
+        <v>2.6859070030949641E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.081214087268396E-2</v>
+        <v>2.1008112067341999E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0708341485939457E-2</v>
+        <v>2.0903335285242085E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.1322719380233297E-2</v>
+        <v>2.1523498282118733E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14748,43 +14748,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.150846629967449E-2</v>
+        <v>9.2370127940914343E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1087542185016851</v>
+        <v>0.10977826952335819</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9964409844914994E-2</v>
+        <v>9.0811532348162763E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9799997034552919E-2</v>
+        <v>7.0457247477439464E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5524735280984797E-2</v>
+        <v>5.6047567063291608E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4563367345268161E-2</v>
+        <v>4.498298474023301E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6374412879665157E-2</v>
+        <v>2.6622759516950135E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2218921227653329E-2</v>
+        <v>2.242813894166136E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7233528363262991E-2</v>
+        <v>1.7395802641636465E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5385164045107008E-2</v>
+        <v>1.5530033763045866E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.079999999999998</v>
+        <v>-15.93</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.079999999999998</v>
+        <v>15.93</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.079999999999998</v>
+        <v>15.93</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22463310478807719</v>
+        <v>0.22866974293726483</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DC9B4A-F0FC-41E4-B5E1-A8E6FCBF2DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57433BE4-29C3-4F7F-8233-7DC7B5BA44B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57433BE4-29C3-4F7F-8233-7DC7B5BA44B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68518E2D-BF5D-4585-B726-3F47E6F73A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68518E2D-BF5D-4585-B726-3F47E6F73A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EE5038-5EF2-4323-8AFF-79910A3C2CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>15.93</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9182.9600100000007</v>
+        <v>9332.8388300000006</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22866974293726483</v>
+        <v>0.22170578839876431</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.5349616990602714E-2</v>
+        <v>8.3978962239672716E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.6541117388575016E-2</v>
+        <v>6.5472513897467569E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13492,20 +13492,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.6541117388575016E-2</v>
+        <v>6.5472513897467569E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.6541117388575016E-2</v>
+        <v>6.5472513897467569E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6541117388575016E-2</v>
+        <v>6.5472513897467569E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.2774639045825489E-2</v>
+        <v>6.1766522544780725E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14691,50 +14691,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.5349616990602714E-2</v>
+        <v>8.3978962239672716E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.438994443679101E-2</v>
+        <v>9.2874108392716523E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10763851779190971</v>
+        <v>0.1059099189885807</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.1299731510582641E-2</v>
+        <v>8.9833522110165612E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.9849727028031591E-2</v>
+        <v>6.8727989595833427E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.6973616250053434E-2</v>
+        <v>5.6058660090386112E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.5040809984372314E-2</v>
+        <v>4.4317486290985232E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.6859070030949641E-2</v>
+        <v>2.6427732278754029E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.1008112067341999E-2</v>
+        <v>2.0670736580158E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0903335285242085E-2</v>
+        <v>2.0567642439401259E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.1523498282118733E-2</v>
+        <v>2.117784605522862E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14748,43 +14748,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2370127940914343E-2</v>
+        <v>9.0886728727533381E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10977826952335819</v>
+        <v>0.10801530781390339</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0811532348162763E-2</v>
+        <v>8.9353163082534451E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0457247477439464E-2</v>
+        <v>6.9325753694602268E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6047567063291608E-2</v>
+        <v>5.5147482601496933E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.498298474023301E-2</v>
+        <v>4.4260589679549843E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6622759516950135E-2</v>
+        <v>2.6195216745214061E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.242813894166136E-2</v>
+        <v>2.2067958822771183E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7395802641636465E-2</v>
+        <v>1.7116438300263673E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5530033763045866E-2</v>
+        <v>1.5280632356103807E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-15.93</v>
+        <v>-16.190000000000001</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>15.93</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>15.93</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22866974293726483</v>
+        <v>0.22170578839876431</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EE5038-5EF2-4323-8AFF-79910A3C2CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5785D2B1-4989-4146-A832-33AA09C82D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>16.190000000000001</v>
+        <v>16.12</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9332.8388300000006</v>
+        <v>9292.4868399999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22170578839876431</v>
+        <v>0.22356543697419196</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.3978962239672716E-2</v>
+        <v>8.434363515262415E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.5472513897467569E-2</v>
+        <v>6.5756823821339946E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13492,20 +13492,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.5472513897467569E-2</v>
+        <v>6.5756823821339946E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5472513897467569E-2</v>
+        <v>6.5756823821339946E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5472513897467569E-2</v>
+        <v>6.5756823821339946E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.1766522544780725E-2</v>
+        <v>6.2034739454094288E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14691,50 +14691,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3978962239672716E-2</v>
+        <v>8.434363515262415E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.2874108392716523E-2</v>
+        <v>9.3277407870848678E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1059099189885807</v>
+        <v>0.10636982558468495</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.9833522110165612E-2</v>
+        <v>9.0223618049849963E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.8727989595833427E-2</v>
+        <v>6.9026436200778113E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.6058660090386112E-2</v>
+        <v>5.6302090996485803E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.4317486290985232E-2</v>
+        <v>4.4509931951057749E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.6427732278754029E-2</v>
+        <v>2.6542492902793285E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0670736580158E-2</v>
+        <v>2.0760497843223202E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0567642439401259E-2</v>
+        <v>2.0656956023195186E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.117784605522862E-2</v>
+        <v>2.1269809406585072E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14748,43 +14748,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0886728727533381E-2</v>
+        <v>9.1281398145084708E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10801530781390339</v>
+        <v>0.10848435691731365</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9353163082534451E-2</v>
+        <v>8.974117309592014E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9325753694602268E-2</v>
+        <v>6.9626796049355497E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5147482601496933E-2</v>
+        <v>5.5386956781528246E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4260589679549843E-2</v>
+        <v>4.445278826996972E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6195216745214061E-2</v>
+        <v>2.6308967686415361E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2067958822771183E-2</v>
+        <v>2.2163787428080985E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7116438300263673E-2</v>
+        <v>1.71907652655874E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5280632356103807E-2</v>
+        <v>1.5346987459387137E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.190000000000001</v>
+        <v>-16.12</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.190000000000001</v>
+        <v>16.12</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.190000000000001</v>
+        <v>16.12</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22170578839876431</v>
+        <v>0.22356543697419196</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5785D2B1-4989-4146-A832-33AA09C82D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FDA320-AC28-4708-89F9-EC6D940444B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>16.12</v>
+        <v>16.23</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9292.4868399999996</v>
+        <v>9355.8971099999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22356543697419196</v>
+        <v>0.22064810646638167</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.434363515262415E-2</v>
+        <v>8.3771990059168286E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.5756823821339946E-2</v>
+        <v>6.5311152187307459E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13492,20 +13492,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.5756823821339946E-2</v>
+        <v>6.5311152187307459E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5756823821339946E-2</v>
+        <v>6.5311152187307459E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5756823821339946E-2</v>
+        <v>6.5311152187307459E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.2034739454094288E-2</v>
+        <v>6.1614294516327786E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14691,50 +14691,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.434363515262415E-2</v>
+        <v>8.3771990059168286E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.3277407870848678E-2</v>
+        <v>9.2645213486018521E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10636982558468495</v>
+        <v>0.10564889639095019</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.0223618049849963E-2</v>
+        <v>8.9612120946616233E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.9026436200778113E-2</v>
+        <v>6.8558604532134526E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.6302090996485803E-2</v>
+        <v>5.5920499498666121E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.4509931951057749E-2</v>
+        <v>4.4208262664882987E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.6542492902793285E-2</v>
+        <v>2.6362599235553157E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.0760497843223202E-2</v>
+        <v>2.061979206609723E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0656956023195186E-2</v>
+        <v>2.0516952008250548E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.1269809406585072E-2</v>
+        <v>2.1125651733465891E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14748,43 +14748,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1281398145084708E-2</v>
+        <v>9.0662731860675624E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10848435691731365</v>
+        <v>0.10774909633438669</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.974117309592014E-2</v>
+        <v>8.9132945798289134E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9626796049355497E-2</v>
+        <v>6.9154895398374036E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5386956781528246E-2</v>
+        <v>5.5011567672103225E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.445278826996972E-2</v>
+        <v>4.4151506279230555E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6308967686415361E-2</v>
+        <v>2.6130656753235715E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2163787428080985E-2</v>
+        <v>2.201357075419997E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.71907652655874E-2</v>
+        <v>1.7074253609443552E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5346987459387137E-2</v>
+        <v>1.5242972140808419E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.12</v>
+        <v>-16.23</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.12</v>
+        <v>16.23</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.12</v>
+        <v>16.23</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22356543697419196</v>
+        <v>0.22064810646638167</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FDA320-AC28-4708-89F9-EC6D940444B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D4785D-70A4-44EA-B46F-8C90B633AB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>16.23</v>
+        <v>16.25</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9355.8971099999999</v>
+        <v>9367.4262500000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22064810646638167</v>
+        <v>0.22012061346574296</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.3771990059168286E-2</v>
+        <v>8.3668886071403145E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>6.5311152187307459E-2</v>
+        <v>6.5230769230769231E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13492,20 +13492,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>6.5311152187307459E-2</v>
+        <v>6.5230769230769231E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5311152187307459E-2</v>
+        <v>6.5230769230769231E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5311152187307459E-2</v>
+        <v>6.5230769230769231E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.1614294516327786E-2</v>
+        <v>6.1538461538461542E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14691,50 +14691,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3771990059168286E-2</v>
+        <v>8.3668886071403145E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>9.2645213486018521E-2</v>
+        <v>9.2531188607881898E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10564889639095019</v>
+        <v>0.10551886698000748</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.9612120946616233E-2</v>
+        <v>8.9501829105451167E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.8558604532134526E-2</v>
+        <v>6.8474224711171899E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5920499498666121E-2</v>
+        <v>5.5851674268513916E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>4.4208262664882987E-2</v>
+        <v>4.4153852495449286E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.6362599235553157E-2</v>
+        <v>2.6330152959570939E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.061979206609723E-2</v>
+        <v>2.0594413860477417E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>2.0516952008250548E-2</v>
+        <v>2.0491700375009626E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>2.1125651733465891E-2</v>
+        <v>2.1099650931332394E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14748,43 +14748,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0662731860675624E-2</v>
+        <v>9.0551146959924028E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10774909633438669</v>
+        <v>0.10761648206197513</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9132945798289134E-2</v>
+        <v>8.9023243711152777E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9154895398374036E-2</v>
+        <v>6.906978168096066E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5011567672103225E-2</v>
+        <v>5.494386112727602E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4151506279230555E-2</v>
+        <v>4.4097165963809963E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6130656753235715E-2</v>
+        <v>2.6098495944924038E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.201357075419997E-2</v>
+        <v>2.1986477128656336E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7074253609443552E-2</v>
+        <v>1.7053239143462698E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5242972140808419E-2</v>
+        <v>1.5224211559712039E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.23</v>
+        <v>-16.25</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.23</v>
+        <v>16.25</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19572,7 +19572,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.23</v>
+        <v>16.25</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19585,7 +19585,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22064810646638167</v>
+        <v>0.22012061346574296</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D4785D-70A4-44EA-B46F-8C90B633AB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2195162A-1400-4439-92BC-89DA6CA514D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2445,6 +2434,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
@@ -2470,9 +2471,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3149,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3894,6 +3892,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4223,10 +4225,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4238,18 +4240,18 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4263,7 +4265,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4272,10 +4274,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4289,7 +4291,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4299,7 +4301,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4312,20 +4314,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4341,17 +4343,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4365,7 +4367,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4391,35 +4393,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4427,7 +4429,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4437,26 +4439,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4477,11 +4479,11 @@
         <v>25.584938697660867</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22012061346574296</v>
+        <v>0.21441960331275056</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4490,7 +4492,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4501,7 +4503,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4509,37 +4511,37 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>12.534408209968158</v>
+        <v>12.351475984935202</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>17.577047192866189</v>
+        <v>17.349133904345301</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F30" s="312">
         <v>0.187</v>
@@ -4547,18 +4549,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>24.315000552184742</v>
+        <v>24.031661285541809</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F31" s="312">
         <v>0.06</v>
@@ -4566,18 +4568,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>22.61787767563613</v>
+        <v>22.348119329440497</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4589,7 +4591,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4597,45 +4599,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4650,18 +4652,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4674,7 +4676,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4686,17 +4688,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4708,17 +4710,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4733,7 +4735,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4748,7 +4750,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4761,12 +4763,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4778,17 +4780,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4800,17 +4802,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4821,27 +4823,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4854,7 +4856,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4867,24 +4869,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>8.3668886071403145E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
-        <v>6.5230769230769231E-2</v>
+        <f>Normalized_FCF!C94</f>
+        <v>5.8707692307692315E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4893,73 +4895,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>450</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>0.23409392300550072</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>0.25256959684173202</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>0.173581864935303</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>0.18394654535282634</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.69418106703013427</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.70676723862204571</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.9427325871638936</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.9427325871638936</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4970,33 +4972,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5005,7 +5007,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5014,7 +5016,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5026,31 +5028,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5058,7 +5060,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5071,7 +5073,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5083,36 +5085,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5125,7 +5127,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5138,7 +5140,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5147,7 +5149,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5156,12 +5158,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5174,7 +5176,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5187,7 +5189,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5200,12 +5202,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5218,7 +5220,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5229,18 +5231,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+    <row r="116" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5253,7 +5255,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5266,7 +5268,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5274,30 +5276,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+    <row r="123" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5412,7 +5414,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5423,18 +5425,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+    <row r="134" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5443,31 +5445,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5476,20 +5478,20 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.06</v>
+        <v>0.95400000000000007</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5498,7 +5500,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5511,11 +5513,11 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5525,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.829322250329541</v>
+        <v>1.6463900252965866</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5540,11 +5542,11 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>12.534408209968158</v>
+        <v>12.351475984935202</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5553,7 +5555,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5566,21 +5568,21 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51008644741782672</v>
+        <v>0.51723644403086055</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5594,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.279132885208865</v>
+        <v>2.0512195966879787</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5609,11 +5611,11 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>17.577047192866189</v>
+        <v>17.349133904345301</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5622,7 +5624,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5635,21 +5637,21 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31299240539227124</v>
+        <v>0.32190050914870993</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5663,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>2.8333926664293383</v>
+        <v>2.5500533997864046</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5678,11 +5680,11 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>24.315000552184742</v>
+        <v>24.031661285541809</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5691,7 +5693,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5704,21 +5706,21 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>4.9636161355830488E-2</v>
+        <v>6.0710616917017179E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5732,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>2.6975834619563113</v>
+        <v>2.4278251157606801</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5747,11 +5749,11 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>22.61787767563613</v>
+        <v>22.348119329440497</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5760,7 +5762,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5773,16 +5775,16 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.11580559118887601</v>
+        <v>0.12635117927883399</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5791,98 +5793,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+    </row>
+    <row r="191" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5920,7 +5922,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -5944,12 +5946,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -6207,7 +6209,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6223,7 +6225,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6239,7 +6241,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6503,7 +6505,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>1040530375</v>
@@ -6539,7 +6541,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-241780101</v>
@@ -6575,7 +6577,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-865081548</v>
@@ -6640,7 +6642,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6793,7 +6795,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7194,7 +7196,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7243,7 +7245,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7591,12 +7593,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7645,7 +7647,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7694,7 +7696,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7743,7 +7745,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7945,7 +7947,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8197,7 +8199,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8563,15 +8565,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8592,7 +8594,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8603,19 +8605,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8676,7 +8678,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8697,7 +8699,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>50322384.659999996</v>
@@ -8708,7 +8710,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8718,7 +8720,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8740,7 +8742,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8804,19 +8806,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8824,7 +8826,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8853,7 +8855,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8873,7 +8875,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8884,7 +8886,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8893,7 +8895,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8914,7 +8916,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8934,7 +8936,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8954,7 +8956,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9013,16 +9015,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -9055,7 +9057,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>0</v>
@@ -9099,7 +9101,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9149,10 +9151,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9160,10 +9162,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9185,7 +9187,7 @@
         <v>70000000</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9201,7 +9203,7 @@
         <v>171292.86</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9217,7 +9219,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9246,14 +9248,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>70171292.859999999</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9273,7 +9275,7 @@
         <v>136752472.12</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9292,7 +9294,7 @@
         <v>206923764.97999999</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9316,13 +9318,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9330,7 +9332,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9362,7 +9364,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9389,7 +9391,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9403,7 +9405,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9415,7 +9417,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9429,7 +9431,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9446,7 +9448,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9483,10 +9485,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9495,7 +9497,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9506,12 +9508,12 @@
         <v>0</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9522,13 +9524,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9536,7 +9538,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9547,12 +9549,12 @@
         <v>790701386.39893258</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9562,7 +9564,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9572,7 +9574,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9582,7 +9584,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9595,7 +9597,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9607,7 +9609,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9618,12 +9620,12 @@
         <v>-466172589.92553371</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9634,12 +9636,12 @@
         <v>3.6961558948054818</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9647,12 +9649,12 @@
         <v>932345179.85106742</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9660,7 +9662,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9668,10 +9670,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9680,7 +9682,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9694,7 +9696,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9708,7 +9710,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9722,7 +9724,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9736,7 +9738,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9747,15 +9749,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>289</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9772,7 +9774,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9789,7 +9791,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9806,7 +9808,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9834,17 +9836,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Q809"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10166,7 +10168,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10333,7 +10335,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10445,7 +10447,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10555,7 +10557,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10612,7 +10614,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10677,7 +10679,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10702,7 +10704,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10796,7 +10798,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -11015,7 +11017,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -11030,7 +11032,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11090,7 +11092,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11207,14 +11209,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-182442565.75</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11272,7 +11274,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11384,7 +11386,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11566,21 +11568,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11634,7 +11636,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11719,7 +11721,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11774,7 +11776,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11890,11 +11892,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11906,7 +11908,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11933,7 +11935,7 @@
         <v>2.3119466464108229E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12012,17 +12014,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12077,7 +12079,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12132,7 +12134,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12187,7 +12189,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12242,13 +12244,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12298,7 +12300,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12357,17 +12359,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12392,7 +12394,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12417,7 +12419,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12442,7 +12444,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12472,12 +12474,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>464</v>
+        <v>59</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12495,7 +12497,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12687,7 +12689,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12860,7 +12862,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12974,7 +12976,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13146,7 +13148,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13253,7 +13255,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13314,7 +13316,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13433,7 +13435,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13488,1310 +13490,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
-        <v>6.5230769230769231E-2</v>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0.1</v>
       </c>
       <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>6.5230769230769231E-2</v>
-      </c>
-      <c r="H93" s="23">
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
+        <v>5.8707692307692315E-2</v>
+      </c>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>5.8707692307692315E-2</v>
+      </c>
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5230769230769231E-2</v>
-      </c>
-      <c r="I93" s="23">
+        <v>5.8707692307692315E-2</v>
+      </c>
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.1538461538461542E-2</v>
-      </c>
-      <c r="J93" s="23">
+        <v>5.5384615384615386E-2</v>
+      </c>
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>-1.7808085751753522E-2</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-1.9179346982288958E-2</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>9.9817583967300338E-2</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.22167664239249651</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.39702156717595383</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>5.5676809853508757E-3</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.1344120049846802</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.3203048570560727</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.43141114700410199</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>-2.4591939303572952E-2</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-7.315082285144836E-2</v>
+        <f>C4/G4-1</f>
+        <v>-1.7808085751753522E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>-1.9179346982288958E-2</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>9.9817583967300338E-2</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.22167664239249651</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.39702156717595383</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>5.5676809853508757E-3</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.1344120049846802</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.3203048570560727</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.43141114700410199</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>-2.4591939303572952E-2</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-7.315082285144836E-2</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>-0.11764082311449808</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>0.20275039965443487</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>0.33611869613839951</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>0.20306609824085897</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>0.28298595437040963</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>0.55073801802000588</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>0.36744670119652811</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>3.5388149733221574E-2</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>-4.1517838553966069E-2</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>8672531611.6100006</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>8672531611.6100006</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>8628787997</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>7976614494</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>5950736130</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>5246920436</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>4677192094</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>3570534120</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>2922308439</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>2546084184</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>2510420855</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>1180157900.1600001</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>851687201</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>790890033</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>567013771</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>458930449</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>595526269</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>2566018245.5700002</v>
+        <f>BS!C4</f>
+        <v>1180157900.1600001</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>851687201</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>790890033</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>567013771</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>458930449</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>595526269</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="346">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="346">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>2566018245.5700002</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>2819492731</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>2459595915</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1867069694</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>1603890018</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>1464309401</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346">
+      <c r="N104" s="346">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="346">
+      <c r="O104" s="346">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="346">
+      <c r="P104" s="346">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>4208442385.48</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>4208442385.48</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>4086723205</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>3962039491</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>2581011486</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>2275269694</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>2004846282</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>1560581012</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>1160274283</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>894522509</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>1020621379</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>4464089226.1300011</v>
+        <f>BS!G30</f>
+        <v>4208442385.48</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>4208442385.48</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>4086723205</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>3962039491</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>2581011486</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>2275269694</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>2004846282</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>1560581012</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>1160274283</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>894522509</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>1020621379</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>4464089226.1300011</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>4464089226.1300011</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>4542064792</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>4014575003</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>3369724644</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>2971650742</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>2672345812</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>2009953108</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>1762034156</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>1651561675</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>1489799476</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>0.19602951336944791</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>0.13894976582280258</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.12655619326339668</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>9.9788746248012927E-2</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>9.8671357490055969E-2</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.17887443048585716</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0.4262271242755018</v>
+        <v>0.19602951336944791</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>0.45999030424732668</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>0.13894976582280258</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.39357822577162382</v>
+        <f t="shared" si="43"/>
+        <v>0.12655619326339668</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.32858557137569266</v>
+        <f t="shared" si="43"/>
+        <v>9.9788746248012927E-2</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.34484093545253147</v>
+        <f t="shared" si="43"/>
+        <v>9.8671357490055969E-2</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.43982528360803785</v>
+        <f t="shared" si="43"/>
+        <v>0.17887443048585716</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
+        <f>C104/C$4</f>
+        <v>0.4262271242755018</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>0.45999030424732668</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.39357822577162382</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.32858557137569266</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.34484093545253147</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.43982528360803785</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>1.2267060985735432</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>0.26587914456111778</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>1.2265191844187875</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>0.89192297644013196</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>1.1870279725250534</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>1.0745976191603042</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>1.3371903704995902</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>0.14539357818327475</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>2.2963859955268697</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>2.0900844453279315</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>1.2267060985735432</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>0.26587914456111778</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>1.2265191844187875</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>0.89192297644013196</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>1.1870279725250534</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>1.0745976191603042</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>1.3371903704995902</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>0.14539357818327475</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>2.2963859955268697</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>2.0900844453279315</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.200456255666277</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>0.27116456999804678</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.2199607244034283</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>0.89968050779407216</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>1.1677340192713959</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.0732180065445227</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.3254255497740837</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.1552213431776675</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.9110575906710221</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>1.5080765021607145</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>0.173581864935303</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.18394654535282634</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.20447293512619397</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.18697389712928372</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.17095909481703916</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.19852071545653932</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.15559485650577207</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.11382236785513526</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>0.10989841504554551</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>0.15193318213542392</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>0.15461618014733902</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.69418106703013427</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.70676723862204571</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.72424065583401998</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.71235001406600507</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.78160094707476135</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.63452418587427573</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.70787430074707558</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.8174051152884656</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>0.75643264909998087</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>0.60653960450508027</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>0.6306654630623677</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.9427325871638936</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.9427325871638936</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.8997500899146134</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>1.9869138048334527</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>1.7659413627744476</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>1.7656585149265163</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>1.7502196283869267</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.776426577211472</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>1.6584856933953782</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>1.5416222249163054</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>1.6850729883059778</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>0.23409392300550072</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>0.25256959684173202</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>0.28132945542067472</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>0.26463875493458239</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>0.23596824667073013</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>0.22241328542010971</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>0.19277199065750988</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>0.16527692694808879</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>0.13787115827055513</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>0.14206587168474952</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>0.16431329514039916</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (CNY)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.3596193986603011</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.5036318148780807</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.7146815884251216</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.4544047229635815</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.1127061515565433</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.90758970686335116</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.71750010305105094</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.42786498559302777</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.33465922523275804</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.33299013109390641</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.3428693276341514</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3668886071403145E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (CNY)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>1.3596193986603011</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>1.5036318148780807</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.7146815884251216</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.4544047229635815</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.1127061515565433</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.90758970686335116</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.71750010305105094</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.42786498559302777</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.33465922523275804</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.33299013109390641</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.3428693276341514</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>8.3668886071403145E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>9.2531188607881898E-2</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>0.10551886698000748</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>8.9501829105451167E-2</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>6.8474224711171899E-2</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>5.5851674268513916E-2</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>4.4153852495449286E-2</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>2.6330152959570939E-2</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>2.0594413860477417E-2</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>2.0491700375009626E-2</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>2.1099650931332394E-2</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>9.0551146959924028E-2</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.10761648206197513</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>8.9023243711152777E-2</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>6.906978168096066E-2</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.494386112727602E-2</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>4.4097165963809963E-2</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.6098495944924038E-2</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.1986477128656336E-2</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.7053239143462698E-2</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.5224211559712039E-2</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15473,6 +15495,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15494,13 +15517,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15517,20 +15540,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15541,7 +15564,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15551,7 +15574,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15560,9 +15583,9 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15572,15 +15595,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15590,13 +15613,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15606,13 +15629,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15622,13 +15645,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15642,7 +15665,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15673,7 +15696,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15683,13 +15706,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15697,9 +15720,9 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15707,7 +15730,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15732,7 +15755,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -16504,7 +16527,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16541,7 +16564,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16762,7 +16785,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16991,19 +17014,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17128,7 +17151,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17254,18 +17277,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17277,31 +17300,31 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
-        <v>611044420</v>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
+        <v>549939978</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17311,7 +17334,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17320,29 +17343,29 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>10184073666.666668</v>
+        <v>9165666300</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>17.666666666666668</v>
+        <v>15.9</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17355,7 +17378,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17365,13 +17388,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1">
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17379,9 +17402,9 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1">
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17389,13 +17412,13 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1">
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>19.198468587193613</v>
+        <v>17.278621728474253</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17411,16 +17434,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17430,7 +17453,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>645640016.1644429</v>
+        <v>581076014.54799867</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17442,7 +17465,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>609094354.87211585</v>
+        <v>548184919.38490438</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17452,7 +17475,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>682194316.53237605</v>
+        <v>613974884.87913847</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17464,7 +17487,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>607150513.11176217</v>
+        <v>546435461.80058599</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17474,7 +17497,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>720818217.3617661</v>
+        <v>648736395.62558961</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17486,7 +17509,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>605212874.85790777</v>
+        <v>544691587.37211716</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17496,7 +17519,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>761628893.54112041</v>
+        <v>685466004.18700838</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17508,7 +17531,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>603281420.31290638</v>
+        <v>542953278.28161573</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17518,7 +17541,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>804750154.06767929</v>
+        <v>724275138.66091144</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17530,7 +17553,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>601356129.74229181</v>
+        <v>541220516.76806271</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18086,11 +18109,11 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>10760666936.074049</v>
+        <v>9684600242.4666443</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18102,7 +18125,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>8040996313.4708843</v>
+        <v>7236896682.1237965</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18113,7 +18136,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>11067091606.367868</v>
+        <v>9960382445.7310829</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18123,7 +18146,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18134,7 +18157,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>11067091606.367868</v>
+        <v>9960382445.7310829</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18164,19 +18187,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>10184073666.666664</v>
+        <v>9165666299.9999962</v>
       </c>
       <c r="C51" s="123">
-        <v>10335360369.920647</v>
+        <v>9301824332.9285812</v>
       </c>
       <c r="D51" s="123">
-        <v>10960472432.552408</v>
+        <v>9864425189.2971668</v>
       </c>
       <c r="E51" s="123">
-        <v>11619670974.634827</v>
+        <v>10457703877.171345</v>
       </c>
       <c r="F51" s="123">
-        <v>11790144287.962168</v>
+        <v>10611129859.165951</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18185,19 +18208,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>10184073666.666662</v>
+        <v>9165666299.9999962</v>
       </c>
       <c r="C52" s="123">
-        <v>10473287830.555006</v>
+        <v>9425959047.4995041</v>
       </c>
       <c r="D52" s="123">
-        <v>11773269132.162727</v>
+        <v>10595942218.946455</v>
       </c>
       <c r="E52" s="123">
-        <v>13345653758.282316</v>
+        <v>12011088382.454086</v>
       </c>
       <c r="F52" s="123">
-        <v>13789057060.391842</v>
+        <v>12410151354.352661</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18206,19 +18229,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>10184073666.66666</v>
+        <v>9165666299.9999943</v>
       </c>
       <c r="C53" s="123">
-        <v>10655661373.557159</v>
+        <v>9590095236.2014408</v>
       </c>
       <c r="D53" s="123">
-        <v>12965390294.20874</v>
+        <v>11668851264.787868</v>
       </c>
       <c r="E53" s="123">
-        <v>16173925861.19178</v>
+        <v>14556533275.072603</v>
       </c>
       <c r="F53" s="123">
-        <v>17159900260.561775</v>
+        <v>15443910234.505602</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18227,19 +18250,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>10184073666.66666</v>
+        <v>9165666299.9999943</v>
       </c>
       <c r="C54" s="123">
-        <v>10854226606.074554</v>
+        <v>9768803945.4670963</v>
       </c>
       <c r="D54" s="123">
-        <v>14413897651.510311</v>
+        <v>12972507886.359283</v>
       </c>
       <c r="E54" s="123">
-        <v>20056284603.593559</v>
+        <v>18050656143.234207</v>
       </c>
       <c r="F54" s="123">
-        <v>21937865135.675831</v>
+        <v>19744078622.108253</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18248,19 +18271,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>10184073666.66666</v>
+        <v>9165666299.9999943</v>
       </c>
       <c r="C55" s="123">
-        <v>11051523321.676662</v>
+        <v>9946370989.5089912</v>
       </c>
       <c r="D55" s="123">
-        <v>16028177466.165306</v>
+        <v>14425359719.548777</v>
       </c>
       <c r="E55" s="123">
-        <v>24991211176.16</v>
+        <v>22492090058.544006</v>
       </c>
       <c r="F55" s="123">
-        <v>28226959801.397446</v>
+        <v>25404263821.257702</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18269,19 +18292,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>10184073666.666658</v>
+        <v>9165666299.9999943</v>
       </c>
       <c r="C56" s="123">
-        <v>11237373310.277342</v>
+        <v>10113635979.249605</v>
       </c>
       <c r="D56" s="123">
-        <v>17741712775.109974</v>
+        <v>15967541497.598978</v>
       </c>
       <c r="E56" s="123">
-        <v>31017238180.316628</v>
+        <v>27915514362.284977</v>
       </c>
       <c r="F56" s="123">
-        <v>36198427980.462364</v>
+        <v>32578585182.416134</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18294,7 +18317,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18331,23 +18354,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>15.9</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>15.9</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>15.9</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>15.9</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>17.666666666666668</v>
+        <v>15.9</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18358,23 +18381,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.666666666666661</v>
+        <v>15.899999999999993</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>17.929108970696248</v>
+        <v>16.13619807362662</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>19.013512599469532</v>
+        <v>17.112161339522579</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>20.157047229255308</v>
+        <v>18.141342506329778</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>20.45277321285398</v>
+        <v>18.407495891568583</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18385,23 +18408,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666657</v>
+        <v>15.899999999999993</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>18.168376532083062</v>
+        <v>16.351538878874756</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>20.423499293377869</v>
+        <v>18.381149364040084</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>23.151169572548024</v>
+        <v>20.836052615293223</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>23.920356696842681</v>
+        <v>21.52832102715842</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18412,23 +18435,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666657</v>
+        <v>15.89999999999999</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>18.484746257842581</v>
+        <v>16.636271632058317</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>22.491513320523023</v>
+        <v>20.242361988470723</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>28.057471522059373</v>
+        <v>25.251724369853438</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>29.76787559273593</v>
+        <v>26.791088033462344</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18439,23 +18462,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666657</v>
+        <v>15.89999999999999</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>18.829204270352438</v>
+        <v>16.94628384331719</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>25.004289394543409</v>
+        <v>22.503860455089075</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>34.792334213295284</v>
+        <v>31.313100791965763</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>38.056377380577963</v>
+        <v>34.250739642520173</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18466,23 +18489,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666657</v>
+        <v>15.89999999999999</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>19.171461742465894</v>
+        <v>17.254315568219297</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>27.80463671386644</v>
+        <v>25.024173042479799</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>43.353122914909527</v>
+        <v>39.017810623418583</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>48.966288554735989</v>
+        <v>44.069659699262395</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18492,40 +18515,40 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>17.666666666666654</v>
+        <v>15.89999999999999</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>19.49386217927329</v>
+        <v>17.544475961345956</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>30.777165990021761</v>
+        <v>27.699449391019588</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>53.806681470285952</v>
+        <v>48.426013323257372</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>62.794671554794832</v>
+        <v>56.515204399315358</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18543,7 +18566,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>23.920356696842681</v>
+        <v>21.52832102715842</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18565,7 +18588,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>20.157047229255308</v>
+        <v>18.141342506329778</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18588,7 +18611,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>19.013512599469532</v>
+        <v>17.112161339522579</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18611,7 +18634,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>17.929108970696248</v>
+        <v>16.13619807362662</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18634,7 +18657,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>17.666666666666657</v>
+        <v>15.899999999999993</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18650,7 +18673,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18702,32 +18725,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="6" width="42.6640625" customWidth="1"/>
-    <col min="8" max="9" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="6" width="42.73046875" customWidth="1"/>
+    <col min="8" max="9" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18739,14 +18762,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18754,7 +18777,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.06</v>
+        <v>0.95400000000000007</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18763,7 +18786,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.06</v>
+        <v>0.95400000000000007</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18775,7 +18798,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18783,12 +18806,12 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>26.644938697660866</v>
+        <v>26.538938697660868</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18798,11 +18821,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 景津装备(603279.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18823,8 +18846,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18845,8 +18868,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18856,8 +18879,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18868,10 +18891,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>447</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>444</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18882,15 +18905,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>9.6365877843450409E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18901,14 +18924,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.12333037284725878</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18925,12 +18948,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.10557193538775511</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18939,38 +18962,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18980,12 +19003,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18995,44 +19018,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.05</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19042,55 +19065,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19100,55 +19123,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.09</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19158,24 +19181,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19188,7 +19211,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19197,12 +19220,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19217,39 +19240,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19259,55 +19282,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.1</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19317,23 +19340,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19344,7 +19367,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19353,7 +19376,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19362,15 +19385,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19378,19 +19401,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
         <v>5.6617154223326201E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19406,20 +19429,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19429,19 +19452,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19451,14 +19474,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19467,7 +19490,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19476,12 +19499,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19491,11 +19514,11 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
-        <v>1.06</v>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
+        <v>0.95400000000000007</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19504,25 +19527,25 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.829322250329541</v>
+        <v>1.6463900252965866</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19530,7 +19553,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19544,18 +19567,18 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>12.534408209968158</v>
+        <v>12.351475984935202</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.51008644741782672</v>
+        <v>0.51723644403086055</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19563,12 +19586,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19581,11 +19604,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22012061346574296</v>
+        <v>0.21441960331275056</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19593,12 +19616,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19607,11 +19630,11 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.279132885208865</v>
+        <v>2.0512195966879787</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19619,7 +19642,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19633,30 +19656,30 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>17.577047192866189</v>
+        <v>17.349133904345301</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.31299240539227124</v>
+        <v>0.32190050914870993</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19667,11 +19690,11 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.8333926664293383</v>
+        <v>2.5500533997864046</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19679,7 +19702,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19691,21 +19714,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>24.315000552184742</v>
+        <v>24.031661285541809</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>4.9636161355830488E-2</v>
+        <v>6.0710616917017179E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19713,12 +19736,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19727,17 +19750,17 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>2.6975834619563113</v>
+        <v>2.4278251157606801</v>
       </c>
       <c r="D103" s="116"/>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19747,21 +19770,21 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>22.61787767563613</v>
+        <v>22.348119329440497</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.11580559118887601</v>
+        <v>0.12635117927883399</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19769,32 +19792,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
+        <v>322</v>
+      </c>
+      <c r="F110" s="284" t="s">
         <v>325</v>
-      </c>
-      <c r="F110" s="284" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2195162A-1400-4439-92BC-89DA6CA514D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8DA78C-7B8B-4669-9022-40748A0E4EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>16.25</v>
+        <v>16.2</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9367.4262500000004</v>
+        <v>9338.6034</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21441960331275056</v>
+        <v>0.21572730031339504</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.3668886071403145E-2</v>
+        <v>8.3927123374092666E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.8707692307692315E-2</v>
+        <v>5.8888888888888893E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.6463900252965866</v>
+        <v>1.6463900252965868</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8707692307692315E-2</v>
+        <v>5.8888888888888893E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8707692307692315E-2</v>
+        <v>5.8888888888888893E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.8707692307692315E-2</v>
+        <v>5.8888888888888893E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.5384615384615386E-2</v>
+        <v>5.5555555555555559E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3668886071403145E-2</v>
+        <v>8.3927123374092666E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.2531188607881898E-2</v>
+        <v>9.2816778696177826E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.10551886698000748</v>
+        <v>0.10584454249537788</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.9501829105451167E-2</v>
+        <v>8.9778069318739606E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.8474224711171899E-2</v>
+        <v>6.8685564910897737E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.5851674268513916E-2</v>
+        <v>5.6024055979219209E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.4153852495449286E-2</v>
+        <v>4.4290129817966109E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6330152959570939E-2</v>
+        <v>2.6411418863767147E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.0594413860477417E-2</v>
+        <v>2.0657976866219632E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.0491700375009626E-2</v>
+        <v>2.0554946363821384E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.1099650931332394E-2</v>
+        <v>2.1164773310750087E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0551146959924028E-2</v>
+        <v>9.0830625808565768E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10761648206197513</v>
+        <v>0.10794863169796888</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9023243711152777E-2</v>
+        <v>8.9298006809026706E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.906978168096066E-2</v>
+        <v>6.9282960019482143E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.494386112727602E-2</v>
+        <v>5.5113440945570087E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4097165963809963E-2</v>
+        <v>4.4233268327895793E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6098495944924038E-2</v>
+        <v>2.6179046858334297E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1986477128656336E-2</v>
+        <v>2.2054336625967005E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7053239143462698E-2</v>
+        <v>1.7105872597609189E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5224211559712039E-2</v>
+        <v>1.5271199866995102E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.25</v>
+        <v>-16.2</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.25</v>
+        <v>16.2</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6463900252965866</v>
+        <v>1.6463900252965868</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.25</v>
+        <v>16.2</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21441960331275056</v>
+        <v>0.21572730031339504</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8DA78C-7B8B-4669-9022-40748A0E4EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7B0C52-CAD1-4CF2-9622-CC243C6F92F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>25.584938697660867</v>
+        <v>22.410983859246461</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21572730031339504</v>
+        <v>0.16748366905435308</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>12.351475984935202</v>
+        <v>11.023450157758077</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>17.349133904345301</v>
+        <v>15.451342015601119</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>24.031661285541809</v>
+        <v>21.366747599735401</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>22.348119329440497</v>
+        <v>19.876895342965671</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
-        <v>1037280588.8935957</v>
+        <v>898092603.37923622</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
-        <v>-213321214.99999997</v>
+        <v>-213321215</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
-        <v>13985177.697766012</v>
+        <v>12828070.849551909</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>7735570.6977660116</v>
+        <v>6578463.8495519087</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-261254039.89784044</v>
+        <v>-226167766.80719703</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
-        <v>866779085.10917377</v>
+        <v>865118716.5321629</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>783762119.69352126</v>
+        <v>678503300.42159104</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.3927123374092666E-2</v>
+        <v>7.2655757114772762E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>0.7796299472076299</v>
+        <v>0.90057693104856651</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4910,11 +4910,11 @@
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
-        <v>0.23409392300550072</v>
+        <v>0.2026552385945618</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G121</f>
-        <v>0.25256959684173202</v>
+        <v>0.25219765791020438</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4924,11 +4924,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C118</f>
-        <v>0.173581864935303</v>
+        <v>0.16696657384597549</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G118</f>
-        <v>0.18394654535282634</v>
+        <v>0.18367566206999161</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="C75" s="324">
         <f>Normalized_FCF!C119</f>
-        <v>0.69418106703013427</v>
+        <v>0.62476296032712075</v>
       </c>
       <c r="D75" s="324">
         <f>Normalized_FCF!G119</f>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>22.660323311005019</v>
+        <v>19.617054420988644</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>0.26060254325045429</v>
+        <v>0.30099118789407647</v>
       </c>
     </row>
     <row r="107" spans="2:6">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>790701386.39893258</v>
+        <v>867841842.9465394</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3716571858767135</v>
+        <v>1.5054754178482339</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>23.615428128302636</v>
+        <v>20.705977470257782</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>31.64 CNY</v>
+        <v>27.65 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>26.81 CNY</v>
+        <v>23.47 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>25.34 CNY</v>
+        <v>22.2 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>23.95 CNY</v>
+        <v>21 CNY</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>23.62 CNY</v>
+        <v>20.71 CNY</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>25.584938697660867</v>
+        <v>22.410983859246461</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>10.705085959638616</v>
+        <v>9.3770601324614908</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>12.351475984935202</v>
+        <v>11.023450157758077</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51723644403086055</v>
+        <v>0.50812288175336162</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>15.297914307657322</v>
+        <v>13.40012241891314</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>17.349133904345301</v>
+        <v>15.451342015601119</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.32190050914870993</v>
+        <v>0.31054602008353549</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>21.481607885755405</v>
+        <v>18.816694199948998</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>24.031661285541809</v>
+        <v>21.366747599735401</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>6.0710616917017179E-2</v>
+        <v>4.6594842335769271E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>19.920294213679817</v>
+        <v>17.449070227204992</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>22.348119329440497</v>
+        <v>19.876895342965671</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.12635117927883399</v>
+        <v>0.11291143043551932</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
-        <v>0.26060254325045429</v>
+        <v>0.30099118789407647</v>
       </c>
       <c r="D50" s="95">
         <f>G31/Normalized_FCF!G8</f>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.15034876548168696</v>
+        <v>0.13017414540681585</v>
       </c>
       <c r="D54" s="92">
         <f>Normalized_FCF!G8/G35</f>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>790701386.39893258</v>
+        <v>867841842.9465394</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-466172589.92553371</v>
+        <v>-427602361.6517303</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.6961558948054818</v>
+        <v>4.0295534374372126</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9646,7 +9646,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>932345179.85106742</v>
+        <v>855204723.3034606</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9778,11 +9778,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>790701386.39893258</v>
+        <v>867841842.9465394</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.3716571858767135</v>
+        <v>1.5054754178482339</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9812,11 +9812,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>550576857.66493261</v>
+        <v>627717314.21253943</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>0.95510481729761743</v>
+        <v>1.088923049269138</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -9949,8 +9949,8 @@
         <v>2</v>
       </c>
       <c r="C4" s="327">
-        <f>AVERAGE(G4:I4)</f>
-        <v>6020307248</v>
+        <f>AVERAGE(G4:I4)*0.9</f>
+        <v>5418276523.1999998</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
@@ -10007,7 +10007,7 @@
       </c>
       <c r="C5" s="328">
         <f>C25</f>
-        <v>-4628427392.8564043</v>
+        <v>-4165584653.5707636</v>
       </c>
       <c r="E5" s="268"/>
       <c r="G5" s="333">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
-        <v>1391879855.1435957</v>
+        <v>1252691869.6292362</v>
       </c>
       <c r="E6" s="268"/>
       <c r="G6" s="329">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
-        <v>1037280588.8935957</v>
+        <v>898092603.37923622</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
@@ -10284,7 +10284,7 @@
       </c>
       <c r="C10" s="328">
         <f>-C4*C78</f>
-        <v>-213321214.99999997</v>
+        <v>-213321215</v>
       </c>
       <c r="E10" s="268"/>
       <c r="G10" s="328">
@@ -10396,32 +10396,32 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>7735570.6977660116</v>
+        <v>6578463.8495519087</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
         <f>G50</f>
-        <v>13818159.109173693</v>
+        <v>12157790.53216283</v>
       </c>
       <c r="H12" s="328">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>12176685.418780401</v>
+        <v>10787766.413925113</v>
       </c>
       <c r="I12" s="328">
         <f t="shared" si="6"/>
-        <v>15999426.385417301</v>
+        <v>14567159.823979978</v>
       </c>
       <c r="J12" s="328">
         <f t="shared" si="6"/>
-        <v>9485582.0078302585</v>
+        <v>8668145.4284623209</v>
       </c>
       <c r="K12" s="328">
         <f t="shared" si="6"/>
-        <v>6784112.6493268209</v>
+        <v>6216681.3090674309</v>
       </c>
       <c r="L12" s="328">
         <f t="shared" si="6"/>
-        <v>3827612.9044996742</v>
+        <v>3510923.5352386222</v>
       </c>
       <c r="M12" s="328">
         <f t="shared" si="6"/>
@@ -10451,32 +10451,32 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>1045016159.5913618</v>
+        <v>904671067.22878814</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>1127493216.1091738</v>
+        <v>1125832847.5321629</v>
       </c>
       <c r="H13" s="329">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>1277816614.4187803</v>
+        <v>1276427695.4139252</v>
       </c>
       <c r="I13" s="329">
         <f t="shared" si="7"/>
-        <v>1062412130.3854173</v>
+        <v>1060979863.82398</v>
       </c>
       <c r="J13" s="329">
         <f t="shared" si="7"/>
-        <v>795148016.00783026</v>
+        <v>794330579.42846227</v>
       </c>
       <c r="K13" s="329">
         <f t="shared" si="7"/>
-        <v>660934604.6493268</v>
+        <v>660367173.30906749</v>
       </c>
       <c r="L13" s="329">
         <f t="shared" si="7"/>
-        <v>515153421.90449965</v>
+        <v>514836732.53523862</v>
       </c>
       <c r="M13" s="329">
         <f t="shared" si="7"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-261254039.89784044</v>
+        <v>-226167766.80719703</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -10618,34 +10618,34 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>783762119.69352126</v>
+        <v>678503300.42159104</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
       <c r="G16" s="329">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>866779085.10917377</v>
+        <v>865118716.5321629</v>
       </c>
       <c r="H16" s="329">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>988440204.41878033</v>
+        <v>987051285.41392517</v>
       </c>
       <c r="I16" s="329">
         <f t="shared" si="8"/>
-        <v>838401783.38541734</v>
+        <v>836969516.82397997</v>
       </c>
       <c r="J16" s="329">
         <f t="shared" si="8"/>
-        <v>641427250.00783026</v>
+        <v>640609813.42846227</v>
       </c>
       <c r="K16" s="329">
         <f t="shared" si="8"/>
-        <v>523186439.6493268</v>
+        <v>522619008.30906749</v>
       </c>
       <c r="L16" s="329">
         <f t="shared" si="8"/>
-        <v>413607956.90449965</v>
+        <v>413291267.53523862</v>
       </c>
       <c r="M16" s="329">
         <f t="shared" si="8"/>
@@ -10726,34 +10726,34 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>783762119.69352126</v>
+        <v>678503300.42159104</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
       <c r="G19" s="334">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>866779085.10917377</v>
+        <v>865118716.5321629</v>
       </c>
       <c r="H19" s="334">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>988440204.41878033</v>
+        <v>987051285.41392517</v>
       </c>
       <c r="I19" s="334">
         <f t="shared" si="9"/>
-        <v>838401783.38541734</v>
+        <v>836969516.82397997</v>
       </c>
       <c r="J19" s="334">
         <f t="shared" si="9"/>
-        <v>641427250.00783026</v>
+        <v>640609813.42846227</v>
       </c>
       <c r="K19" s="334">
         <f t="shared" si="9"/>
-        <v>523186439.6493268</v>
+        <v>522619008.30906749</v>
       </c>
       <c r="L19" s="334">
         <f t="shared" si="9"/>
-        <v>413607956.90449965</v>
+        <v>413291267.53523862</v>
       </c>
       <c r="M19" s="334">
         <f t="shared" si="9"/>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
-        <v>-4328934333.5839558</v>
+        <v>-3896040900.2255597</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="C24" s="328">
         <f>-C4*C29</f>
-        <v>-299493059.2724486</v>
+        <v>-269543753.3452037</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
-        <v>-4628427392.8564043</v>
+        <v>-4165584653.5707636</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
@@ -11398,7 +11398,7 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>3.0304527366208603E-2</v>
+        <v>3.3671697073565113E-2</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="265"/>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C39" s="23">
         <f>ABS(C34/$C$4)</f>
-        <v>2.8595999075826571E-2</v>
+        <v>3.1773332306473966E-2</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="265"/>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
-        <v>5.8900526442035174E-2</v>
+        <v>6.5445029380039085E-2</v>
       </c>
       <c r="E40" s="268"/>
       <c r="G40" s="30">
@@ -11587,27 +11587,27 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.23123343650766176</v>
+        <v>0.23157445758621098</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.22646161173262247</v>
+        <v>0.22670803135947301</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21085070528960778</v>
+        <v>0.21113534256213184</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.1933234604190803</v>
+        <v>0.19352240739693713</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20841421228517046</v>
+        <v>0.20859329562029971</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19711693775534064</v>
+        <v>0.19723818947407681</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
@@ -11725,32 +11725,32 @@
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
-        <v>13985177.697766012</v>
+        <v>12828070.849551909</v>
       </c>
       <c r="E48" s="268"/>
       <c r="G48" s="337">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>20067766.109173693</v>
+        <v>18407397.53216283</v>
       </c>
       <c r="H48" s="337">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>16786936.418780401</v>
+        <v>15398017.413925113</v>
       </c>
       <c r="I48" s="337">
         <f t="shared" si="19"/>
-        <v>17310849.385417301</v>
+        <v>15878582.823979978</v>
       </c>
       <c r="J48" s="337">
         <f t="shared" si="19"/>
-        <v>9879810.0078302585</v>
+        <v>9062373.4284623209</v>
       </c>
       <c r="K48" s="337">
         <f t="shared" si="19"/>
-        <v>6858163.6493268209</v>
+        <v>6290732.3090674309</v>
       </c>
       <c r="L48" s="337">
         <f t="shared" si="19"/>
-        <v>3827612.9044996742</v>
+        <v>3510923.5352386222</v>
       </c>
       <c r="M48" s="337">
         <f t="shared" si="19"/>
@@ -11837,32 +11837,32 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>7735570.6977660116</v>
+        <v>6578463.8495519087</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>13818159.109173693</v>
+        <v>12157790.53216283</v>
       </c>
       <c r="H50" s="329">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>12176685.418780401</v>
+        <v>10787766.413925113</v>
       </c>
       <c r="I50" s="329">
         <f t="shared" si="20"/>
-        <v>15999426.385417301</v>
+        <v>14567159.823979978</v>
       </c>
       <c r="J50" s="329">
         <f t="shared" si="20"/>
-        <v>9485582.0078302585</v>
+        <v>8668145.4284623209</v>
       </c>
       <c r="K50" s="329">
         <f t="shared" si="20"/>
-        <v>6784112.6493268209</v>
+        <v>6216681.3090674309</v>
       </c>
       <c r="L50" s="329">
         <f t="shared" si="20"/>
-        <v>3827612.9044996742</v>
+        <v>3510923.5352386222</v>
       </c>
       <c r="M50" s="329">
         <f t="shared" si="20"/>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>165.97533075177299</v>
+        <v>143.70385263893172</v>
       </c>
       <c r="E55" s="268"/>
       <c r="G55" s="42">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
-        <v>0.23119747843533911</v>
+        <v>0.23119747843533914</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="265"/>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
-        <v>5.8900526442035174E-2</v>
+        <v>6.5445029380039085E-2</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="265"/>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
-        <v>0.17229695199330394</v>
+        <v>0.16575244905530004</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="265"/>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
-        <v>3.5433609318007347E-2</v>
+        <v>3.9370677020008168E-2</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="265"/>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
-        <v>3.5433609318007347E-2</v>
+        <v>3.9370677020008168E-2</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
@@ -12923,34 +12923,34 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>1.2849129419990712E-3</v>
+        <v>1.2141247906754507E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>2.2543839687475952E-3</v>
+        <v>1.9835006859128691E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>1.9484819492810032E-3</v>
+        <v>1.7262306947811623E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.815738843295518E-3</v>
+        <v>2.5636742696137915E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.0394272276666094E-3</v>
+        <v>1.8636760280588834E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>2.0377006853751984E-3</v>
+        <v>1.8672649496029364E-3</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1560767245484278E-3</v>
+        <v>1.0604251480046704E-3</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
@@ -12980,34 +12980,34 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.173581864935303</v>
+        <v>0.16696657384597549</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.18394654535282634</v>
+        <v>0.18367566206999161</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.20447293512619397</v>
+        <v>0.20425068387169415</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.18697389712928372</v>
+        <v>0.18672183255560199</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.17095909481703916</v>
+        <v>0.17078334361743144</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19852071545653932</v>
+        <v>0.19835027972076708</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.15559485650577207</v>
+        <v>0.15549920492922834</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>4.3395466233825751E-2</v>
+        <v>4.1741643461493873E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -13152,34 +13152,34 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>0.13018639870147725</v>
+        <v>0.12522493038448163</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.14141195353717986</v>
+        <v>0.14114107025434514</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15816766468181612</v>
+        <v>0.1579454134273163</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.14755031904882768</v>
+        <v>0.14729825447514594</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13790869101689551</v>
+        <v>0.13773293981728776</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15714617692237623</v>
+        <v>0.15697574118660398</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.12492447486087264</v>
+        <v>0.12482882328432889</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
@@ -13259,34 +13259,34 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>0.13018639870147725</v>
+        <v>0.12522493038448163</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.14141195353717986</v>
+        <v>0.14114107025434514</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15816766468181612</v>
+        <v>0.1579454134273163</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.14755031904882768</v>
+        <v>0.14729825447514594</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13790869101689551</v>
+        <v>0.13773293981728776</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15714617692237623</v>
+        <v>0.15697574118660398</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.12492447486087264</v>
+        <v>0.12482882328432889</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
@@ -13439,20 +13439,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.7796299472076299</v>
+        <v>0.90057693104856651</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.70495981098002258</v>
+        <v>0.70631279652505707</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>0.61819057669685196</v>
+        <v>0.61906045717143798</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>0.68756652409814822</v>
+        <v>0.68874312434634644</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="C97" s="77">
         <f>C4/G4-1</f>
-        <v>-1.7808085751753522E-2</v>
+        <v>-0.11602727717657824</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
@@ -13652,34 +13652,34 @@
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
-        <v>-7.315082285144836E-2</v>
+        <v>-0.19644282078655251</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="265"/>
       <c r="F98" s="27"/>
       <c r="G98" s="6">
         <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-0.11764082311449808</v>
+        <v>-0.11798149509199329</v>
       </c>
       <c r="H98" s="6">
         <f t="shared" si="41"/>
-        <v>0.20275039965443487</v>
+        <v>0.20306495809772374</v>
       </c>
       <c r="I98" s="6">
         <f t="shared" si="41"/>
-        <v>0.33611869613839951</v>
+        <v>0.33569056926824792</v>
       </c>
       <c r="J98" s="6">
         <f t="shared" si="41"/>
-        <v>0.20306609824085897</v>
+        <v>0.20286200092004991</v>
       </c>
       <c r="K98" s="6">
         <f t="shared" si="41"/>
-        <v>0.28298595437040963</v>
+        <v>0.282672994324211</v>
       </c>
       <c r="L98" s="6">
         <f t="shared" si="41"/>
-        <v>0.55073801802000588</v>
+        <v>0.54978470542625413</v>
       </c>
       <c r="M98" s="6">
         <f t="shared" si="41"/>
@@ -14057,7 +14057,7 @@
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0.19602951336944791</v>
+        <v>0.21781057041049767</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="C110" s="94">
         <f>C104/C$4</f>
-        <v>0.4262271242755018</v>
+        <v>0.47358569363944647</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
@@ -14263,27 +14263,27 @@
       <c r="E115" s="268"/>
       <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.200456255666277</v>
+        <v>1.2027602167376248</v>
       </c>
       <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.27116456999804678</v>
+        <v>0.27154613641742054</v>
       </c>
       <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.2199607244034283</v>
+        <v>1.2220483858017317</v>
       </c>
       <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>0.89968050779407216</v>
+        <v>0.90082852604386965</v>
       </c>
       <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>1.1677340192713959</v>
+        <v>1.1690018814598866</v>
       </c>
       <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.0732180065445227</v>
+        <v>1.0740403726583754</v>
       </c>
       <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
@@ -14371,32 +14371,32 @@
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>0.173581864935303</v>
+        <v>0.16696657384597549</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="23">
         <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>0.18394654535282634</v>
+        <v>0.18367566206999161</v>
       </c>
       <c r="H118" s="23">
         <f t="shared" si="45"/>
-        <v>0.20447293512619397</v>
+        <v>0.20425068387169415</v>
       </c>
       <c r="I118" s="23">
         <f t="shared" si="45"/>
-        <v>0.18697389712928372</v>
+        <v>0.18672183255560199</v>
       </c>
       <c r="J118" s="23">
         <f t="shared" si="45"/>
-        <v>0.17095909481703916</v>
+        <v>0.17078334361743144</v>
       </c>
       <c r="K118" s="23">
         <f t="shared" si="45"/>
-        <v>0.19852071545653932</v>
+        <v>0.19835027972076708</v>
       </c>
       <c r="L118" s="23">
         <f t="shared" si="45"/>
-        <v>0.15559485650577207</v>
+        <v>0.15549920492922834</v>
       </c>
       <c r="M118" s="23">
         <f t="shared" si="45"/>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C119" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
-        <v>0.69418106703013427</v>
+        <v>0.62476296032712075</v>
       </c>
       <c r="E119" s="268"/>
       <c r="G119" s="42">
@@ -14536,34 +14536,34 @@
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
-        <v>0.23409392300550072</v>
+        <v>0.2026552385945618</v>
       </c>
       <c r="D121" s="103"/>
       <c r="E121" s="271"/>
       <c r="F121" s="103"/>
       <c r="G121" s="102">
         <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
-        <v>0.25256959684173202</v>
+        <v>0.25219765791020438</v>
       </c>
       <c r="H121" s="102">
         <f t="shared" si="48"/>
-        <v>0.28132945542067472</v>
+        <v>0.2810236651978445</v>
       </c>
       <c r="I121" s="102">
         <f t="shared" si="48"/>
-        <v>0.26463875493458239</v>
+        <v>0.26428198826304999</v>
       </c>
       <c r="J121" s="102">
         <f t="shared" si="48"/>
-        <v>0.23596824667073013</v>
+        <v>0.23572566406659257</v>
       </c>
       <c r="K121" s="102">
         <f t="shared" si="48"/>
-        <v>0.22241328542010971</v>
+        <v>0.22222233722682458</v>
       </c>
       <c r="L121" s="102">
         <f t="shared" si="48"/>
-        <v>0.19277199065750988</v>
+        <v>0.1926534845241199</v>
       </c>
       <c r="M121" s="102">
         <f t="shared" si="48"/>
@@ -14657,34 +14657,34 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.3596193986603011</v>
+        <v>1.1770232652593187</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.5036318148780807</v>
+        <v>1.5007515157802973</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>1.7146815884251216</v>
+        <v>1.7122721823378417</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>1.4544047229635815</v>
+        <v>1.4519201203628025</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.1127061515565433</v>
+        <v>1.1112881159019012</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>0.90758970686335116</v>
+        <v>0.90660536398910496</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>0.71750010305105094</v>
+        <v>0.7169507309916241</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
@@ -14714,34 +14714,34 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.3927123374092666E-2</v>
+        <v>7.2655757114772762E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.2816778696177826E-2</v>
+        <v>9.2638982455573907E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.10584454249537788</v>
+        <v>0.10569581372455814</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.9778069318739606E-2</v>
+        <v>8.962469878782732E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.8685564910897737E-2</v>
+        <v>6.8598031845796381E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.6024055979219209E-2</v>
+        <v>5.5963294073401545E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.4290129817966109E-2</v>
+        <v>4.4256217962445936E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
@@ -15557,7 +15557,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>783762119.69352126</v>
+        <v>678503300.42159104</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>13062701994.892021</v>
+        <v>11308388340.359852</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>790701386.39893258</v>
+        <v>867841842.9465394</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>13613278852.556953</v>
+        <v>11936105654.57239</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>23.615428128302636</v>
+        <v>20.705977470257782</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>25.580208888730507</v>
+        <v>22.406889261039971</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15771,7 +15771,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>828136500.4986105</v>
+        <v>716918226.4225961</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>781260849.52699101</v>
+        <v>676337949.45527923</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>875023232.46530604</v>
+        <v>757508096.21347773</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>778767561.82387495</v>
+        <v>674179508.91195941</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>924564557.76678765</v>
+        <v>800396048.92221439</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>776282231.1092273</v>
+        <v>672027956.73795664</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>976910771.92329133</v>
+        <v>845712195.46378446</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -15859,7 +15859,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>773804831.98940206</v>
+        <v>669883270.94997776</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>1032220679.7597009</v>
+        <v>893594013.26290524</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>771335339.15179336</v>
+        <v>667745429.63488555</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>13802275008.310175</v>
+        <v>11948637107.043268</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>10313862804.104702</v>
+        <v>8928716732.8487206</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>14195313617.70599</v>
+        <v>12288890848.53878</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16575,7 +16575,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>14195313617.70599</v>
+        <v>12288890848.53878</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16605,19 +16605,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>13062701994.892017</v>
+        <v>11308388340.359848</v>
       </c>
       <c r="C56" s="123">
-        <v>13256751368.951902</v>
+        <v>11476376990.788452</v>
       </c>
       <c r="D56" s="123">
-        <v>14058557488.471428</v>
+        <v>12170500991.837341</v>
       </c>
       <c r="E56" s="123">
-        <v>14904084965.24864</v>
+        <v>12902474596.041143</v>
       </c>
       <c r="F56" s="123">
-        <v>15122744232.940859</v>
+        <v>13091768044.995977</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16626,19 +16626,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>13062701994.892015</v>
+        <v>11308388340.359846</v>
       </c>
       <c r="C57" s="123">
-        <v>13433665379.410797</v>
+        <v>11629531547.472206</v>
       </c>
       <c r="D57" s="123">
-        <v>15101099148.808468</v>
+        <v>13073029883.693321</v>
       </c>
       <c r="E57" s="123">
-        <v>17117933714.683388</v>
+        <v>14819004682.635612</v>
       </c>
       <c r="F57" s="123">
-        <v>17686669309.945793</v>
+        <v>15311359401.95233</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16647,19 +16647,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>13062701994.892014</v>
+        <v>11308388340.359844</v>
       </c>
       <c r="C58" s="341">
-        <v>13667588593.43734</v>
+        <v>11832039003.209286</v>
       </c>
       <c r="D58" s="123">
-        <v>16630185052.083202</v>
+        <v>14396760395.708538</v>
       </c>
       <c r="E58" s="123">
-        <v>20745644672.990433</v>
+        <v>17959516065.284988</v>
       </c>
       <c r="F58" s="123">
-        <v>22010314408.807312</v>
+        <v>19054341354.915714</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16678,19 +16678,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>13062701994.892012</v>
+        <v>11308388340.359842</v>
       </c>
       <c r="C59" s="341">
-        <v>13922280236.862001</v>
+        <v>12052525699.760794</v>
       </c>
       <c r="D59" s="123">
-        <v>18488127223.865643</v>
+        <v>16005181961.221029</v>
       </c>
       <c r="E59" s="123">
-        <v>25725390200.092201</v>
+        <v>22270484521.784805</v>
       </c>
       <c r="F59" s="123">
-        <v>28138817927.979591</v>
+        <v>24359790240.388432</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16709,19 +16709,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>13062701994.892012</v>
+        <v>11308388340.35984</v>
       </c>
       <c r="C60" s="341">
-        <v>14175344804.62105</v>
+        <v>12271603836.008841</v>
       </c>
       <c r="D60" s="123">
-        <v>20558699064.309685</v>
+        <v>17797677148.47332</v>
       </c>
       <c r="E60" s="123">
-        <v>32055222180.304966</v>
+        <v>27750223567.310406</v>
       </c>
       <c r="F60" s="123">
-        <v>36205586897.343864</v>
+        <v>31343196597.909771</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16740,19 +16740,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>13062701994.892008</v>
+        <v>11308388340.359842</v>
       </c>
       <c r="C61" s="341">
-        <v>14413727115.698677</v>
+        <v>12477971534.528822</v>
       </c>
       <c r="D61" s="123">
-        <v>22756581938.206429</v>
+        <v>19700385567.78577</v>
       </c>
       <c r="E61" s="123">
-        <v>39784564832.854187</v>
+        <v>34441519775.775749</v>
       </c>
       <c r="F61" s="123">
-        <v>46430268757.777794</v>
+        <v>40194709338.507645</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16832,23 +16832,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>23.615428128302636</v>
+        <v>20.705977470257782</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>23.615428128302636</v>
+        <v>20.705977470257782</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>23.615428128302636</v>
+        <v>20.705977470257782</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>23.615428128302636</v>
+        <v>20.705977470257782</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>23.615428128302636</v>
+        <v>20.705977470257782</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16859,23 +16859,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>23.615428128302632</v>
+        <v>20.705977470257775</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>23.952052324140109</v>
+        <v>20.997393222739927</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>25.342973276647452</v>
+        <v>22.201514260473687</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>26.809739187681949</v>
+        <v>23.471294320744967</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>27.189055021633514</v>
+        <v>23.799668247950002</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16886,23 +16886,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>23.615428128302629</v>
+        <v>20.705977470257771</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>24.258951208981294</v>
+        <v>21.263075757055155</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>27.151506541638664</v>
+        <v>23.767162508054998</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>30.650179583816868</v>
+        <v>26.79596569535655</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>31.63678499456287</v>
+        <v>27.650070545010067</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16913,23 +16913,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>23.615428128302625</v>
+        <v>20.705977470257768</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>24.664745941331741</v>
+        <v>21.614372481246345</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>29.804065020891645</v>
+        <v>26.063483850349769</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>36.943295910458836</v>
+        <v>32.243919979282985</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>39.137162470873363</v>
+        <v>34.14315147379294</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16940,23 +16940,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>23.615428128302622</v>
+        <v>20.705977470257764</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>25.106568390230205</v>
+        <v>21.99685841957567</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>33.027101902710136</v>
+        <v>28.853668661207283</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>45.581833610758714</v>
+        <v>39.722306843350587</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>49.768490599723009</v>
+        <v>43.34669811382458</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16967,23 +16967,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>23.615428128302622</v>
+        <v>20.705977470257761</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>25.545568294401807</v>
+        <v>22.376900879374141</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>36.618994863406328</v>
+        <v>31.963172383518394</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>56.5624132207084</v>
+        <v>49.22820068369878</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>63.762195194106063</v>
+        <v>55.46105591938742</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16993,23 +16993,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>23.615428128302614</v>
+        <v>20.705977470257764</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>25.959098377439442</v>
+        <v>22.734894100932696</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>40.431738700148259</v>
+        <v>35.263866831347897</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>69.970772651766083</v>
+        <v>60.835824857688067</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>81.499306306355422</v>
+        <v>70.816082817487143</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.63678499456287</v>
+        <v>27.650070545010067</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>26.809739187681949</v>
+        <v>23.471294320744967</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>25.342973276647452</v>
+        <v>22.201514260473687</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>23.952052324140109</v>
+        <v>20.997393222739927</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17135,7 +17135,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>23.615428128302629</v>
+        <v>20.705977470257771</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>26.538938697660868</v>
+        <v>23.364983859246461</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
-        <v>866779085.10917377</v>
+        <v>865118716.5321629</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -18862,7 +18862,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>783762119.69352126</v>
+        <v>678503300.42159104</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>0.10557193538775511</v>
+        <v>0.10533530085337128</v>
       </c>
       <c r="E14" s="368"/>
       <c r="F14" s="368"/>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>23.615428128302636</v>
+        <v>20.705977470257782</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>25.342973276647452</v>
+        <v>22.201514260473687</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>23.952052324140109</v>
+        <v>20.997393222739927</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>26.809739187681949</v>
+        <v>23.471294320744967</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>25.358142268352882</v>
+        <v>22.214646064981189</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19276,7 +19276,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>23.615428128302629</v>
+        <v>20.705977470257771</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>31.63678499456287</v>
+        <v>27.650070545010067</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19360,7 +19360,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>25.584938697660867</v>
+        <v>22.410983859246461</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>25.580208888730507</v>
+        <v>22.406889261039971</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>3.7330744802016626E-2</v>
+        <v>4.858881056307858E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>10.705085959638616</v>
+        <v>9.3770601324614908</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>12.351475984935202</v>
+        <v>11.023450157758077</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.51723644403086055</v>
+        <v>0.50812288175336162</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21572730031339504</v>
+        <v>0.16748366905435308</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>15.297914307657322</v>
+        <v>13.40012241891314</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>17.349133904345301</v>
+        <v>15.451342015601119</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.32190050914870993</v>
+        <v>0.31054602008353549</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>21.481607885755405</v>
+        <v>18.816694199948998</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>24.031661285541809</v>
+        <v>21.366747599735401</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19728,7 +19728,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>6.0710616917017179E-2</v>
+        <v>4.6594842335769271E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>19.920294213679817</v>
+        <v>17.449070227204992</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>22.348119329440497</v>
+        <v>19.876895342965671</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.12635117927883399</v>
+        <v>0.11291143043551932</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7B0C52-CAD1-4CF2-9622-CC243C6F92F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4394087-8FFE-4606-8B12-9B8F145B6DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>22.410983859246461</v>
+        <v>21.769702959467441</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16748366905435308</v>
+        <v>0.15722159025573346</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>11.023450157758077</v>
+        <v>10.755129516558478</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>15.451342015601119</v>
+        <v>15.067903135098593</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>21.366747599735401</v>
+        <v>20.82831579044063</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>19.876895342965671</v>
+        <v>19.377597519813985</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C126" s="229">
         <f>DCF!C74</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D126" s="230">
         <f>DCF!D74</f>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>27.65 CNY</v>
+        <v>25.98 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C127" s="219">
         <f>DCF!C75</f>
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="D127" s="220">
         <f>DCF!D75</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>23.47 CNY</v>
+        <v>22.2 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="C128" s="219">
         <f>DCF!C76</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D128" s="220">
         <f>DCF!D76</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>22.2 CNY</v>
+        <v>21.59 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>22.410983859246461</v>
+        <v>21.769702959467441</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>9.3770601324614908</v>
+        <v>9.1087394912618915</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>11.023450157758077</v>
+        <v>10.755129516558478</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.50812288175336162</v>
+        <v>0.5059588301878426</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>13.40012241891314</v>
+        <v>13.016683538410614</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>15.451342015601119</v>
+        <v>15.067903135098593</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31054602008353549</v>
+        <v>0.30784985155042266</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>18.816694199948998</v>
+        <v>18.278262390654227</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>21.366747599735401</v>
+        <v>20.82831579044063</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>4.6594842335769271E-2</v>
+        <v>4.3242995587930655E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>17.449070227204992</v>
+        <v>16.949772404053306</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>19.876895342965671</v>
+        <v>19.377597519813985</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.11291143043551932</v>
+        <v>0.1099317532421018</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>22.406889261039971</v>
+        <v>21.770912051292132</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15771,11 +15771,11 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>716918226.4225961</v>
+        <v>702885205.51361799</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>676337949.45527923</v>
+        <v>663099250.48454523</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15793,11 +15793,11 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>757508096.21347773</v>
+        <v>728143270.37605023</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>674179508.91195941</v>
+        <v>648044918.45501077</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15815,11 +15815,11 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>800396048.92221439</v>
+        <v>754308979.66689038</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>672027956.73795664</v>
+        <v>633332364.69274151</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15847,11 +15847,11 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>845712195.46378446</v>
+        <v>781414949.44017541</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
@@ -15859,7 +15859,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>669883270.94997776</v>
+        <v>618953829.81102109</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15879,11 +15879,11 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>893594013.26290524</v>
+        <v>809494967.80250764</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>667745429.63488555</v>
+        <v>604901730.58436942</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>11948637107.043268</v>
+        <v>11714753425.226967</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>8928716732.8487206</v>
+        <v>8753945240.1114845</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>12288890848.53878</v>
+        <v>11922277334.139172</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16575,7 +16575,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>12288890848.53878</v>
+        <v>11922277334.139172</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16587,15 +16587,15 @@
       </c>
       <c r="D55" s="131">
         <f>C76</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E55" s="131">
         <f>C75</f>
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="F55" s="131">
         <f>C74</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -16611,13 +16611,13 @@
         <v>11476376990.788452</v>
       </c>
       <c r="D56" s="123">
+        <v>11818908282.530104</v>
+      </c>
+      <c r="E56" s="123">
         <v>12170500991.837341</v>
       </c>
-      <c r="E56" s="123">
-        <v>12902474596.041143</v>
-      </c>
       <c r="F56" s="123">
-        <v>13091768044.995977</v>
+        <v>12715753999.968578</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16632,13 +16632,13 @@
         <v>11629531547.472206</v>
       </c>
       <c r="D57" s="123">
+        <v>12317647223.512791</v>
+      </c>
+      <c r="E57" s="123">
         <v>13073029883.693321</v>
       </c>
-      <c r="E57" s="123">
-        <v>14819004682.635612</v>
-      </c>
       <c r="F57" s="123">
-        <v>15311359401.95233</v>
+        <v>14350248364.725914</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16653,13 +16653,13 @@
         <v>11832039003.209286</v>
       </c>
       <c r="D58" s="123">
+        <v>13011512513.445005</v>
+      </c>
+      <c r="E58" s="123">
         <v>14396760395.708538</v>
       </c>
-      <c r="E58" s="123">
-        <v>17959516065.284988</v>
-      </c>
       <c r="F58" s="123">
-        <v>19054341354.915714</v>
+        <v>16953815807.281326</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16684,13 +16684,13 @@
         <v>12052525699.760794</v>
       </c>
       <c r="D59" s="123">
+        <v>13808238612.99328</v>
+      </c>
+      <c r="E59" s="123">
         <v>16005181961.221029</v>
       </c>
-      <c r="E59" s="123">
-        <v>22270484521.784805</v>
-      </c>
       <c r="F59" s="123">
-        <v>24359790240.388432</v>
+        <v>20416939448.341022</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16715,13 +16715,13 @@
         <v>12271603836.008841</v>
       </c>
       <c r="D60" s="123">
+        <v>14644622605.031479</v>
+      </c>
+      <c r="E60" s="123">
         <v>17797677148.47332</v>
       </c>
-      <c r="E60" s="123">
-        <v>27750223567.310406</v>
-      </c>
       <c r="F60" s="123">
-        <v>31343196597.909771</v>
+        <v>24671047517.628006</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16746,13 +16746,13 @@
         <v>12477971534.528822</v>
       </c>
       <c r="D61" s="123">
+        <v>15478410848.436249</v>
+      </c>
+      <c r="E61" s="123">
         <v>19700385567.78577</v>
       </c>
-      <c r="E61" s="123">
-        <v>34441519775.775749</v>
-      </c>
       <c r="F61" s="123">
-        <v>40194709338.507645</v>
+        <v>29679464410.002403</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16814,15 +16814,15 @@
       </c>
       <c r="D64" s="132">
         <f>D55</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E64" s="132">
         <f>E55</f>
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="F64" s="132">
         <f>F55</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -16867,15 +16867,15 @@
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>22.201514260473687</v>
+        <v>21.591594163558845</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>23.471294320744967</v>
+        <v>22.201514260473687</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>23.799668247950002</v>
+        <v>23.147383610887051</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16894,15 +16894,15 @@
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>23.767162508054998</v>
+        <v>22.456773944501201</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>26.79596569535655</v>
+        <v>23.767162508054998</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>27.650070545010067</v>
+        <v>25.982797813086581</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16921,15 +16921,15 @@
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>26.063483850349769</v>
+        <v>23.660446187066064</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>32.243919979282985</v>
+        <v>26.063483850349769</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>34.14315147379294</v>
+        <v>30.49929677581132</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16948,15 +16948,15 @@
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>28.853668661207283</v>
+        <v>25.042554652308528</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>39.722306843350587</v>
+        <v>28.853668661207283</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>43.34669811382458</v>
+        <v>36.506897760897282</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16975,15 +16975,15 @@
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>31.963172383518394</v>
+        <v>26.493459042468071</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>49.22820068369878</v>
+        <v>31.963172383518394</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>55.46105591938742</v>
+        <v>43.886646934360321</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17001,15 +17001,15 @@
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>35.263866831347897</v>
+        <v>27.93986049722492</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>60.835824857688067</v>
+        <v>35.263866831347897</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>70.816082817487143</v>
+        <v>52.574921848836851</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="C74" s="142">
         <f>Scenarios!C56</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D74" s="145">
         <f>Scenarios!C55</f>
@@ -17044,7 +17044,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>27.650070545010067</v>
+        <v>25.982797813086581</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17058,7 +17058,7 @@
       </c>
       <c r="C75" s="142">
         <f>Scenarios!C38</f>
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="D75" s="145">
         <f>Scenarios!C37</f>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>23.471294320744967</v>
+        <v>22.201514260473687</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="C76" s="142">
         <f>Scenarios!C26</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D76" s="145">
         <f>Scenarios!C25</f>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>22.201514260473687</v>
+        <v>21.591594163558845</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17398,7 +17398,7 @@
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="H11" s="120"/>
     </row>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>17.278621728474253</v>
+        <v>16.763149965079872</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17453,11 +17453,11 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>581076014.54799867</v>
+        <v>569701981.13480556</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
@@ -17465,7 +17465,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>548184919.38490438</v>
+        <v>537454699.18377876</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17475,11 +17475,11 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>613974884.87913847</v>
+        <v>590174128.61903691</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
@@ -17487,7 +17487,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>546435461.80058599</v>
+        <v>525252873.45944893</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17497,11 +17497,11 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>648736395.62558961</v>
+        <v>611381939.37370527</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>544691587.37211716</v>
+        <v>513328065.5958485</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17519,11 +17519,11 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>685466004.18700838</v>
+        <v>633351849.33807349</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>542953278.28161573</v>
+        <v>501673986.46076941</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17541,11 +17541,11 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>724275138.66091144</v>
+        <v>656111244.4225564</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>541220516.76806271</v>
+        <v>490284489.70407438</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>9684600242.4666443</v>
+        <v>9495033018.9134254</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18125,7 +18125,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>7236896682.1237965</v>
+        <v>7095241025.0161266</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18136,7 +18136,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>9960382445.7310829</v>
+        <v>9663235139.4200478</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18157,7 +18157,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>9960382445.7310829</v>
+        <v>9663235139.4200478</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18169,15 +18169,15 @@
       </c>
       <c r="D50" s="131">
         <f>C71</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E50" s="131">
         <f>C70</f>
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="F50" s="131">
         <f>C69</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H50" s="120"/>
     </row>
@@ -18193,13 +18193,13 @@
         <v>9301824332.9285812</v>
       </c>
       <c r="D51" s="123">
+        <v>9579452534.4829006</v>
+      </c>
+      <c r="E51" s="123">
         <v>9864425189.2971668</v>
       </c>
-      <c r="E51" s="123">
-        <v>10457703877.171345</v>
-      </c>
       <c r="F51" s="123">
-        <v>10611129859.165951</v>
+        <v>10306363241.934212</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18214,13 +18214,13 @@
         <v>9425959047.4995041</v>
       </c>
       <c r="D52" s="123">
+        <v>9983690040.861042</v>
+      </c>
+      <c r="E52" s="123">
         <v>10595942218.946455</v>
       </c>
-      <c r="E52" s="123">
-        <v>12011088382.454086</v>
-      </c>
       <c r="F52" s="123">
-        <v>12410151354.352661</v>
+        <v>11631152368.880617</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18235,13 +18235,13 @@
         <v>9590095236.2014408</v>
       </c>
       <c r="D53" s="123">
+        <v>10546081206.892492</v>
+      </c>
+      <c r="E53" s="123">
         <v>11668851264.787868</v>
       </c>
-      <c r="E53" s="123">
-        <v>14556533275.072603</v>
-      </c>
       <c r="F53" s="123">
-        <v>15443910234.505602</v>
+        <v>13741393868.355684</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18256,13 +18256,13 @@
         <v>9768803945.4670963</v>
       </c>
       <c r="D54" s="123">
+        <v>11191843037.948223</v>
+      </c>
+      <c r="E54" s="123">
         <v>12972507886.359283</v>
       </c>
-      <c r="E54" s="123">
-        <v>18050656143.234207</v>
-      </c>
       <c r="F54" s="123">
-        <v>19744078622.108253</v>
+        <v>16548322202.812235</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18277,13 +18277,13 @@
         <v>9946370989.5089912</v>
       </c>
       <c r="D55" s="123">
+        <v>11869748353.803341</v>
+      </c>
+      <c r="E55" s="123">
         <v>14425359719.548777</v>
       </c>
-      <c r="E55" s="123">
-        <v>22492090058.544006</v>
-      </c>
       <c r="F55" s="123">
-        <v>25404263821.257702</v>
+        <v>19996358633.26091</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18298,13 +18298,13 @@
         <v>10113635979.249605</v>
       </c>
       <c r="D56" s="123">
+        <v>12545549765.454197</v>
+      </c>
+      <c r="E56" s="123">
         <v>15967541497.598978</v>
       </c>
-      <c r="E56" s="123">
-        <v>27915514362.284977</v>
-      </c>
       <c r="F56" s="123">
-        <v>32578585182.416134</v>
+        <v>24055776876.172607</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18336,15 +18336,15 @@
       </c>
       <c r="D59" s="132">
         <f>D50</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E59" s="132">
         <f>E50</f>
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="F59" s="132">
         <f>F50</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H59" s="120"/>
     </row>
@@ -18389,15 +18389,15 @@
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>17.112161339522579</v>
+        <v>16.617809367364611</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>18.141342506329778</v>
+        <v>17.112161339522579</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>18.407495891568583</v>
+        <v>17.878806644613928</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18416,15 +18416,15 @@
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>18.381149364040084</v>
+        <v>17.319054224098313</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>20.836052615293223</v>
+        <v>18.381149364040084</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>21.52832102715842</v>
+        <v>20.17696440303547</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18443,15 +18443,15 @@
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>20.242361988470723</v>
+        <v>18.294653732875986</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>25.251724369853438</v>
+        <v>20.242361988470723</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>26.791088033462344</v>
+        <v>23.837673700476678</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18470,15 +18470,15 @@
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>22.503860455089075</v>
+        <v>19.414879232879855</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>31.313100791965763</v>
+        <v>22.503860455089075</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>34.250739642520173</v>
+        <v>28.706949872778431</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18497,15 +18497,15 @@
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>25.024173042479799</v>
+        <v>20.59086515352115</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>39.017810623418583</v>
+        <v>25.024173042479799</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>44.069659699262395</v>
+        <v>34.688378549069419</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18523,15 +18523,15 @@
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>27.699449391019588</v>
+        <v>21.763201358391342</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>48.426013323257372</v>
+        <v>27.699449391019588</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>56.515204399315358</v>
+        <v>41.730392511796381</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="C69" s="142">
         <f>Scenarios!C56</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D69" s="145">
         <f>Scenarios!C55</f>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>21.52832102715842</v>
+        <v>20.17696440303547</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="C70" s="142">
         <f>Scenarios!C38</f>
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="D70" s="145">
         <f>Scenarios!C37</f>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>18.141342506329778</v>
+        <v>17.112161339522579</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18603,7 +18603,7 @@
       </c>
       <c r="C71" s="142">
         <f>Scenarios!C26</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D71" s="145">
         <f>Scenarios!C25</f>
@@ -18611,7 +18611,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>17.112161339522579</v>
+        <v>16.617809367364611</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>23.364983859246461</v>
+        <v>22.723702959467442</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -19047,7 +19047,7 @@
         <v>133</v>
       </c>
       <c r="C26" s="164">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
       <c r="E26" s="367"/>
@@ -19059,7 +19059,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>22.201514260473687</v>
+        <v>21.591594163558845</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -19163,7 +19163,7 @@
         <v>133</v>
       </c>
       <c r="C38" s="164">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
       <c r="E38" s="367"/>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>23.471294320744967</v>
+        <v>22.201514260473687</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>22.214646064981189</v>
+        <v>21.594737994778029</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19322,7 +19322,7 @@
         <v>133</v>
       </c>
       <c r="C56" s="164">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
       <c r="E56" s="367"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>27.650070545010067</v>
+        <v>25.982797813086581</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19360,7 +19360,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>22.410983859246461</v>
+        <v>21.769702959467441</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19409,7 +19409,7 @@
         <v>133</v>
       </c>
       <c r="C65" s="151">
-        <v>5.6617154223326201E-2</v>
+        <v>3.5934836391919057E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>22.406889261039971</v>
+        <v>21.770912051292132</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>4.858881056307858E-2</v>
+        <v>5.0020115170913503E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>9.3770601324614908</v>
+        <v>9.1087394912618915</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>11.023450157758077</v>
+        <v>10.755129516558478</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.50812288175336162</v>
+        <v>0.5059588301878426</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16748366905435308</v>
+        <v>0.15722159025573346</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>13.40012241891314</v>
+        <v>13.016683538410614</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>15.451342015601119</v>
+        <v>15.067903135098593</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.31054602008353549</v>
+        <v>0.30784985155042266</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>18.816694199948998</v>
+        <v>18.278262390654227</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>21.366747599735401</v>
+        <v>20.82831579044063</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19728,7 +19728,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>4.6594842335769271E-2</v>
+        <v>4.3242995587930655E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>17.449070227204992</v>
+        <v>16.949772404053306</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>19.876895342965671</v>
+        <v>19.377597519813985</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.11291143043551932</v>
+        <v>0.1099317532421018</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4394087-8FFE-4606-8B12-9B8F145B6DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EAE89D-DABD-43E7-97CF-3BA7557ACF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>16.2</v>
+        <v>15</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>9338.6034</v>
+        <v>8646.8549999999996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15722159025573346</v>
+        <v>0.18888383193830616</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.2655757114772762E-2</v>
+        <v>7.846821768395458E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>5.8888888888888893E-2</v>
+        <v>6.3600000000000004E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>5.8888888888888893E-2</v>
+        <v>6.3600000000000004E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>5.8888888888888893E-2</v>
+        <v>6.3600000000000004E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>5.8888888888888893E-2</v>
+        <v>6.3600000000000004E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.5555555555555559E-2</v>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.2655757114772762E-2</v>
+        <v>7.846821768395458E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.2638982455573907E-2</v>
+        <v>0.10005010105201982</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.10569581372455814</v>
+        <v>0.11415147882252279</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.962469878782732E-2</v>
+        <v>9.6794674690853497E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.8598031845796381E-2</v>
+        <v>7.408587439346008E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>5.5963294073401545E-2</v>
+        <v>6.0440357599273666E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.4256217962445936E-2</v>
+        <v>4.7796715399441608E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6411418863767147E-2</v>
+        <v>2.8524332372868517E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.0657976866219632E-2</v>
+        <v>2.2310615015517201E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.0554946363821384E-2</v>
+        <v>2.2199342072927095E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.1164773310750087E-2</v>
+        <v>2.2857955175610092E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0830625808565768E-2</v>
+        <v>9.8097075873251033E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10794863169796888</v>
+        <v>0.1165845222338064</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9298006809026706E-2</v>
+        <v>9.6441847353748847E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9282960019482143E-2</v>
+        <v>7.4825596821040716E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5113440945570087E-2</v>
+        <v>5.9522516221215689E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4233268327895793E-2</v>
+        <v>4.7771929794127463E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6179046858334297E-2</v>
+        <v>2.8273370607001042E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2054336625967005E-2</v>
+        <v>2.3818683556044364E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7105872597609189E-2</v>
+        <v>1.8474342405417923E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5271199866995102E-2</v>
+        <v>1.649289585635471E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-16.2</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>16.2</v>
+        <v>15</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>16.2</v>
+        <v>15</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15722159025573346</v>
+        <v>0.18888383193830616</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EAE89D-DABD-43E7-97CF-3BA7557ACF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EA1BEC-521F-4CB4-B4EE-CB5D728B5256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>15</v>
+        <v>14.93</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8646.8549999999996</v>
+        <v>8606.5030100000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18888383193830616</v>
+        <v>0.19083819809107139</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.846821768395458E-2</v>
+        <v>7.8836119575306007E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.3600000000000004E-2</v>
+        <v>6.3898191560616213E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.3600000000000004E-2</v>
+        <v>6.3898191560616213E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.3600000000000004E-2</v>
+        <v>6.3898191560616213E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.3600000000000004E-2</v>
+        <v>6.3898191560616213E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0000000000000005E-2</v>
+        <v>6.0281312793034163E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.846821768395458E-2</v>
+        <v>7.8836119575306007E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10005010105201982</v>
+        <v>0.10051919060819138</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11415147882252279</v>
+        <v>0.11468668334479851</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.6794674690853497E-2</v>
+        <v>9.7248501028988785E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.408587439346008E-2</v>
+        <v>7.4433229464293454E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.0440357599273666E-2</v>
+        <v>6.0723735029410919E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.7796715399441608E-2</v>
+        <v>4.80208125245562E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.8524332372868517E-2</v>
+        <v>2.8658070033022624E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2310615015517201E-2</v>
+        <v>2.2415219372589286E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2199342072927095E-2</v>
+        <v>2.2303424721628023E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.2857955175610092E-2</v>
+        <v>2.2965125762501769E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8097075873251033E-2</v>
+        <v>9.85570085799575E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1165845222338064</v>
+        <v>0.11713113419337548</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6441847353748847E-2</v>
+        <v>9.6894019444489804E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4825596821040716E-2</v>
+        <v>7.5176420114910297E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9522516221215689E-2</v>
+        <v>5.9801590309325879E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7771929794127463E-2</v>
+        <v>4.7995910710777759E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8273370607001042E-2</v>
+        <v>2.8405931621233466E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3818683556044364E-2</v>
+        <v>2.3930358562670159E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8474342405417923E-2</v>
+        <v>1.8560960219776882E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.649289585635471E-2</v>
+        <v>1.6570223566330922E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-15</v>
+        <v>-14.93</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>15</v>
+        <v>14.93</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>15</v>
+        <v>14.93</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18888383193830616</v>
+        <v>0.19083819809107139</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EA1BEC-521F-4CB4-B4EE-CB5D728B5256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6903A0F-09C6-4BC3-A831-387034A163DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.93</v>
+        <v>14.67</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8606.5030100000004</v>
+        <v>8456.6241900000005</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19083819809107139</v>
+        <v>0.19820951651537744</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.8836119575306007E-2</v>
+        <v>8.0233351415086474E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.3898191560616213E-2</v>
+        <v>6.5030674846625766E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.3898191560616213E-2</v>
+        <v>6.5030674846625766E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.3898191560616213E-2</v>
+        <v>6.5030674846625766E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.3898191560616213E-2</v>
+        <v>6.5030674846625766E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0281312793034163E-2</v>
+        <v>6.1349693251533742E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8836119575306007E-2</v>
+        <v>8.0233351415086474E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10051919060819138</v>
+        <v>0.10230071682210616</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11468668334479851</v>
+        <v>0.11671930349951205</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.7248501028988785E-2</v>
+        <v>9.8972060011097651E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.4433229464293454E-2</v>
+        <v>7.5752427805173911E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.0723735029410919E-2</v>
+        <v>6.1799956645474094E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.80208125245562E-2</v>
+        <v>4.8871897136443361E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.8658070033022624E-2</v>
+        <v>2.9165984021337955E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2415219372589286E-2</v>
+        <v>2.2812489790917385E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2303424721628023E-2</v>
+        <v>2.2698713775999073E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.2965125762501769E-2</v>
+        <v>2.3372142306349788E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.85570085799575E-2</v>
+        <v>0.10030375856160637</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11713113419337548</v>
+        <v>0.1192070779486773</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6894019444489804E-2</v>
+        <v>9.861129586272889E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5176420114910297E-2</v>
+        <v>7.6508790205563101E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9801590309325879E-2</v>
+        <v>6.0861468528850396E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7995910710777759E-2</v>
+        <v>4.8846553981725417E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8405931621233466E-2</v>
+        <v>2.8909376898774073E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3930358562670159E-2</v>
+        <v>2.4354482163644546E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8560960219776882E-2</v>
+        <v>1.8889920659936527E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6570223566330922E-2</v>
+        <v>1.6863901693614222E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.93</v>
+        <v>-14.67</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.93</v>
+        <v>14.67</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.93</v>
+        <v>14.67</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19083819809107139</v>
+        <v>0.19820951651537744</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6903A0F-09C6-4BC3-A831-387034A163DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5EC68E-0588-4747-9C82-6D4E23F8F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.67</v>
+        <v>14.51</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8456.6241900000005</v>
+        <v>8364.3910699999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19820951651537744</v>
+        <v>0.20283599107840344</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.0233351415086474E-2</v>
+        <v>8.1118074793888259E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.5030674846625766E-2</v>
+        <v>6.574776016540318E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.5030674846625766E-2</v>
+        <v>6.574776016540318E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.5030674846625766E-2</v>
+        <v>6.574776016540318E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.5030674846625766E-2</v>
+        <v>6.574776016540318E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.1349693251533742E-2</v>
+        <v>6.202618883528601E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0233351415086474E-2</v>
+        <v>8.1118074793888259E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10230071682210616</v>
+        <v>0.10342877434736715</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11671930349951205</v>
+        <v>0.11800635302121583</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.8972060011097651E-2</v>
+        <v>0.10006341284374931</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.5752427805173911E-2</v>
+        <v>7.6587740585933928E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.1799956645474094E-2</v>
+        <v>6.2481417228746033E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.8871897136443361E-2</v>
+        <v>4.9410801584536465E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.9165984021337955E-2</v>
+        <v>2.9487593769333409E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2812489790917385E-2</v>
+        <v>2.3064040333063959E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2698713775999073E-2</v>
+        <v>2.2949009723908093E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.3372142306349788E-2</v>
+        <v>2.3629864068514913E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10030375856160637</v>
+        <v>0.10140979587172745</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1192070779486773</v>
+        <v>0.12052155985576127</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.861129586272889E-2</v>
+        <v>9.9698670593124247E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6508790205563101E-2</v>
+        <v>7.735244330224747E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0861468528850396E-2</v>
+        <v>6.1532580518141651E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8846553981725417E-2</v>
+        <v>4.9385178973942928E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8909376898774073E-2</v>
+        <v>2.9228157071331196E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4354482163644546E-2</v>
+        <v>2.462303606758549E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8889920659936527E-2</v>
+        <v>1.9098217510769736E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6863901693614222E-2</v>
+        <v>1.7049857880449389E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.67</v>
+        <v>-14.51</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.67</v>
+        <v>14.51</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.67</v>
+        <v>14.51</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19820951651537744</v>
+        <v>0.20283599107840344</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5EC68E-0588-4747-9C82-6D4E23F8F9C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF1087C-7D40-41F0-B21A-8A31DDB5C8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.51</v>
+        <v>14.74</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8364.3910699999997</v>
+        <v>8496.9761799999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.20283599107840344</v>
+        <v>0.196207286361328</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>8.1118074793888259E-2</v>
+        <v>7.9852324644458517E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.574776016540318E-2</v>
+        <v>6.4721845318860244E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.574776016540318E-2</v>
+        <v>6.4721845318860244E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.574776016540318E-2</v>
+        <v>6.4721845318860244E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.574776016540318E-2</v>
+        <v>6.4721845318860244E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.202618883528601E-2</v>
+        <v>6.1058344640434192E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.1118074793888259E-2</v>
+        <v>7.9852324644458517E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10342877434736715</v>
+        <v>0.10181489252240823</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11800635302121583</v>
+        <v>0.11616500558601368</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>0.10006341284374931</v>
+        <v>9.8502043443880763E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.6587740585933928E-2</v>
+        <v>7.5392680861730066E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.2481417228746033E-2</v>
+        <v>6.1506469741458951E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.9410801584536465E-2</v>
+        <v>4.8639805358997562E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.9487593769333409E-2</v>
+        <v>2.9027475277681666E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3064040333063959E-2</v>
+        <v>2.2704153679291589E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2949009723908093E-2</v>
+        <v>2.2590917984661223E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.3629864068514913E-2</v>
+        <v>2.3261148414799961E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10140979587172745</v>
+        <v>9.9827417781463049E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.12052155985576127</v>
+        <v>0.1186409656382019</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9698670593124247E-2</v>
+        <v>9.8142992558089059E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.735244330224747E-2</v>
+        <v>7.6145451310421344E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1532580518141651E-2</v>
+        <v>6.0572438488347043E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9385178973942928E-2</v>
+        <v>4.8614582558474347E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.9228157071331196E-2</v>
+        <v>2.8772086777816529E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.462303606758549E-2</v>
+        <v>2.4238823157439991E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9098217510769736E-2</v>
+        <v>1.880021275992326E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7049857880449389E-2</v>
+        <v>1.6783815321934913E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.51</v>
+        <v>-14.74</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.51</v>
+        <v>14.74</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.51</v>
+        <v>14.74</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.20283599107840344</v>
+        <v>0.196207286361328</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF1087C-7D40-41F0-B21A-8A31DDB5C8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6E9C9E-ADF1-4E40-A281-D7AEF7BF7A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.74</v>
+        <v>14.89</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8496.9761799999997</v>
+        <v>8583.4447299999993</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.196207286361328</v>
+        <v>0.19196066679108825</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.9852324644458517E-2</v>
+        <v>7.9047902300827311E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.4721845318860244E-2</v>
+        <v>6.4069845533915384E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.4721845318860244E-2</v>
+        <v>6.4069845533915384E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.4721845318860244E-2</v>
+        <v>6.4069845533915384E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.4721845318860244E-2</v>
+        <v>6.4069845533915384E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.1058344640434192E-2</v>
+        <v>6.044325050369375E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9852324644458517E-2</v>
+        <v>7.9047902300827311E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10181489252240823</v>
+        <v>0.10078922201345179</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11616500558601368</v>
+        <v>0.11499477383061395</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.8502043443880763E-2</v>
+        <v>9.7509746162713393E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.5392680861730066E-2</v>
+        <v>7.4633184412484968E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.1506469741458951E-2</v>
+        <v>6.0886861248428806E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.8639805358997562E-2</v>
+        <v>4.8149814035703432E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.9027475277681666E-2</v>
+        <v>2.8735056117731885E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2704153679291589E-2</v>
+        <v>2.2475434871239625E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2590917984661223E-2</v>
+        <v>2.2363339898852006E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.3261148414799961E-2</v>
+        <v>2.3026818511360066E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9827417781463049E-2</v>
+        <v>9.8821768844779403E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1186409656382019</v>
+        <v>0.11744579137052356</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8142992558089059E-2</v>
+        <v>9.7154312310693935E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6145451310421344E-2</v>
+        <v>7.5378371545709241E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0572438488347043E-2</v>
+        <v>5.996223930948525E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8614582558474347E-2</v>
+        <v>4.8124845326521955E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8772086777816529E-2</v>
+        <v>2.8482240369712267E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4238823157439991E-2</v>
+        <v>2.399464428077001E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.880021275992326E-2</v>
+        <v>1.8610821765028131E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6783815321934913E-2</v>
+        <v>1.6614737262949673E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.74</v>
+        <v>-14.89</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.74</v>
+        <v>14.89</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.74</v>
+        <v>14.89</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.196207286361328</v>
+        <v>0.19196066679108825</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6E9C9E-ADF1-4E40-A281-D7AEF7BF7A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A594DD4-8E8E-4C53-AA20-149551C86167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.89</v>
+        <v>14.87</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8583.4447299999993</v>
+        <v>8571.9155900000005</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19196066679108825</v>
+        <v>0.19252346326877756</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.9047902300827311E-2</v>
+        <v>7.9154220932032185E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.4069845533915384E-2</v>
+        <v>6.4156018829858788E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.4069845533915384E-2</v>
+        <v>6.4156018829858788E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.4069845533915384E-2</v>
+        <v>6.4156018829858788E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.4069845533915384E-2</v>
+        <v>6.4156018829858788E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.044325050369375E-2</v>
+        <v>6.052454606590451E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9047902300827311E-2</v>
+        <v>7.9154220932032185E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10078922201345179</v>
+        <v>0.10092478250035625</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11499477383061395</v>
+        <v>0.11514944064141505</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.7509746162713393E-2</v>
+        <v>9.7640895787680065E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.4633184412484968E-2</v>
+        <v>7.4733565292663173E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.0886861248428806E-2</v>
+        <v>6.0968753462616342E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.8149814035703432E-2</v>
+        <v>4.8214575049873851E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.8735056117731885E-2</v>
+        <v>2.8773704478347532E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2475434871239625E-2</v>
+        <v>2.2505664104422195E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2363339898852006E-2</v>
+        <v>2.2393418365427468E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.3026818511360066E-2</v>
+        <v>2.3057789349976557E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8821768844779403E-2</v>
+        <v>9.8954683127018522E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11744579137052356</v>
+        <v>0.11760375477519139</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7154312310693935E-2</v>
+        <v>9.7284983880715048E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5378371545709241E-2</v>
+        <v>7.5479754695064613E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.996223930948525E-2</v>
+        <v>6.0042887916491955E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8124845326521955E-2</v>
+        <v>4.8189572758030388E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8482240369712267E-2</v>
+        <v>2.8520548695697083E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.399464428077001E-2</v>
+        <v>2.4026916835283491E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8610821765028131E-2</v>
+        <v>1.8635853132566837E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6614737262949673E-2</v>
+        <v>1.6637083916968436E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.89</v>
+        <v>-14.87</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.89</v>
+        <v>14.87</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.89</v>
+        <v>14.87</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19196066679108825</v>
+        <v>0.19252346326877756</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A594DD4-8E8E-4C53-AA20-149551C86167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D97A475-39DD-468E-9176-D14DF445BF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.87</v>
+        <v>15.02</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8571.9155900000005</v>
+        <v>8658.3841400000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19252346326877756</v>
+        <v>0.18832775240825339</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.9154220932032185E-2</v>
+        <v>7.8363732707011899E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.4156018829858788E-2</v>
+        <v>6.3515312916111857E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.4156018829858788E-2</v>
+        <v>6.3515312916111857E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.4156018829858788E-2</v>
+        <v>6.3515312916111857E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.4156018829858788E-2</v>
+        <v>6.3515312916111857E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.052454606590451E-2</v>
+        <v>5.9920106524633823E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9154220932032185E-2</v>
+        <v>7.8363732707011899E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10092478250035625</v>
+        <v>9.9916878547290103E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11514944064141505</v>
+        <v>0.11399947951650079</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.7640895787680065E-2</v>
+        <v>9.666578697488698E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.4733565292663173E-2</v>
+        <v>7.3987224760446155E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.0968753462616342E-2</v>
+        <v>6.0359877762257326E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.8214575049873851E-2</v>
+        <v>4.7733071304369115E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.8773704478347532E-2</v>
+        <v>2.8486350572105711E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2505664104422195E-2</v>
+        <v>2.2280907139331427E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2393418365427468E-2</v>
+        <v>2.2169782363109614E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.3057789349976557E-2</v>
+        <v>2.2827518484297697E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8954683127018522E-2</v>
+        <v>9.796645393467146E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11760375477519139</v>
+        <v>0.11642928318955366</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7284983880715048E-2</v>
+        <v>9.6313429447818427E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5479754695064613E-2</v>
+        <v>7.4725962204767696E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0042887916491955E-2</v>
+        <v>5.9443258543158149E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8189572758030388E-2</v>
+        <v>4.7708318702524094E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8520548695697083E-2</v>
+        <v>2.8235722976365889E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4026916835283491E-2</v>
+        <v>2.3786967599245371E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8635853132566837E-2</v>
+        <v>1.8449742748420029E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6637083916968436E-2</v>
+        <v>1.6470934610207766E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.87</v>
+        <v>-15.02</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.87</v>
+        <v>15.02</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.87</v>
+        <v>15.02</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19252346326877756</v>
+        <v>0.18832775240825339</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D97A475-39DD-468E-9176-D14DF445BF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A4A392-2FC3-4CAA-A676-64609ABEEBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>15.02</v>
+        <v>14.86</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8658.3841400000001</v>
+        <v>8566.1510199999993</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18832775240825339</v>
+        <v>0.19280525351101208</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>10.755129516558478</v>
+        <v>10.465993175620561</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4525,7 +4525,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>15.067903135098593</v>
+        <v>13.008295915247331</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4544,7 +4544,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.8363732707011899E-2</v>
+        <v>7.9207487567921842E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.3515312916111857E-2</v>
+        <v>6.41991924629879E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.6463900252965868</v>
+        <v>1.6178692272519435</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>9.1087394912618915</v>
+        <v>8.8481239483686167</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>10.755129516558478</v>
+        <v>10.465993175620561</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5059588301878426</v>
+        <v>0.5192404234863941</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.0512195966879787</v>
+        <v>1.8622080000000001</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>13.016683538410614</v>
+        <v>11.14608791524733</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>15.067903135098593</v>
+        <v>13.008295915247331</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.30784985155042266</v>
+        <v>0.4024587317765792</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.3515312916111857E-2</v>
+        <v>6.41991924629879E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.3515312916111857E-2</v>
+        <v>6.41991924629879E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.3515312916111857E-2</v>
+        <v>6.41991924629879E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>5.9920106524633823E-2</v>
+        <v>6.0565275908479141E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8363732707011899E-2</v>
+        <v>7.9207487567921842E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>9.9916878547290103E-2</v>
+        <v>0.10099269958144666</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11399947951650079</v>
+        <v>0.11522693017078343</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.666578697488698E-2</v>
+        <v>9.770660298538375E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.3987224760446155E-2</v>
+        <v>7.4783857059347328E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.0359877762257326E-2</v>
+        <v>6.1009782233452554E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.7733071304369115E-2</v>
+        <v>4.8247020928103915E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.8486350572105711E-2</v>
+        <v>2.8793067671132423E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2280907139331427E-2</v>
+        <v>2.2520809235044282E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2169782363109614E-2</v>
+        <v>2.2408487960558977E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.2827518484297697E-2</v>
+        <v>2.3073306031907902E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.796645393467146E-2</v>
+        <v>9.902127443464101E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11642928318955366</v>
+        <v>0.11768289592914508</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6313429447818427E-2</v>
+        <v>9.7350451568387134E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4725962204767696E-2</v>
+        <v>7.5530548608049169E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9443258543158149E-2</v>
+        <v>6.0083293628414226E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7708318702524094E-2</v>
+        <v>4.822200181103041E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8235722976365889E-2</v>
+        <v>2.8539741527928375E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3786967599245371E-2</v>
+        <v>2.4043085689143033E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8449742748420029E-2</v>
+        <v>1.8648394083530879E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6470934610207766E-2</v>
+        <v>1.6648279801165587E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-15.02</v>
+        <v>-14.86</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>15.02</v>
+        <v>14.86</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6463900252965868</v>
+        <v>1.6178692272519435</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19557,7 +19557,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>9.1087394912618915</v>
+        <v>8.8481239483686167</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>10.755129516558478</v>
+        <v>10.465993175620561</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.5059588301878426</v>
+        <v>0.5192404234863941</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>15.02</v>
+        <v>14.86</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18832775240825339</v>
+        <v>0.19280525351101208</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.0512195966879787</v>
+        <v>1.8622080000000001</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>13.016683538410614</v>
+        <v>11.14608791524733</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>15.067903135098593</v>
+        <v>13.008295915247331</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.30784985155042266</v>
+        <v>0.4024587317765792</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A4A392-2FC3-4CAA-A676-64609ABEEBC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCCDACE-B771-47B3-A328-5BA8E3272B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.86</v>
+        <v>14.76</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8566.1510199999993</v>
+        <v>8508.5053200000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19280525351101208</v>
+        <v>0.19563763057598882</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.9207487567921842E-2</v>
+        <v>7.9744123662555469E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.41991924629879E-2</v>
+        <v>6.4634146341463417E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.41991924629879E-2</v>
+        <v>6.4634146341463417E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.41991924629879E-2</v>
+        <v>6.4634146341463417E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.41991924629879E-2</v>
+        <v>6.4634146341463417E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0565275908479141E-2</v>
+        <v>6.0975609756097567E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9207487567921842E-2</v>
+        <v>7.9744123662555469E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10099269958144666</v>
+        <v>0.10167693196343477</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11522693017078343</v>
+        <v>0.11600760042939308</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.770660298538375E-2</v>
+        <v>9.8368571840298277E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.4783857059347328E-2</v>
+        <v>7.5290522757581385E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.1009782233452554E-2</v>
+        <v>6.1423127641538275E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.8247020928103915E-2</v>
+        <v>4.8573897763660168E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.8793067671132423E-2</v>
+        <v>2.8988142655354186E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2520809235044282E-2</v>
+        <v>2.2673389243411793E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2408487960558977E-2</v>
+        <v>2.2560306984682005E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.3073306031907902E-2</v>
+        <v>2.3229629243506193E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.902127443464101E-2</v>
+        <v>9.9692150277694139E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11768289592914508</v>
+        <v>0.11848020552216097</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7350451568387134E-2</v>
+        <v>9.8010007473322003E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5530548608049169E-2</v>
+        <v>7.604227319211454E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0083293628414226E-2</v>
+        <v>6.0490362013430582E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.822200181103041E-2</v>
+        <v>4.8548709140373437E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8539741527928375E-2</v>
+        <v>2.8733100210366912E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4043085689143033E-2</v>
+        <v>2.4205979223622321E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8648394083530879E-2</v>
+        <v>1.8774738216888135E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6648279801165587E-2</v>
+        <v>1.676107302475072E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.86</v>
+        <v>-14.76</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.86</v>
+        <v>14.76</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.86</v>
+        <v>14.76</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19280525351101208</v>
+        <v>0.19563763057598882</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCCDACE-B771-47B3-A328-5BA8E3272B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2B9147-9B22-44F1-92EB-936394779332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.76</v>
+        <v>14.93</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8508.5053200000002</v>
+        <v>8606.5030100000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19563763057598882</v>
+        <v>0.19083819809107139</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.9744123662555469E-2</v>
+        <v>7.8836119575306007E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.4634146341463417E-2</v>
+        <v>6.3898191560616213E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13515,20 +13515,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.4634146341463417E-2</v>
+        <v>6.3898191560616213E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.4634146341463417E-2</v>
+        <v>6.3898191560616213E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.4634146341463417E-2</v>
+        <v>6.3898191560616213E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0975609756097567E-2</v>
+        <v>6.0281312793034163E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14714,50 +14714,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9744123662555469E-2</v>
+        <v>7.8836119575306007E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10167693196343477</v>
+        <v>0.10051919060819138</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11600760042939308</v>
+        <v>0.11468668334479851</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.8368571840298277E-2</v>
+        <v>9.7248501028988785E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.5290522757581385E-2</v>
+        <v>7.4433229464293454E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.1423127641538275E-2</v>
+        <v>6.0723735029410919E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.8573897763660168E-2</v>
+        <v>4.80208125245562E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.8988142655354186E-2</v>
+        <v>2.8658070033022624E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2673389243411793E-2</v>
+        <v>2.2415219372589286E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2560306984682005E-2</v>
+        <v>2.2303424721628023E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.3229629243506193E-2</v>
+        <v>2.2965125762501769E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14771,43 +14771,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9692150277694139E-2</v>
+        <v>9.85570085799575E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11848020552216097</v>
+        <v>0.11713113419337548</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8010007473322003E-2</v>
+        <v>9.6894019444489804E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.604227319211454E-2</v>
+        <v>7.5176420114910297E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0490362013430582E-2</v>
+        <v>5.9801590309325879E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8548709140373437E-2</v>
+        <v>4.7995910710777759E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8733100210366912E-2</v>
+        <v>2.8405931621233466E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4205979223622321E-2</v>
+        <v>2.3930358562670159E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8774738216888135E-2</v>
+        <v>1.8560960219776882E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.676107302475072E-2</v>
+        <v>1.6570223566330922E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.76</v>
+        <v>-14.93</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.76</v>
+        <v>14.93</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.76</v>
+        <v>14.93</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19563763057598882</v>
+        <v>0.19083819809107139</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2B9147-9B22-44F1-92EB-936394779332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830E65A2-045C-4D27-8DE1-627DB56F9F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>CN</t>
@@ -3896,29 +3900,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4240,13 +4244,13 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4277,7 +4281,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4324,10 +4328,10 @@
         <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4394,13 +4398,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4421,7 +4425,7 @@
         <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4429,7 +4433,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4442,7 +4446,7 @@
         <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4450,7 +4454,7 @@
         <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -4600,22 +4604,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4631,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4657,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4692,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4714,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4784,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4806,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4828,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4974,22 +4978,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5037,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5085,13 +5089,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5108,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5232,13 +5236,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5277,13 +5281,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5426,13 +5430,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5449,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5779,7 +5783,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.1099317532421018</v>
+        <v>0.10993175324210214</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5797,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5840,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5854,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5893,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5909,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6642,7 +6646,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12811,7 +12815,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -15716,7 +15720,7 @@
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -15736,7 +15740,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>21.770912051292132</v>
+        <v>21.770912051292139</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15771,11 +15775,11 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>702885205.51361799</v>
+        <v>702885205.51361811</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15783,7 +15787,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>663099250.48454523</v>
+        <v>663099250.48454535</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15793,11 +15797,11 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>728143270.37605023</v>
+        <v>728143270.37605047</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
@@ -15805,7 +15809,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>648044918.45501077</v>
+        <v>648044918.45501101</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15815,11 +15819,11 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>754308979.66689038</v>
+        <v>754308979.66689074</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
@@ -15827,7 +15831,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>633332364.69274151</v>
+        <v>633332364.69274175</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15847,11 +15851,11 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>781414949.44017541</v>
+        <v>781414949.44017601</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
@@ -15859,7 +15863,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>618953829.81102109</v>
+        <v>618953829.81102157</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15879,11 +15883,11 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>809494967.80250764</v>
+        <v>809494967.80250847</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
@@ -15891,7 +15895,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>604901730.58436942</v>
+        <v>604901730.58437002</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16531,7 +16535,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>11714753425.226967</v>
+        <v>11714753425.226969</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16543,7 +16547,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>8753945240.1114845</v>
+        <v>8753945240.1114864</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16554,7 +16558,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>11922277334.139172</v>
+        <v>11922277334.139175</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16575,7 +16579,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>11922277334.139172</v>
+        <v>11922277334.139175</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -17398,7 +17402,7 @@
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="H11" s="120"/>
     </row>
@@ -17418,7 +17422,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>16.763149965079872</v>
+        <v>16.763149965079879</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17453,11 +17457,11 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>569701981.13480556</v>
+        <v>569701981.13480568</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
@@ -17465,7 +17469,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>537454699.18377876</v>
+        <v>537454699.18377888</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17475,11 +17479,11 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>590174128.61903691</v>
+        <v>590174128.61903715</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
@@ -17487,7 +17491,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>525252873.45944893</v>
+        <v>525252873.45944917</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17497,11 +17501,11 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>611381939.37370527</v>
+        <v>611381939.37370574</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
@@ -17509,7 +17513,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>513328065.5958485</v>
+        <v>513328065.59584892</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17519,11 +17523,11 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>633351849.33807349</v>
+        <v>633351849.33807409</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
@@ -17531,7 +17535,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>501673986.46076941</v>
+        <v>501673986.46076989</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17541,11 +17545,11 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>656111244.4225564</v>
+        <v>656111244.42255723</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
@@ -17553,7 +17557,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>490284489.70407438</v>
+        <v>490284489.70407498</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18113,7 +18117,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>9495033018.9134254</v>
+        <v>9495033018.9134293</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18125,7 +18129,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>7095241025.0161266</v>
+        <v>7095241025.0161295</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18136,7 +18140,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>9663235139.4200478</v>
+        <v>9663235139.4200516</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18157,7 +18161,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>9663235139.4200478</v>
+        <v>9663235139.4200516</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -19409,7 +19413,7 @@
         <v>133</v>
       </c>
       <c r="C65" s="151">
-        <v>3.5934836391919057E-2</v>
+        <v>3.5934836391919099E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
@@ -19422,7 +19426,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>21.770912051292132</v>
+        <v>21.770912051292139</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19784,7 +19788,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.1099317532421018</v>
+        <v>0.10993175324210214</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19834,4 +19838,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830E65A2-045C-4D27-8DE1-627DB56F9F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98693623-C39C-4C41-AEE6-B1562C0D5668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2504,7 +2517,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2944,6 +2957,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3147,11 +3166,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3936,9 +3956,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{0387460B-B4E6-4B1C-A60A-A789B5B2569B}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4023,6 +4049,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>576457000</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>14.93</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19841,22 +19950,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6250F0AA-52FB-4191-8409-8BDDA69B8C32}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98693623-C39C-4C41-AEE6-B1562C0D5668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D346785-C700-40F1-A4DB-8403DF5D56D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3920,47 +3920,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4449,7 +4449,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.93</v>
+        <v>14.94</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8606.5030100000004</v>
+        <v>8612.2675799999997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4507,13 +4507,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4589,14 +4589,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>21.769702959467441</v>
+        <v>17.692199895960851</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19083819809107139</v>
+        <v>0.11852527700395354</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>10.465993175620561</v>
+        <v>7.2279420709207756</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4638,7 +4638,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>13.008295915247331</v>
+        <v>9.7854619462725747</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4657,7 +4657,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>20.82831579044063</v>
+        <v>16.722424859968235</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4676,7 +4676,7 @@
         <v>433</v>
       </c>
       <c r="F31" s="312">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>19.377597519813985</v>
+        <v>16.202875796143875</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4713,13 +4713,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4740,13 +4740,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4766,13 +4766,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4801,13 +4801,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4823,13 +4823,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4893,13 +4893,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4915,13 +4915,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4937,22 +4937,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.8836119575306007E-2</v>
+        <v>7.8783351088307807E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.3898191560616213E-2</v>
+        <v>6.3855421686746988E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -5087,13 +5087,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5146,22 +5146,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>19.617054420988644</v>
+        <v>15.693643536790917</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5198,13 +5198,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5217,13 +5217,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5345,13 +5345,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>20.705977470257782</v>
+        <v>16.782566586060053</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5390,13 +5390,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>25.98 CNY</v>
+        <v>21.39 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>22.2 CNY</v>
+        <v>18.05 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>21.59 CNY</v>
+        <v>17.53 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>21 CNY</v>
+        <v>17.03 CNY</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>20.71 CNY</v>
+        <v>16.78 CNY</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>21.769702959467441</v>
+        <v>17.692199895960851</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5539,13 +5539,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5558,22 +5558,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>1.6178692272519435</v>
+        <v>1.4246045348312761</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>8.8481239483686167</v>
+        <v>5.8033375360894999</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>10.465993175620561</v>
+        <v>7.2279420709207756</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5192404234863941</v>
+        <v>0.59146165465997691</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>1.8622080000000001</v>
+        <v>1.7325716886663638</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>11.14608791524733</v>
+        <v>8.0528902576062116</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>13.008295915247331</v>
+        <v>9.7854619462725747</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.4024587317765792</v>
+        <v>0.44690530268615114</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>2.5500533997864046</v>
+        <v>2.4809015558378498</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>18.278262390654227</v>
+        <v>14.241523304130386</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>20.82831579044063</v>
+        <v>16.722424859968235</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>4.3242995587930655E-2</v>
+        <v>5.481370557055576E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>16.949772404053306</v>
+        <v>13.775050680383194</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>19.377597519813985</v>
+        <v>16.202875796143875</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.10993175324210214</v>
+        <v>8.3913949117474296E-2</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5906,13 +5906,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5920,13 +5920,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5949,13 +5949,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5963,22 +5963,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6002,6 +6002,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6018,17 +6029,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13628,20 +13628,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.3898191560616213E-2</v>
+        <v>6.3855421686746988E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.3898191560616213E-2</v>
+        <v>6.3855421686746988E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>6.3898191560616213E-2</v>
+        <v>6.3855421686746988E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>6.0281312793034163E-2</v>
+        <v>6.0240963855421693E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14827,50 +14827,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8836119575306007E-2</v>
+        <v>7.8783351088307807E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>0.10051919060819138</v>
+        <v>0.10045190868676689</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>0.11468668334479851</v>
+        <v>0.11460991849650883</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.7248501028988785E-2</v>
+        <v>9.7183408324150108E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>7.4433229464293454E-2</v>
+        <v>7.4383408025562328E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>6.0723735029410919E-2</v>
+        <v>6.0683089959110106E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>4.80208125245562E-2</v>
+        <v>4.7988670079760654E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.8658070033022624E-2</v>
+        <v>2.8638887924566786E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.2415219372589286E-2</v>
+        <v>2.2400215879033337E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>2.2303424721628023E-2</v>
+        <v>2.2288496057155716E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>2.2965125762501769E-2</v>
+        <v>2.2949754192379612E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14884,43 +14884,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.85570085799575E-2</v>
+        <v>9.8491040033384561E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11713113419337548</v>
+        <v>0.11705273316647229</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6894019444489804E-2</v>
+        <v>9.6829164009787999E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5176420114910297E-2</v>
+        <v>7.5126101225944486E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9801590309325879E-2</v>
+        <v>5.9761562471100094E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7995910710777759E-2</v>
+        <v>4.7963784933862913E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.8405931621233466E-2</v>
+        <v>2.8386918280121527E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3930358562670159E-2</v>
+        <v>2.3914340919723259E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8560960219776882E-2</v>
+        <v>1.8548536551624421E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6570223566330922E-2</v>
+        <v>1.6559132385898304E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15702,16 +15702,16 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11308388340.359852</v>
+        <v>9046710672.2878819</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15726,8 +15726,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15742,8 +15742,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15758,8 +15758,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>11936105654.57239</v>
+        <v>9674427986.5004196</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>20.705977470257782</v>
+        <v>16.782566586060053</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>21.770912051292139</v>
+        <v>17.687067476395459</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15892,11 +15892,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>663099250.48454535</v>
+        <v>653846702.80336571</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15914,11 +15914,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>648044918.45501101</v>
+        <v>630086118.22697723</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15936,11 +15936,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>633332364.69274175</v>
+        <v>607188985.858868</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15968,11 +15968,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>618953829.81102157</v>
+        <v>585123928.11598301</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -16000,11 +16000,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>604901730.58437002</v>
+        <v>563860707.66681659</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>11714753425.226969</v>
+        <v>9371802740.1815758</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16652,11 +16652,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>8753945240.1114864</v>
+        <v>6528010099.3559494</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>11922277334.139175</v>
+        <v>9568116542.0279598</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16688,7 +16688,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>11922277334.139175</v>
+        <v>9568116542.0279598</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16718,19 +16718,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>11308388340.359848</v>
+        <v>9046710672.2878819</v>
       </c>
       <c r="C56" s="123">
-        <v>11476376990.788452</v>
+        <v>9189126412.0592842</v>
       </c>
       <c r="D56" s="123">
-        <v>11818908282.530104</v>
+        <v>9480135567.5542622</v>
       </c>
       <c r="E56" s="123">
-        <v>12170500991.837341</v>
+        <v>9779684253.9565125</v>
       </c>
       <c r="F56" s="123">
-        <v>12715753999.968578</v>
+        <v>10245838099.369934</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16739,19 +16739,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>11308388340.359846</v>
+        <v>9046710672.2878838</v>
       </c>
       <c r="C57" s="123">
-        <v>11629531547.472206</v>
+        <v>9325672023.4796867</v>
       </c>
       <c r="D57" s="123">
-        <v>12317647223.512791</v>
+        <v>9924663459.6226807</v>
       </c>
       <c r="E57" s="123">
-        <v>13073029883.693321</v>
+        <v>10583880788.585932</v>
       </c>
       <c r="F57" s="123">
-        <v>14350248364.725914</v>
+        <v>11701610024.736546</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16760,19 +16760,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>11308388340.359844</v>
+        <v>9046710672.2878838</v>
       </c>
       <c r="C58" s="341">
-        <v>11832039003.209286</v>
+        <v>9494256863.4140472</v>
       </c>
       <c r="D58" s="123">
-        <v>13011512513.445005</v>
+        <v>10502126679.177025</v>
       </c>
       <c r="E58" s="123">
-        <v>14396760395.708538</v>
+        <v>11685202072.98748</v>
       </c>
       <c r="F58" s="123">
-        <v>16953815807.281326</v>
+        <v>13866673764.9659</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16791,19 +16791,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>11308388340.359842</v>
+        <v>9046710672.2878838</v>
       </c>
       <c r="C59" s="341">
-        <v>12052525699.760794</v>
+        <v>9665474811.5622597</v>
       </c>
       <c r="D59" s="123">
-        <v>13808238612.99328</v>
+        <v>11120631761.98378</v>
       </c>
       <c r="E59" s="123">
-        <v>16005181961.221029</v>
+        <v>12933423051.518507</v>
       </c>
       <c r="F59" s="123">
-        <v>20416939448.341022</v>
+        <v>16552819224.067139</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16822,19 +16822,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>11308388340.35984</v>
+        <v>9046710672.2878838</v>
       </c>
       <c r="C60" s="341">
-        <v>12271603836.008841</v>
+        <v>9824116343.9132061</v>
       </c>
       <c r="D60" s="123">
-        <v>14644622605.031479</v>
+        <v>11726093812.342928</v>
       </c>
       <c r="E60" s="123">
-        <v>17797677148.47332</v>
+        <v>14230570095.96228</v>
       </c>
       <c r="F60" s="123">
-        <v>24671047517.628006</v>
+        <v>19629581241.677238</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16853,19 +16853,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>11308388340.359842</v>
+        <v>9046710672.2878838</v>
       </c>
       <c r="C61" s="341">
-        <v>12477971534.528822</v>
+        <v>9963447858.5559425</v>
       </c>
       <c r="D61" s="123">
-        <v>15478410848.436249</v>
+        <v>12288853416.963266</v>
       </c>
       <c r="E61" s="123">
-        <v>19700385567.78577</v>
+        <v>15514325764.510073</v>
       </c>
       <c r="F61" s="123">
-        <v>29679464410.002403</v>
+        <v>23006732277.651726</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16945,23 +16945,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>20.705977470257782</v>
+        <v>16.782566586060053</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>20.705977470257782</v>
+        <v>16.782566586060053</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>20.705977470257782</v>
+        <v>16.782566586060053</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>20.705977470257782</v>
+        <v>16.782566586060053</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>20.705977470257782</v>
+        <v>16.782566586060053</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16972,23 +16972,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20.705977470257775</v>
+        <v>16.782566586060053</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>20.997393222739927</v>
+        <v>17.029620121313162</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>21.591594163558845</v>
+        <v>17.534443821077375</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>22.201514260473687</v>
+        <v>18.054081342006516</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>23.147383610887051</v>
+        <v>18.862734624755138</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16999,23 +16999,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>20.705977470257771</v>
+        <v>16.782566586060057</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>21.263075757055155</v>
+        <v>17.266490540824769</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>22.456773944501201</v>
+        <v>18.305581810673161</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>23.767162508054998</v>
+        <v>19.449149030714295</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>25.982797813086581</v>
+        <v>21.388112797570475</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17026,23 +17026,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>20.705977470257768</v>
+        <v>16.782566586060057</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>21.614372481246345</v>
+        <v>17.558940523970712</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>23.660446187066064</v>
+        <v>19.30732733471805</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>26.063483850349769</v>
+        <v>21.359649353204173</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>30.49929677581132</v>
+        <v>25.143924142092885</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17053,23 +17053,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>20.705977470257764</v>
+        <v>16.782566586060057</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>21.99685841957567</v>
+        <v>17.855958251482413</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>25.042554652308528</v>
+        <v>20.380269605879221</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>28.853668661207283</v>
+        <v>23.524981682469022</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>36.506897760897282</v>
+        <v>29.803674061169659</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17080,23 +17080,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>20.705977470257761</v>
+        <v>16.782566586060057</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>22.376900879374141</v>
+        <v>18.131159233257197</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>26.493459042468071</v>
+        <v>21.430585675176928</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>31.963172383518394</v>
+        <v>25.775187759320847</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>43.886646934360321</v>
+        <v>35.141040105141897</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17106,23 +17106,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>20.705977470257764</v>
+        <v>16.782566586060057</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>22.734894100932696</v>
+        <v>18.372862455948113</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>27.93986049722492</v>
+        <v>22.406824327184516</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>35.263866831347897</v>
+        <v>28.002163350818204</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>52.574921848836851</v>
+        <v>40.999501423114417</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>25.982797813086581</v>
+        <v>21.388112797570475</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17179,7 +17179,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>22.201514260473687</v>
+        <v>18.054081342006516</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>21.591594163558845</v>
+        <v>17.534443821077375</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>20.997393222739927</v>
+        <v>17.029620121313162</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>20.705977470257771</v>
+        <v>16.782566586060057</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17462,14 +17462,14 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>9165666300</v>
+        <v>7332533040</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17478,7 +17478,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>15.9</v>
+        <v>12.72</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17531,7 +17531,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>16.763149965079879</v>
+        <v>13.453115372354064</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17574,11 +17574,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>537454699.18377888</v>
+        <v>529955331.28819132</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17596,11 +17596,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>525252873.45944917</v>
+        <v>510696920.38423985</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17618,11 +17618,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>513328065.59584892</v>
+        <v>492138354.10614377</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17640,11 +17640,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>501673986.46076989</v>
+        <v>474254200.31919664</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17662,11 +17662,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>490284489.70407498</v>
+        <v>457019951.08450925</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18226,7 +18226,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>9495033018.9134293</v>
+        <v>7596026415.130743</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18234,11 +18234,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>7095241025.0161295</v>
+        <v>5291077771.0188265</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18249,7 +18249,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>9663235139.4200516</v>
+        <v>7755142528.201107</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18270,7 +18270,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>9663235139.4200516</v>
+        <v>7755142528.201107</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18300,19 +18300,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>9165666299.9999962</v>
+        <v>7332533040</v>
       </c>
       <c r="C51" s="123">
-        <v>9301824332.9285812</v>
+        <v>7447963736.8707056</v>
       </c>
       <c r="D51" s="123">
-        <v>9579452534.4829006</v>
+        <v>7683832255.8171406</v>
       </c>
       <c r="E51" s="123">
-        <v>9864425189.2971668</v>
+        <v>7926622228.8469315</v>
       </c>
       <c r="F51" s="123">
-        <v>10306363241.934212</v>
+        <v>8304448888.3959465</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18321,19 +18321,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>9165666299.9999962</v>
+        <v>7332533040.0000019</v>
       </c>
       <c r="C52" s="123">
-        <v>9425959047.4995041</v>
+        <v>7558636581.7837286</v>
       </c>
       <c r="D52" s="123">
-        <v>9983690040.861042</v>
+        <v>8044130664.1411581</v>
       </c>
       <c r="E52" s="123">
-        <v>10595942218.946455</v>
+        <v>8578438991.2517395</v>
       </c>
       <c r="F52" s="123">
-        <v>11631152368.880617</v>
+        <v>9484380039.9639416</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18342,19 +18342,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>9165666299.9999943</v>
+        <v>7332533040.0000038</v>
       </c>
       <c r="C53" s="123">
-        <v>9590095236.2014408</v>
+        <v>7695277837.7761898</v>
       </c>
       <c r="D53" s="123">
-        <v>10546081206.892492</v>
+        <v>8512175712.7948647</v>
       </c>
       <c r="E53" s="123">
-        <v>11668851264.787868</v>
+        <v>9471081079.4160709</v>
       </c>
       <c r="F53" s="123">
-        <v>13741393868.355684</v>
+        <v>11239205852.794197</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18363,19 +18363,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>9165666299.9999943</v>
+        <v>7332533040.0000029</v>
       </c>
       <c r="C54" s="123">
-        <v>9768803945.4670963</v>
+        <v>7834053278.6315641</v>
       </c>
       <c r="D54" s="123">
-        <v>11191843037.948223</v>
+        <v>9013485981.1757069</v>
       </c>
       <c r="E54" s="123">
-        <v>12972507886.359283</v>
+        <v>10482788195.720387</v>
       </c>
       <c r="F54" s="123">
-        <v>16548322202.812235</v>
+        <v>13416378423.31089</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18384,19 +18384,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>9165666299.9999943</v>
+        <v>7332533040.0000019</v>
       </c>
       <c r="C55" s="123">
-        <v>9946370989.5089912</v>
+        <v>7962635292.5388746</v>
       </c>
       <c r="D55" s="123">
-        <v>11869748353.803341</v>
+        <v>9504224620.8366394</v>
       </c>
       <c r="E55" s="123">
-        <v>14425359719.548777</v>
+        <v>11534150829.683891</v>
       </c>
       <c r="F55" s="123">
-        <v>19996358633.26091</v>
+        <v>15910153229.158379</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18405,19 +18405,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>9165666299.9999943</v>
+        <v>7332533040.0000019</v>
       </c>
       <c r="C56" s="123">
-        <v>10113635979.249605</v>
+        <v>8075566165.6086483</v>
       </c>
       <c r="D56" s="123">
-        <v>12545549765.454197</v>
+        <v>9960352106.7190208</v>
       </c>
       <c r="E56" s="123">
-        <v>15967541497.598978</v>
+        <v>12574659495.861166</v>
       </c>
       <c r="F56" s="123">
-        <v>24055776876.172607</v>
+        <v>18647399113.257225</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18467,23 +18467,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>15.9</v>
+        <v>12.72</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>15.9</v>
+        <v>12.72</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>15.9</v>
+        <v>12.72</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>15.9</v>
+        <v>12.72</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>15.9</v>
+        <v>12.72</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18494,23 +18494,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>15.899999999999993</v>
+        <v>12.72</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>16.13619807362662</v>
+        <v>12.920241643124649</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>16.617809367364611</v>
+        <v>13.329410963553466</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>17.112161339522579</v>
+        <v>13.750587171023913</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>17.878806644613928</v>
+        <v>14.406016213518001</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18521,23 +18521,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>15.899999999999993</v>
+        <v>12.720000000000004</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>16.351538878874756</v>
+        <v>13.112229675038604</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>17.319054224098313</v>
+        <v>13.954433139230087</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>18.381149364040084</v>
+        <v>14.881316370955231</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>20.17696440303547</v>
+        <v>16.45288380566797</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18548,23 +18548,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>15.89999999999999</v>
+        <v>12.720000000000006</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>16.636271632058317</v>
+        <v>13.349266012514706</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>18.294653732875986</v>
+        <v>14.76636715799247</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>20.242361988470723</v>
+        <v>16.429813636430939</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>23.837673700476678</v>
+        <v>19.497041154490617</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18575,23 +18575,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>15.89999999999999</v>
+        <v>12.720000000000004</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>16.94628384331719</v>
+        <v>13.59000459467326</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>19.414879232879855</v>
+        <v>15.636007509971614</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>22.503860455089075</v>
+        <v>18.184857145841558</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>28.706949872778431</v>
+        <v>23.273858107908985</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18602,23 +18602,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>15.89999999999999</v>
+        <v>12.720000000000004</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>17.254315568219297</v>
+        <v>13.813060284702718</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>20.59086515352115</v>
+        <v>16.487308890058824</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>25.024173042479799</v>
+        <v>20.00869246046781</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>34.688378549069419</v>
+        <v>27.599895966495989</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18628,23 +18628,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>15.89999999999999</v>
+        <v>12.720000000000004</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>17.544475961345956</v>
+        <v>14.008965396566698</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>21.763201358391342</v>
+        <v>17.278569098335211</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>27.699449391019588</v>
+        <v>21.81369901980749</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>41.730392511796381</v>
+        <v>32.348291569461772</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18679,7 +18679,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>20.17696440303547</v>
+        <v>16.45288380566797</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>17.112161339522579</v>
+        <v>13.750587171023913</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>16.617809367364611</v>
+        <v>13.329410963553466</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>16.13619807362662</v>
+        <v>12.920241643124649</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18770,7 +18770,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>15.899999999999993</v>
+        <v>12.720000000000004</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18870,7 +18870,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.93</v>
+        <v>-14.94</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18919,7 +18919,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>22.723702959467442</v>
+        <v>18.646199895960851</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18934,11 +18934,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 景津装备(603279.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18959,8 +18959,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18981,8 +18981,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18992,8 +18992,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -19006,8 +19006,8 @@
       <c r="B11" s="159" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19025,8 +19025,8 @@
         <v>9.6365877843450409E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19043,8 +19043,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.12333037284725878</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19061,8 +19061,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.10533530085337128</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19088,21 +19088,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19110,14 +19110,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.93</v>
+        <v>14.94</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19125,14 +19125,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>20.705977470257782</v>
+        <v>16.782566586060053</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19152,8 +19152,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19163,8 +19163,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19172,14 +19172,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>21.591594163558845</v>
+        <v>17.534443821077375</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19189,8 +19189,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19210,8 +19210,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19221,8 +19221,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19230,14 +19230,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>20.997393222739927</v>
+        <v>17.029620121313162</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19247,8 +19247,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19268,8 +19268,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19279,8 +19279,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19288,14 +19288,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>22.201514260473687</v>
+        <v>18.054081342006516</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -19306,8 +19306,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>21.594737994778029</v>
+        <v>17.537406585310361</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19369,8 +19369,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="370"/>
+      <c r="F49" s="370"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19380,8 +19380,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19389,14 +19389,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>20.705977470257771</v>
+        <v>16.782566586060057</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="370"/>
+      <c r="F51" s="370"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19406,8 +19406,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="370"/>
+      <c r="F52" s="370"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19427,8 +19427,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="370"/>
+      <c r="F55" s="370"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19438,8 +19438,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="370"/>
+      <c r="F56" s="370"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19447,14 +19447,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>25.982797813086581</v>
+        <v>21.388112797570475</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="370"/>
+      <c r="F57" s="370"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19464,8 +19464,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>21.769702959467441</v>
+        <v>17.692199895960851</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19535,7 +19535,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>21.770912051292139</v>
+        <v>17.687067476395459</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19598,7 +19598,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>5.0020115170913503E-2</v>
+        <v>6.1548199527054877E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.6178692272519435</v>
+        <v>1.4246045348312761</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>8.8481239483686167</v>
+        <v>5.8033375360894999</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>10.465993175620561</v>
+        <v>7.2279420709207756</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.5192404234863941</v>
+        <v>0.59146165465997691</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.93</v>
+        <v>14.94</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19721,7 +19721,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19083819809107139</v>
+        <v>0.11852527700395354</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.8622080000000001</v>
+        <v>1.7325716886663638</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>11.14608791524733</v>
+        <v>8.0528902576062116</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19769,7 +19769,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>13.008295915247331</v>
+        <v>9.7854619462725747</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.4024587317765792</v>
+        <v>0.44690530268615114</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>2.5500533997864046</v>
+        <v>2.4809015558378498</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19819,7 +19819,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>18.278262390654227</v>
+        <v>14.241523304130386</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>20.82831579044063</v>
+        <v>16.722424859968235</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>4.3242995587930655E-2</v>
+        <v>5.481370557055576E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>16.949772404053306</v>
+        <v>13.775050680383194</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19887,7 +19887,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>19.377597519813985</v>
+        <v>16.202875796143875</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.10993175324210214</v>
+        <v>8.3913949117474296E-2</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19954,19 +19954,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="372"/>
+    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="360"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="370" t="s">
+      <c r="B2" s="358" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,45 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D346785-C700-40F1-A4DB-8403DF5D56D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35C8C23-B2CD-455F-93B8-3D9621E5DA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="DDM" sheetId="10" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId3"/>
+    <sheet name="BS" sheetId="3" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId7"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
-    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,20 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="561">
   <si>
     <t>Sales</t>
   </si>
@@ -411,10 +406,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1348,10 +1339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1504,10 +1491,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1525,10 +1508,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1760,71 +1739,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1864,32 +1783,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1987,30 +1880,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2034,58 +1903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2103,23 +1920,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2162,10 +1962,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2284,10 +2080,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2334,133 +2126,1148 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
   <si>
     <t>CN</t>
@@ -3171,7 +3978,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3920,33 +4727,55 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3961,10 +4790,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{0387460B-B4E6-4B1C-A60A-A789B5B2569B}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{C0F7CDBB-44D8-4143-B469-38A121901CE2}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4076,7 +4910,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>14.93</v>
+            <v>14.94</v>
           </cell>
         </row>
         <row r="13">
@@ -4101,7 +4935,7 @@
         </row>
         <row r="86">
           <cell r="C86">
-            <v>0.06</v>
+            <v>7.4999999999999997E-2</v>
           </cell>
         </row>
         <row r="92">
@@ -4331,6 +5165,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45797</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>CN</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>景津装备</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>576457000</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>603279.SS</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>14.94</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>8612.2675799999997</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>IND_01</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (CNY) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>17.692199895960851</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>0.11852527700395354</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>603279.SS (CNY)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>7.2279420709207756</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>9.7854619462725747</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>16.722424859968235</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>16.202875796143875</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>898092603.37923622</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>213321214.99999997</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>-213321215</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>12828070.849551909</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-6249607</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>6578463.8495519087</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-226167766.80719703</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>865118716.5321629</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>678503300.42159104</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>7.8783351088307807E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>6.3855421686746988E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>0.90057693104856651</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>0.2026552385945618</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>0.25219765791020438</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>0.16696657384597549</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>0.18367566206999161</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.62476296032712075</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.70676723862204571</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.9427325871638936</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.9427325871638936</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>15.693643536790917</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>270317959.52999997</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.46892996273789717</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>6.0553888114002474E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>0.30099118789407647</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>1723046566.25</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>867841842.9465394</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.5054754178482339</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>30193430.795999996</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>5.2377594158801083E-2</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>16.782566586060053</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>-0.43338518935931036</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.08</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>21.39 CNY</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.05</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>5</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>18.05 CNY</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.03</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>5</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>17.53 CNY</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.01</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>5</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>17.03 CNY</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>16.78 CNY</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>17.692199895960851</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.95400000000000007</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>603279.SS</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>1.4246045348312761</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>5.8033375360894999</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>7.2279420709207756</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.59146165465997691</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>1.7325716886663638</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>8.0528902576062116</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>9.7854619462725747</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.44690530268615114</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>2.4809015558378498</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>14.241523304130386</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>16.722424859968235</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>5.481370557055576E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>2.4278251157606801</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>13.775050680383194</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>16.202875796143875</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>8.3913949117474296E-2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4347,24 +6924,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4378,7 +6955,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4387,15 +6964,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C6" s="51">
         <v>576457000</v>
@@ -4404,7 +6981,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4414,7 +6991,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4427,26 +7004,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="C12" s="50">
         <v>14.94</v>
@@ -4456,17 +7033,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4480,7 +7057,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4494,7 +7071,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="C16" s="50">
         <v>1</v>
@@ -4507,71 +7084,71 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="361" t="s">
-        <v>356</v>
-      </c>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="361"/>
-      <c r="F18" s="361"/>
+      <c r="B18" s="371" t="s">
+        <v>468</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>464</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
         <v/>
       </c>
       <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4592,7 +7169,7 @@
         <v>17.692199895960851</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4605,7 +7182,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4616,7 +7193,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4624,7 +7201,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4635,7 +7212,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F29" s="302">
         <v>0.45</v>
@@ -4643,7 +7220,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4654,7 +7231,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F30" s="312">
         <v>0.3</v>
@@ -4662,7 +7239,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4673,7 +7250,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4681,7 +7258,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4692,7 +7269,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4704,7 +7281,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4712,27 +7289,27 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="361" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="361"/>
-      <c r="F36" s="361"/>
+    <row r="36" spans="1:6">
+      <c r="B36" s="371" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
-        <v>336</v>
-      </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4740,17 +7317,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="362" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
+      <c r="B40" s="367" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4766,17 +7343,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="362" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="362"/>
-      <c r="D43" s="362"/>
-      <c r="E43" s="362"/>
-      <c r="F43" s="362"/>
+      <c r="B43" s="367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4789,7 +7366,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4801,17 +7378,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="362" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="362"/>
-      <c r="D47" s="362"/>
-      <c r="E47" s="362"/>
-      <c r="F47" s="362"/>
+      <c r="B47" s="367" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4823,17 +7400,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="362" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="362"/>
-      <c r="D50" s="362"/>
-      <c r="E50" s="362"/>
-      <c r="F50" s="362"/>
+      <c r="B50" s="367" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4848,7 +7425,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4863,7 +7440,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4876,12 +7453,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4893,17 +7470,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="362" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="362"/>
-      <c r="D58" s="362"/>
-      <c r="E58" s="362"/>
-      <c r="F58" s="362"/>
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4915,17 +7492,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="362" t="s">
-        <v>335</v>
-      </c>
-      <c r="C61" s="365"/>
-      <c r="D61" s="365"/>
-      <c r="E61" s="365"/>
-      <c r="F61" s="365"/>
+      <c r="B61" s="367" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4937,26 +7514,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="361" t="s">
-        <v>340</v>
-      </c>
-      <c r="C64" s="361"/>
-      <c r="D64" s="361"/>
-      <c r="E64" s="361"/>
-      <c r="F64" s="361"/>
+      <c r="B64" s="371" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="361" t="s">
-        <v>358</v>
-      </c>
-      <c r="C65" s="361"/>
-      <c r="D65" s="361"/>
-      <c r="E65" s="361"/>
-      <c r="F65" s="361"/>
+      <c r="B65" s="371" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4969,7 +7546,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4982,7 +7559,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -4992,14 +7569,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>6.3855421686746988E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -5008,18 +7585,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -5074,7 +7651,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -5085,33 +7662,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="361" t="s">
-        <v>359</v>
-      </c>
-      <c r="C80" s="361"/>
-      <c r="D80" s="361"/>
-      <c r="E80" s="361"/>
-      <c r="F80" s="361"/>
+      <c r="B80" s="371" t="s">
+        <v>471</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5120,7 +7697,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5129,7 +7706,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5141,31 +7718,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="361" t="s">
-        <v>360</v>
-      </c>
-      <c r="C89" s="361"/>
-      <c r="D89" s="361"/>
-      <c r="E89" s="361"/>
-      <c r="F89" s="361"/>
+      <c r="B89" s="371" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="361" t="s">
-        <v>361</v>
-      </c>
-      <c r="C90" s="361"/>
-      <c r="D90" s="361"/>
-      <c r="E90" s="361"/>
-      <c r="F90" s="361"/>
+      <c r="B90" s="371" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5173,7 +7750,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5186,7 +7763,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5198,36 +7775,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="361" t="s">
-        <v>362</v>
-      </c>
-      <c r="C97" s="361"/>
-      <c r="D97" s="361"/>
-      <c r="E97" s="361"/>
-      <c r="F97" s="361"/>
+      <c r="B97" s="371" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="361" t="s">
-        <v>341</v>
-      </c>
-      <c r="C101" s="361"/>
-      <c r="D101" s="361"/>
-      <c r="E101" s="361"/>
-      <c r="F101" s="361"/>
+      <c r="B101" s="371" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5240,7 +7817,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5253,7 +7830,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5262,7 +7839,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5271,12 +7848,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5289,7 +7866,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5302,7 +7879,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5315,12 +7892,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5333,7 +7910,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5345,17 +7922,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="361" t="s">
-        <v>363</v>
-      </c>
-      <c r="C116" s="361"/>
-      <c r="D116" s="361"/>
-      <c r="E116" s="361"/>
-      <c r="F116" s="361"/>
+      <c r="B116" s="371" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5368,7 +7945,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5381,7 +7958,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5389,30 +7966,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="362" t="s">
-        <v>364</v>
-      </c>
-      <c r="C123" s="362"/>
-      <c r="D123" s="362"/>
-      <c r="E123" s="362"/>
-      <c r="F123" s="362"/>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>473</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5527,7 +8104,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5539,17 +8116,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="366" t="s">
-        <v>367</v>
-      </c>
-      <c r="C134" s="366"/>
-      <c r="D134" s="366"/>
-      <c r="E134" s="366"/>
-      <c r="F134" s="366"/>
+      <c r="B134" s="369" t="s">
+        <v>474</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5558,31 +8135,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="364" t="s">
-        <v>365</v>
-      </c>
-      <c r="C138" s="364"/>
-      <c r="D138" s="364"/>
-      <c r="E138" s="364"/>
-      <c r="F138" s="364"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="361" t="s">
-        <v>366</v>
-      </c>
-      <c r="C139" s="361"/>
-      <c r="D139" s="361"/>
-      <c r="E139" s="361"/>
-      <c r="F139" s="361"/>
+      <c r="B138" s="370" t="s">
+        <v>353</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="B139" s="371" t="s">
+        <v>476</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5591,7 +8168,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5600,7 +8177,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5613,7 +8190,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5626,7 +8203,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5655,7 +8232,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5668,7 +8245,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5681,7 +8258,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5690,12 +8267,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5724,7 +8301,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5737,7 +8314,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5750,7 +8327,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5759,12 +8336,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5793,7 +8370,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5806,7 +8383,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5819,7 +8396,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5828,12 +8405,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5862,7 +8439,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5875,7 +8452,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5888,7 +8465,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5897,7 +8474,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5906,113 +8483,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="368" t="s">
-        <v>373</v>
-      </c>
-      <c r="C179" s="361"/>
-      <c r="D179" s="361"/>
-      <c r="E179" s="361"/>
-      <c r="F179" s="361"/>
+      <c r="B179" s="372" t="s">
+        <v>477</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="365" t="s">
-        <v>377</v>
-      </c>
-      <c r="C182" s="365"/>
-      <c r="D182" s="365"/>
-      <c r="E182" s="365"/>
-      <c r="F182" s="365"/>
+      <c r="B182" s="373" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="362" t="s">
-        <v>378</v>
-      </c>
-      <c r="C188" s="362"/>
-      <c r="D188" s="362"/>
-      <c r="E188" s="362"/>
-      <c r="F188" s="362"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="34.35" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>478</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="367" t="s">
-        <v>379</v>
-      </c>
-      <c r="C191" s="367"/>
-      <c r="D191" s="367"/>
-      <c r="E191" s="367"/>
-      <c r="F191" s="367"/>
+      <c r="B191" s="368" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="367" t="s">
-        <v>380</v>
-      </c>
-      <c r="C192" s="367"/>
-      <c r="D192" s="367"/>
-      <c r="E192" s="367"/>
-      <c r="F192" s="367"/>
+      <c r="B192" s="368" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6029,6 +8595,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6053,7 +8630,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6118,7 +8695,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6134,7 +8711,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="106">
         <v>1</v>
@@ -6142,7 +8719,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="351">
         <v>6129461219</v>
@@ -6178,7 +8755,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="351">
         <v>4407422084</v>
@@ -6214,7 +8791,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="351">
         <v>456603351</v>
@@ -6250,7 +8827,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="352">
         <v>304923157</v>
@@ -6286,7 +8863,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="351">
         <v>151760727</v>
@@ -6322,7 +8899,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6338,7 +8915,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6354,7 +8931,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6370,7 +8947,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="351">
         <v>6249607</v>
@@ -6404,7 +8981,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="351">
         <v>37086796</v>
@@ -6438,7 +9015,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="351">
         <v>260714131</v>
@@ -6474,7 +9051,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="353">
         <v>848231191</v>
@@ -6510,7 +9087,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="351">
         <v>0</v>
@@ -6546,13 +9123,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="351">
         <v>213321215</v>
@@ -6586,7 +9163,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="351"/>
       <c r="D20" s="351"/>
@@ -6602,7 +9179,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="351"/>
       <c r="D21" s="351"/>
@@ -6618,7 +9195,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C22" s="351">
         <v>1040530375</v>
@@ -6654,7 +9231,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C23" s="351">
         <v>-241780101</v>
@@ -6690,7 +9267,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C24" s="351">
         <v>-865081548</v>
@@ -6752,15 +9329,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>465</v>
+        <v>559</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
@@ -6797,7 +9374,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
@@ -6834,7 +9411,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
@@ -6871,7 +9448,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
@@ -6908,7 +9485,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6945,7 +9522,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6961,12 +9538,12 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="333">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -7015,7 +9592,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="333">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7064,7 +9641,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="329">
         <f>IF(C36="","",C36+C37)</f>
@@ -7113,7 +9690,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="333">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7162,7 +9739,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="346">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7211,7 +9788,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C41" s="346">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7260,7 +9837,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="333">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7309,7 +9886,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7358,7 +9935,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7407,7 +9984,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="349">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7456,7 +10033,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="333">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -7505,7 +10082,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="334">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -7554,7 +10131,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="333">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -7603,12 +10180,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="333">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -7657,7 +10234,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="333">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -7706,12 +10283,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7760,7 +10337,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7809,7 +10386,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7858,7 +10435,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7907,13 +10484,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" s="333">
         <f>IF(C$4="","",-C19)</f>
@@ -7962,7 +10539,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="333">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -8011,7 +10588,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="333">
         <f>IF(C$4="","",-C21)</f>
@@ -8060,7 +10637,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8109,7 +10686,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
@@ -8158,7 +10735,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8213,7 +10790,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8312,7 +10889,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8411,7 +10988,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -8427,13 +11004,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
@@ -8482,7 +11059,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -8516,7 +11093,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
@@ -8550,7 +11127,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -8599,7 +11176,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -8671,7 +11248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8691,7 +11268,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="99">
         <v>45657</v>
@@ -8707,7 +11284,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8718,27 +11295,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="19">
         <f>162848038.15+872554672.94+94302275.67+50452913.4</f>
@@ -8749,7 +11326,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="19">
         <v>1723046566.25</v>
@@ -8760,7 +11337,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -8770,7 +11347,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -8781,7 +11358,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="19">
         <v>2566018245.5700002</v>
@@ -8791,7 +11368,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8802,7 +11379,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8812,7 +11389,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19">
         <v>50322384.659999996</v>
@@ -8823,7 +11400,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8833,7 +11410,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8844,7 +11421,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="19">
         <f>21769366.3+88430040.42</f>
@@ -8855,7 +11432,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8866,7 +11443,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="19">
         <v>0</v>
@@ -8878,7 +11455,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="19">
         <v>66428111.5</v>
@@ -8890,7 +11467,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8901,7 +11478,7 @@
         <v>2005445209.1280003</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8919,27 +11496,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>185</v>
-      </c>
       <c r="G14" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H14" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8948,7 +11525,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8959,7 +11536,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -8968,7 +11545,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8979,7 +11556,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8988,7 +11565,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8999,7 +11576,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -9008,7 +11585,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -9019,7 +11596,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="19">
         <f>2276113969.89+136330644.02+1116002.95</f>
@@ -9029,7 +11606,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -9040,7 +11617,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -9049,7 +11626,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -9060,7 +11637,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="19">
         <v>308495762.44999999</v>
@@ -9069,7 +11646,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9080,7 +11657,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="19">
         <v>128281177.8</v>
@@ -9092,7 +11669,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19">
         <v>126021439.64</v>
@@ -9104,7 +11681,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -9115,7 +11692,7 @@
         <v>372233909.82849997</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -9128,30 +11705,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H26" s="186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19">
         <v>200146666.66999999</v>
       </c>
       <c r="F27" s="187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
@@ -9164,13 +11741,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G28" s="12">
         <v>0</v>
@@ -9179,13 +11756,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="190" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9198,13 +11775,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
@@ -9214,14 +11791,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>200146666.66999999</v>
       </c>
       <c r="F31" s="190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
@@ -9231,14 +11808,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>3801371953.8299999</v>
       </c>
       <c r="F32" s="192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
@@ -9251,7 +11828,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="84">
         <v>4001518620.5</v>
@@ -9264,24 +11841,24 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H34" s="198" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F35" s="199" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G35" s="193">
         <f>C12+C24</f>
@@ -9294,13 +11871,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19">
         <v>70000000</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9310,13 +11887,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19">
         <v>171292.86</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9326,13 +11903,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19">
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9342,13 +11919,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G39" s="191">
         <f>C7+C17+C19+C20</f>
@@ -9361,14 +11938,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>70171292.859999999</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9381,14 +11958,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>136752472.12</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9401,13 +11978,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" s="84">
         <v>206923764.97999999</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9420,7 +11997,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -9431,21 +12008,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="F45" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9477,20 +12054,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C49" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D49" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -9504,7 +12081,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9518,19 +12095,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C53" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D53" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" s="253"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9544,7 +12121,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9561,19 +12138,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C57" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D57" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57" s="253"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -9584,7 +12161,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -9598,19 +12175,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D61" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F61" s="253"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9621,12 +12198,12 @@
         <v>0</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9637,21 +12214,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F65" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9662,12 +12239,12 @@
         <v>867841842.9465394</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9677,7 +12254,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9687,7 +12264,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9697,7 +12274,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9710,19 +12287,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C72" s="234" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D72" s="182" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F72" s="253"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9733,12 +12310,12 @@
         <v>-427602361.6517303</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9749,12 +12326,12 @@
         <v>4.0295534374372126</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9762,12 +12339,12 @@
         <v>855204723.3034606</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9775,7 +12352,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9783,19 +12360,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D78" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" s="253"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9809,7 +12386,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9823,7 +12400,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9837,7 +12414,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9851,7 +12428,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9862,15 +12439,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9887,7 +12464,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9904,7 +12481,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9921,7 +12498,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9943,7 +12520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9969,7 +12546,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -10022,12 +12599,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -10045,7 +12622,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -10059,7 +12636,7 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="327">
         <f>AVERAGE(G4:I4)*0.9</f>
@@ -10116,7 +12693,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="328">
         <f>C25</f>
@@ -10171,7 +12748,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
@@ -10226,7 +12803,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="328">
         <f>C35</f>
@@ -10281,7 +12858,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10338,7 +12915,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="328">
         <f>BS!$G$39*BS!D58</f>
@@ -10393,7 +12970,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" s="328">
         <f>-C4*C78</f>
@@ -10448,7 +13025,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10505,7 +13082,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="328">
         <f>C50</f>
@@ -10560,7 +13137,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10615,7 +13192,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -10670,7 +13247,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10727,7 +13304,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10784,7 +13361,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="328">
         <f>-C4*C85</f>
@@ -10792,7 +13369,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10810,14 +13387,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="328">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10835,7 +13412,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
@@ -10911,12 +13488,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10934,7 +13511,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10955,7 +13532,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
@@ -11012,7 +13589,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="328">
         <f>-C4*C29</f>
@@ -11069,7 +13646,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
@@ -11130,14 +13707,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="63">
         <f>G28</f>
@@ -11145,7 +13722,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11205,7 +13782,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11256,7 +13833,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -11315,21 +13892,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-182442565.75</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11379,7 +13956,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="340">
         <f>AVERAGE(G34:J34)</f>
@@ -11387,7 +13964,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11438,7 +14015,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="329">
         <f>C33+C34</f>
@@ -11499,7 +14076,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11622,7 +14199,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -11681,21 +14258,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11749,12 +14326,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -11772,14 +14349,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="328">
         <f>-BS!G31*Normalized_FCF!C54</f>
@@ -11834,7 +14411,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11889,7 +14466,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11946,7 +14523,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
@@ -12005,23 +14582,23 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" s="87">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -12041,14 +14618,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>2.3119466464108229E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12068,7 +14645,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -12127,17 +14704,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12192,7 +14769,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12247,7 +14824,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12302,7 +14879,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12357,13 +14934,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12413,7 +14990,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12472,17 +15049,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12507,7 +15084,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12532,7 +15109,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12557,7 +15134,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12587,12 +15164,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12610,7 +15187,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12631,7 +15208,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -12688,7 +15265,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -12745,7 +15322,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -12802,7 +15379,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12859,7 +15436,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12916,7 +15493,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12924,7 +15501,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>466</v>
+        <v>560</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12975,7 +15552,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -13032,7 +15609,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -13089,7 +15666,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13146,7 +15723,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -13261,7 +15838,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13318,7 +15895,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C85" s="264">
         <v>0</v>
@@ -13344,7 +15921,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -13368,7 +15945,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13429,7 +16006,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13548,7 +16125,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13603,7 +16180,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C93" s="356">
         <v>0.1</v>
@@ -13624,7 +16201,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
@@ -13683,7 +16260,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C96" s="62"/>
       <c r="D96" s="27"/>
@@ -13704,7 +16281,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C97" s="77">
         <f>C4/G4-1</f>
@@ -13761,7 +16338,7 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
@@ -13821,12 +16398,12 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="54"/>
       <c r="D100" s="56"/>
       <c r="E100" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="37"/>
@@ -13844,17 +16421,17 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E101" s="268"/>
       <c r="G101" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="344">
         <f>BS!G32</f>
@@ -13911,7 +16488,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C103" s="345">
         <f>BS!C4</f>
@@ -13968,7 +16545,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="345">
         <f>BS!C6+BS!C7</f>
@@ -14025,7 +16602,7 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C105" s="344">
         <f>BS!G30</f>
@@ -14082,7 +16659,7 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" s="344">
         <f>BS!G27</f>
@@ -14143,14 +16720,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
@@ -14166,7 +16743,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -14223,7 +16800,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C110" s="94">
         <f>C104/C$4</f>
@@ -14280,7 +16857,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C111" s="94">
         <f>BS!$G$38/C$4</f>
@@ -14311,14 +16888,14 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -14370,7 +16947,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
@@ -14426,7 +17003,7 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="55"/>
       <c r="D117" s="55"/>
@@ -14480,7 +17057,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
@@ -14534,7 +17111,7 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C119" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
@@ -14588,7 +17165,7 @@
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="B120" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C120" s="15">
         <f>C102/C106</f>
@@ -14645,7 +17222,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
@@ -14721,12 +17298,12 @@
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C123" s="54"/>
       <c r="D123" s="56"/>
       <c r="E123" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F123" s="56"/>
       <c r="G123" s="37"/>
@@ -14744,7 +17321,7 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C124" s="179"/>
       <c r="D124" s="27"/>
@@ -14823,7 +17400,7 @@
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14879,7 +17456,7 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
@@ -15624,7 +18201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15641,32 +18218,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15677,7 +18254,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15687,7 +18264,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15698,7 +18275,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15708,15 +18285,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15726,13 +18303,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="369"/>
-      <c r="F7" s="369"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15742,13 +18319,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="369"/>
-      <c r="F8" s="369"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15758,13 +18335,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="369"/>
-      <c r="F9" s="369"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15778,7 +18355,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15792,7 +18369,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -15809,7 +18386,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15819,13 +18396,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15835,7 +18412,7 @@
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15845,7 +18422,7 @@
     </row>
     <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -15862,19 +18439,19 @@
     </row>
     <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="128" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="129" t="s">
         <v>107</v>
-      </c>
-      <c r="C20" s="128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="128" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="129" t="s">
-        <v>110</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -16640,7 +19217,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16663,7 +19240,7 @@
     <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
@@ -16677,7 +19254,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16898,7 +19475,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -17127,19 +19704,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D73" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E73" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17264,20 +19841,20 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C80" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="3:3">
@@ -17384,7 +19961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -17401,32 +19978,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
@@ -17437,7 +20014,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17447,7 +20024,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17458,7 +20035,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17468,13 +20045,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369"/>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17491,7 +20068,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17501,13 +20078,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17517,7 +20094,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17527,7 +20104,7 @@
     </row>
     <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
@@ -17544,19 +20121,19 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -18222,7 +20799,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -18245,7 +20822,7 @@
     <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
@@ -18259,7 +20836,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18430,7 +21007,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18649,19 +21226,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D68" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E68" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F68" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18786,20 +21363,20 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C75" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="3:3">
@@ -18835,7 +21412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -18850,20 +21427,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18875,14 +21452,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18904,14 +21481,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="107">
         <f>DCF!C3</f>
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18924,7 +21501,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18934,11 +21511,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="371" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 景津装备(603279.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="371"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18949,7 +21526,7 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
@@ -18959,8 +21536,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="371"/>
-      <c r="F8" s="371"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18971,7 +21548,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
@@ -18981,8 +21558,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="371"/>
-      <c r="F9" s="371"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18992,8 +21569,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="371"/>
-      <c r="F10" s="371"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -19004,10 +21581,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>444</v>
-      </c>
-      <c r="E11" s="371"/>
-      <c r="F11" s="371"/>
+        <v>424</v>
+      </c>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19018,15 +21595,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>9.6365877843450409E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="371"/>
-      <c r="F12" s="371"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19037,14 +21614,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.12333037284725878</v>
       </c>
-      <c r="E13" s="371"/>
-      <c r="F13" s="371"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19055,18 +21632,18 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.10533530085337128</v>
       </c>
-      <c r="E14" s="371"/>
-      <c r="F14" s="371"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -19075,38 +21652,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="371" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="372"/>
+      <c r="E18" s="377" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="372"/>
-      <c r="F19" s="372"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="372"/>
-      <c r="F20" s="372"/>
+        <v>298</v>
+      </c>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -19116,12 +21693,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="372"/>
-      <c r="F21" s="372"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -19131,44 +21708,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="372"/>
-      <c r="F22" s="372"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="370"/>
-      <c r="F25" s="370"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="164">
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="370"/>
-      <c r="F26" s="370"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19178,55 +21755,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="370"/>
-      <c r="F27" s="370"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="370"/>
-      <c r="F28" s="370"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="370"/>
-      <c r="F31" s="370"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C32" s="164">
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="370"/>
-      <c r="F32" s="370"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19236,55 +21813,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="370"/>
-      <c r="F33" s="370"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="370"/>
-      <c r="F34" s="370"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="370"/>
-      <c r="F37" s="370"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" s="164">
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="370"/>
-      <c r="F38" s="370"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19294,24 +21871,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="370"/>
-      <c r="F39" s="370"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19324,7 +21901,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19333,12 +21910,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19353,39 +21930,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="370"/>
-      <c r="F49" s="370"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19395,55 +21972,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="370"/>
-      <c r="F51" s="370"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="370"/>
-      <c r="F52" s="370"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="370"/>
-      <c r="F55" s="370"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="164">
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="370"/>
-      <c r="F56" s="370"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19453,23 +22030,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="370"/>
-      <c r="F57" s="370"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19480,7 +22057,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19489,7 +22066,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19498,15 +22075,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" s="252" t="s">
         <v>303</v>
-      </c>
-      <c r="E63" s="252" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19514,24 +22091,24 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C65" s="151">
         <v>3.5934836391919099E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
@@ -19542,20 +22119,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19565,19 +22142,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19587,14 +22164,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19603,7 +22180,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19612,12 +22189,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19627,7 +22204,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
@@ -19640,12 +22217,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19654,7 +22231,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19666,7 +22243,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19676,7 +22253,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
@@ -19687,7 +22264,7 @@
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19699,12 +22276,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19717,7 +22294,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19729,12 +22306,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19743,7 +22320,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19755,7 +22332,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19765,7 +22342,7 @@
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
@@ -19776,7 +22353,7 @@
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19785,14 +22362,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19803,7 +22380,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19815,7 +22392,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19827,17 +22404,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>16.722424859968235</v>
       </c>
       <c r="D99" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19849,12 +22426,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19863,7 +22440,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19873,7 +22450,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19883,17 +22460,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>16.202875796143875</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19905,32 +22482,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -19949,24 +22526,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6250F0AA-52FB-4191-8409-8BDDA69B8C32}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533D86B1-3154-40D5-AEA0-A4D315097B86}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="360"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="358" t="s">
-        <v>456</v>
-      </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
+      <c r="B2" s="379" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/603279.SS_Valuation.xlsx
+++ b/financial_models/opportunities/603279.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35C8C23-B2CD-455F-93B8-3D9621E5DA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70711BF7-205A-44BE-938B-948D302BE624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4754,8 +4754,22 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4766,16 +4780,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -4790,11 +4795,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>14.94</v>
+        <v>14.92</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>8612.2675799999997</v>
+        <v>8600.7384399999992</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11852527700395354</v>
+        <v>0.11905397545440977</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5577,13 +5577,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5595,13 +5595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5621,13 +5621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5656,13 +5656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5678,13 +5678,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5770,7 +5770,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="373"/>
@@ -5841,7 +5841,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.8783351088307807E-2</v>
+        <v>7.8888958797541459E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.3855421686746988E-2</v>
+        <v>6.3941018766756036E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5951,13 +5951,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6245,13 +6245,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6394,13 +6394,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6413,13 +6413,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
       <c r="B139" s="371" t="s">
@@ -6761,7 +6761,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
       <c r="C179" s="371"/>
@@ -6804,13 +6804,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6818,22 +6818,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6857,12 +6857,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,15 +6878,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7026,7 +7026,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>14.94</v>
+        <v>14.92</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>8612.2675799999997</v>
+        <v>8600.7384399999992</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11852527700395354</v>
+        <v>0.11905397545440977</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7299,13 +7299,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7317,13 +7317,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7343,13 +7343,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7378,13 +7378,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7400,13 +7400,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -7470,13 +7470,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7492,7 +7492,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="373"/>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>7.8783351088307807E-2</v>
+        <v>7.8888958797541459E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>6.3855421686746988E-2</v>
+        <v>6.3941018766756036E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7673,13 +7673,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7967,13 +7967,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8116,13 +8116,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8135,13 +8135,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="371" t="s">
@@ -8483,7 +8483,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
       <c r="C179" s="371"/>
@@ -8526,13 +8526,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -8540,22 +8540,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8579,6 +8579,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8595,17 +8606,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B